--- a/repair/back/doc/estimate/supervision.xlsx
+++ b/repair/back/doc/estimate/supervision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seongjaehyeon/anb_origin2/repair/back/doc/estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E1C678-A8B2-EF46-8250-2F797BA8C81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802455B7-FAD9-9F4E-A2DF-272867C7781F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19780" tabRatio="731" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19780" tabRatio="731" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -9854,7 +9854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3104" applyFont="1">
       <alignment vertical="center"/>
@@ -10231,9 +10231,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -10256,6 +10253,186 @@
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="3113" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="3113" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="245" fontId="113" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="71" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="72" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="59" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="60" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="73" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="71" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="6" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="54" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="71" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="72" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="2" borderId="59" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="2" borderId="60" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="49" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="7" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="68" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="69" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="75" fillId="2" borderId="21" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10286,419 +10463,248 @@
     <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="121" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="121" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="93" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="49" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="7" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="49" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="7" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="68" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="69" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="73" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="74" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="71" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="6" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="54" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="71" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="72" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="59" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="2" borderId="60" xfId="2637" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="75" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="50" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="75" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="50" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" xfId="3102" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="71" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="72" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="59" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="7" borderId="60" xfId="3102" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="73" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="245" fontId="113" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="3113" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3113" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="121" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="121" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="93" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3119">
@@ -14481,9 +14487,9 @@
       <sheetName val="견적서(조정D)"/>
       <sheetName val="견적서(D)"/>
       <sheetName val="숫자읽기"/>
-      <sheetName val="갑지"/>
       <sheetName val="산출내역(감리)"/>
       <sheetName val="계약서1"/>
+      <sheetName val="갑지"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -14961,36 +14967,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" s="34" customFormat="1" ht="42" customHeight="1">
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="139" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="202"/>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="202"/>
-      <c r="Y1" s="202"/>
-      <c r="Z1" s="202"/>
-      <c r="AA1" s="202"/>
-      <c r="AB1" s="202"/>
-      <c r="AC1" s="202"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="139"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
+      <c r="Z1" s="139"/>
+      <c r="AA1" s="139"/>
+      <c r="AB1" s="139"/>
+      <c r="AC1" s="139"/>
     </row>
     <row r="2" spans="2:29" s="34" customFormat="1" ht="12" customHeight="1">
       <c r="B2" s="36"/>
@@ -15023,36 +15029,36 @@
       <c r="AC2" s="38"/>
     </row>
     <row r="3" spans="2:29" s="34" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="203" t="s">
+      <c r="B3" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="203"/>
-      <c r="Q3" s="203"/>
-      <c r="R3" s="203"/>
-      <c r="S3" s="203"/>
-      <c r="T3" s="203"/>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="203"/>
-      <c r="X3" s="203"/>
-      <c r="Y3" s="203"/>
-      <c r="Z3" s="203"/>
-      <c r="AA3" s="203"/>
-      <c r="AB3" s="203"/>
-      <c r="AC3" s="203"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="140"/>
+      <c r="S3" s="140"/>
+      <c r="T3" s="140"/>
+      <c r="U3" s="140"/>
+      <c r="V3" s="140"/>
+      <c r="W3" s="140"/>
+      <c r="X3" s="140"/>
+      <c r="Y3" s="140"/>
+      <c r="Z3" s="140"/>
+      <c r="AA3" s="140"/>
+      <c r="AB3" s="140"/>
+      <c r="AC3" s="140"/>
     </row>
     <row r="4" spans="2:29" s="34" customFormat="1" ht="7.5" customHeight="1">
       <c r="B4" s="43"/>
@@ -15115,12 +15121,12 @@
       <c r="AC5" s="38"/>
     </row>
     <row r="6" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B6" s="201" t="s">
+      <c r="B6" s="137" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
       <c r="F6" s="36" t="s">
         <v>59</v>
       </c>
@@ -15149,23 +15155,23 @@
       <c r="AC6" s="38"/>
     </row>
     <row r="7" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B7" s="201" t="s">
+      <c r="B7" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="201"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="204">
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="141">
         <v>46072</v>
       </c>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="204"/>
-      <c r="K7" s="204"/>
-      <c r="L7" s="204"/>
-      <c r="M7" s="204"/>
-      <c r="N7" s="204"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="141"/>
       <c r="O7" s="36"/>
       <c r="P7" s="36"/>
       <c r="Q7" s="36"/>
@@ -15183,21 +15189,21 @@
       <c r="AC7" s="38"/>
     </row>
     <row r="8" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B8" s="201" t="s">
+      <c r="B8" s="137" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
-      <c r="F8" s="135" t="s">
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="136"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
       <c r="M8" s="42"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
@@ -15217,21 +15223,21 @@
       <c r="AC8" s="38"/>
     </row>
     <row r="9" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B9" s="201" t="s">
+      <c r="B9" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="201"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
-      <c r="F9" s="135" t="s">
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="135"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
       <c r="M9" s="36"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
@@ -15251,38 +15257,38 @@
       <c r="AC9" s="38"/>
     </row>
     <row r="10" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B10" s="201" t="s">
+      <c r="B10" s="137" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="201"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="201"/>
-      <c r="F10" s="135" t="s">
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="143" t="s">
         <v>176</v>
       </c>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="38"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="38"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
+      <c r="L10" s="143"/>
+      <c r="M10" s="143"/>
+      <c r="N10" s="143"/>
+      <c r="O10" s="143"/>
+      <c r="P10" s="143"/>
+      <c r="Q10" s="143"/>
+      <c r="R10" s="143"/>
+      <c r="S10" s="143"/>
+      <c r="T10" s="143"/>
+      <c r="U10" s="143"/>
+      <c r="V10" s="143"/>
+      <c r="W10" s="143"/>
+      <c r="X10" s="143"/>
+      <c r="Y10" s="143"/>
+      <c r="Z10" s="143"/>
+      <c r="AA10" s="143"/>
+      <c r="AB10" s="143"/>
+      <c r="AC10" s="143"/>
     </row>
     <row r="11" spans="2:29" s="34" customFormat="1" ht="13.5" hidden="1" customHeight="1" thickBot="1">
       <c r="B11" s="40"/>
@@ -15375,36 +15381,36 @@
       <c r="AC13" s="38"/>
     </row>
     <row r="14" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B14" s="192" t="s">
+      <c r="B14" s="142" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="192"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-      <c r="F14" s="192"/>
-      <c r="G14" s="192"/>
-      <c r="H14" s="192"/>
-      <c r="I14" s="192"/>
-      <c r="J14" s="192"/>
-      <c r="K14" s="192"/>
-      <c r="L14" s="192"/>
-      <c r="M14" s="192"/>
-      <c r="N14" s="192"/>
-      <c r="O14" s="192"/>
-      <c r="P14" s="192"/>
-      <c r="Q14" s="192"/>
-      <c r="R14" s="192"/>
-      <c r="S14" s="192"/>
-      <c r="T14" s="192"/>
-      <c r="U14" s="192"/>
-      <c r="V14" s="192"/>
-      <c r="W14" s="192"/>
-      <c r="X14" s="192"/>
-      <c r="Y14" s="192"/>
-      <c r="Z14" s="192"/>
-      <c r="AA14" s="192"/>
-      <c r="AB14" s="192"/>
-      <c r="AC14" s="192"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="142"/>
+      <c r="N14" s="142"/>
+      <c r="O14" s="142"/>
+      <c r="P14" s="142"/>
+      <c r="Q14" s="142"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="142"/>
+      <c r="T14" s="142"/>
+      <c r="U14" s="142"/>
+      <c r="V14" s="142"/>
+      <c r="W14" s="142"/>
+      <c r="X14" s="142"/>
+      <c r="Y14" s="142"/>
+      <c r="Z14" s="142"/>
+      <c r="AA14" s="142"/>
+      <c r="AB14" s="142"/>
+      <c r="AC14" s="142"/>
     </row>
     <row r="15" spans="2:29" s="34" customFormat="1" ht="10" customHeight="1">
       <c r="B15" s="123"/>
@@ -15437,36 +15443,36 @@
       <c r="AC15" s="124"/>
     </row>
     <row r="16" spans="2:29" s="34" customFormat="1" ht="70.5" customHeight="1">
-      <c r="B16" s="198" t="s">
+      <c r="B16" s="138" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="198"/>
-      <c r="D16" s="198"/>
-      <c r="E16" s="198"/>
-      <c r="F16" s="198"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="198"/>
-      <c r="I16" s="198"/>
-      <c r="J16" s="198"/>
-      <c r="K16" s="198"/>
-      <c r="L16" s="198"/>
-      <c r="M16" s="198"/>
-      <c r="N16" s="198"/>
-      <c r="O16" s="198"/>
-      <c r="P16" s="198"/>
-      <c r="Q16" s="198"/>
-      <c r="R16" s="198"/>
-      <c r="S16" s="198"/>
-      <c r="T16" s="198"/>
-      <c r="U16" s="198"/>
-      <c r="V16" s="198"/>
-      <c r="W16" s="198"/>
-      <c r="X16" s="198"/>
-      <c r="Y16" s="198"/>
-      <c r="Z16" s="198"/>
-      <c r="AA16" s="198"/>
-      <c r="AB16" s="198"/>
-      <c r="AC16" s="198"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
+      <c r="M16" s="138"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="138"/>
+      <c r="Q16" s="138"/>
+      <c r="R16" s="138"/>
+      <c r="S16" s="138"/>
+      <c r="T16" s="138"/>
+      <c r="U16" s="138"/>
+      <c r="V16" s="138"/>
+      <c r="W16" s="138"/>
+      <c r="X16" s="138"/>
+      <c r="Y16" s="138"/>
+      <c r="Z16" s="138"/>
+      <c r="AA16" s="138"/>
+      <c r="AB16" s="138"/>
+      <c r="AC16" s="138"/>
     </row>
     <row r="17" spans="2:29" s="34" customFormat="1" ht="5" customHeight="1">
       <c r="B17" s="123"/>
@@ -15499,36 +15505,36 @@
       <c r="AC17" s="124"/>
     </row>
     <row r="18" spans="2:29" s="34" customFormat="1" ht="39" customHeight="1">
-      <c r="B18" s="198" t="s">
+      <c r="B18" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="198"/>
-      <c r="D18" s="198"/>
-      <c r="E18" s="198"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="198"/>
-      <c r="I18" s="198"/>
-      <c r="J18" s="198"/>
-      <c r="K18" s="198"/>
-      <c r="L18" s="198"/>
-      <c r="M18" s="198"/>
-      <c r="N18" s="198"/>
-      <c r="O18" s="198"/>
-      <c r="P18" s="198"/>
-      <c r="Q18" s="198"/>
-      <c r="R18" s="198"/>
-      <c r="S18" s="198"/>
-      <c r="T18" s="198"/>
-      <c r="U18" s="198"/>
-      <c r="V18" s="198"/>
-      <c r="W18" s="198"/>
-      <c r="X18" s="198"/>
-      <c r="Y18" s="198"/>
-      <c r="Z18" s="198"/>
-      <c r="AA18" s="198"/>
-      <c r="AB18" s="198"/>
-      <c r="AC18" s="198"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="138"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="138"/>
+      <c r="Q18" s="138"/>
+      <c r="R18" s="138"/>
+      <c r="S18" s="138"/>
+      <c r="T18" s="138"/>
+      <c r="U18" s="138"/>
+      <c r="V18" s="138"/>
+      <c r="W18" s="138"/>
+      <c r="X18" s="138"/>
+      <c r="Y18" s="138"/>
+      <c r="Z18" s="138"/>
+      <c r="AA18" s="138"/>
+      <c r="AB18" s="138"/>
+      <c r="AC18" s="138"/>
     </row>
     <row r="19" spans="2:29" s="34" customFormat="1" ht="10" customHeight="1">
       <c r="B19" s="123"/>
@@ -15561,18 +15567,18 @@
       <c r="AC19" s="124"/>
     </row>
     <row r="20" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B20" s="192" t="s">
+      <c r="B20" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="192"/>
-      <c r="D20" s="192"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="192"/>
-      <c r="G20" s="192"/>
-      <c r="H20" s="192"/>
-      <c r="I20" s="192"/>
-      <c r="J20" s="192"/>
-      <c r="K20" s="192"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="142"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
       <c r="L20" s="123"/>
       <c r="M20" s="123"/>
       <c r="N20" s="123"/>
@@ -15597,32 +15603,32 @@
       <c r="C21" s="123"/>
       <c r="D21" s="123"/>
       <c r="E21" s="123"/>
-      <c r="F21" s="200" t="s">
+      <c r="F21" s="145" t="s">
         <v>152</v>
       </c>
-      <c r="G21" s="200"/>
-      <c r="H21" s="200"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="200"/>
-      <c r="L21" s="134" t="str">
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="133" t="str">
         <f>F8</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="M21" s="134"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="134"/>
-      <c r="S21" s="134"/>
-      <c r="T21" s="134"/>
-      <c r="U21" s="134"/>
-      <c r="V21" s="134"/>
-      <c r="W21" s="134"/>
-      <c r="X21" s="134"/>
-      <c r="Y21" s="134"/>
-      <c r="Z21" s="134"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="133"/>
+      <c r="T21" s="133"/>
+      <c r="U21" s="133"/>
+      <c r="V21" s="133"/>
+      <c r="W21" s="133"/>
+      <c r="X21" s="133"/>
+      <c r="Y21" s="133"/>
+      <c r="Z21" s="133"/>
       <c r="AA21" s="125"/>
       <c r="AB21" s="125"/>
       <c r="AC21" s="125"/>
@@ -15632,31 +15638,31 @@
       <c r="C22" s="123"/>
       <c r="D22" s="123"/>
       <c r="E22" s="123"/>
-      <c r="F22" s="200" t="s">
+      <c r="F22" s="145" t="s">
         <v>153</v>
       </c>
-      <c r="G22" s="200"/>
-      <c r="H22" s="200"/>
-      <c r="I22" s="200"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="200"/>
-      <c r="L22" s="134" t="s">
+      <c r="G22" s="145"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="M22" s="134"/>
-      <c r="N22" s="134"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="134"/>
-      <c r="Q22" s="134"/>
-      <c r="R22" s="134"/>
-      <c r="S22" s="134"/>
-      <c r="T22" s="134"/>
-      <c r="U22" s="134"/>
-      <c r="V22" s="134"/>
-      <c r="W22" s="134"/>
-      <c r="X22" s="134"/>
-      <c r="Y22" s="134"/>
-      <c r="Z22" s="134"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="133"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="133"/>
+      <c r="Q22" s="133"/>
+      <c r="R22" s="133"/>
+      <c r="S22" s="133"/>
+      <c r="T22" s="133"/>
+      <c r="U22" s="133"/>
+      <c r="V22" s="133"/>
+      <c r="W22" s="133"/>
+      <c r="X22" s="133"/>
+      <c r="Y22" s="133"/>
+      <c r="Z22" s="133"/>
       <c r="AA22" s="125"/>
       <c r="AB22" s="125"/>
       <c r="AC22" s="125"/>
@@ -15666,31 +15672,31 @@
       <c r="C23" s="123"/>
       <c r="D23" s="123"/>
       <c r="E23" s="123"/>
-      <c r="F23" s="200" t="s">
+      <c r="F23" s="145" t="s">
         <v>154</v>
       </c>
-      <c r="G23" s="200"/>
-      <c r="H23" s="200"/>
-      <c r="I23" s="200"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="200"/>
-      <c r="L23" s="134" t="s">
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="M23" s="134"/>
-      <c r="N23" s="134"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="134"/>
-      <c r="Q23" s="134"/>
-      <c r="R23" s="134"/>
-      <c r="S23" s="134"/>
-      <c r="T23" s="134"/>
-      <c r="U23" s="134"/>
-      <c r="V23" s="134"/>
-      <c r="W23" s="134"/>
-      <c r="X23" s="134"/>
-      <c r="Y23" s="134"/>
-      <c r="Z23" s="134"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="133"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="133"/>
+      <c r="S23" s="133"/>
+      <c r="T23" s="133"/>
+      <c r="U23" s="133"/>
+      <c r="V23" s="133"/>
+      <c r="W23" s="133"/>
+      <c r="X23" s="133"/>
+      <c r="Y23" s="133"/>
+      <c r="Z23" s="133"/>
       <c r="AA23" s="125"/>
       <c r="AB23" s="125"/>
       <c r="AC23" s="125"/>
@@ -15700,31 +15706,31 @@
       <c r="C24" s="123"/>
       <c r="D24" s="123"/>
       <c r="E24" s="123"/>
-      <c r="F24" s="200" t="s">
+      <c r="F24" s="145" t="s">
         <v>155</v>
       </c>
-      <c r="G24" s="200"/>
-      <c r="H24" s="200"/>
-      <c r="I24" s="200"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="200"/>
-      <c r="L24" s="134" t="s">
+      <c r="G24" s="145"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="M24" s="134"/>
-      <c r="N24" s="134"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="134"/>
-      <c r="S24" s="134"/>
-      <c r="T24" s="134"/>
-      <c r="U24" s="134"/>
-      <c r="V24" s="134"/>
-      <c r="W24" s="134"/>
-      <c r="X24" s="134"/>
-      <c r="Y24" s="134"/>
-      <c r="Z24" s="134"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="133"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="133"/>
+      <c r="Q24" s="133"/>
+      <c r="R24" s="133"/>
+      <c r="S24" s="133"/>
+      <c r="T24" s="133"/>
+      <c r="U24" s="133"/>
+      <c r="V24" s="133"/>
+      <c r="W24" s="133"/>
+      <c r="X24" s="133"/>
+      <c r="Y24" s="133"/>
+      <c r="Z24" s="133"/>
       <c r="AA24" s="125"/>
       <c r="AB24" s="125"/>
       <c r="AC24" s="125"/>
@@ -15734,15 +15740,15 @@
       <c r="C25" s="123"/>
       <c r="D25" s="123"/>
       <c r="E25" s="123"/>
-      <c r="F25" s="200" t="s">
+      <c r="F25" s="145" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="200"/>
-      <c r="H25" s="200"/>
-      <c r="I25" s="200"/>
-      <c r="J25" s="200"/>
-      <c r="K25" s="200"/>
-      <c r="L25" s="134"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="133"/>
       <c r="M25" s="125"/>
       <c r="N25" s="125"/>
       <c r="O25" s="125"/>
@@ -15792,18 +15798,18 @@
       <c r="AC26" s="124"/>
     </row>
     <row r="27" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B27" s="192" t="s">
+      <c r="B27" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="192"/>
-      <c r="D27" s="192"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="192"/>
-      <c r="G27" s="192"/>
-      <c r="H27" s="192"/>
-      <c r="I27" s="192"/>
-      <c r="J27" s="192"/>
-      <c r="K27" s="192"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="142"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
       <c r="L27" s="123"/>
       <c r="M27" s="123"/>
       <c r="N27" s="123"/>
@@ -15828,64 +15834,64 @@
       <c r="C28" s="123"/>
       <c r="D28" s="123"/>
       <c r="E28" s="123"/>
-      <c r="F28" s="195" t="s">
+      <c r="F28" s="148" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="195"/>
-      <c r="H28" s="195"/>
-      <c r="I28" s="195"/>
-      <c r="J28" s="195"/>
-      <c r="K28" s="195"/>
-      <c r="L28" s="195"/>
-      <c r="M28" s="195"/>
-      <c r="N28" s="195"/>
-      <c r="O28" s="195"/>
-      <c r="P28" s="195"/>
-      <c r="Q28" s="195"/>
-      <c r="R28" s="195"/>
-      <c r="S28" s="195"/>
-      <c r="T28" s="195"/>
-      <c r="U28" s="195"/>
-      <c r="V28" s="195"/>
-      <c r="W28" s="195"/>
-      <c r="X28" s="195"/>
-      <c r="Y28" s="195"/>
-      <c r="Z28" s="195"/>
-      <c r="AA28" s="195"/>
-      <c r="AB28" s="195"/>
-      <c r="AC28" s="195"/>
+      <c r="G28" s="148"/>
+      <c r="H28" s="148"/>
+      <c r="I28" s="148"/>
+      <c r="J28" s="148"/>
+      <c r="K28" s="148"/>
+      <c r="L28" s="148"/>
+      <c r="M28" s="148"/>
+      <c r="N28" s="148"/>
+      <c r="O28" s="148"/>
+      <c r="P28" s="148"/>
+      <c r="Q28" s="148"/>
+      <c r="R28" s="148"/>
+      <c r="S28" s="148"/>
+      <c r="T28" s="148"/>
+      <c r="U28" s="148"/>
+      <c r="V28" s="148"/>
+      <c r="W28" s="148"/>
+      <c r="X28" s="148"/>
+      <c r="Y28" s="148"/>
+      <c r="Z28" s="148"/>
+      <c r="AA28" s="148"/>
+      <c r="AB28" s="148"/>
+      <c r="AC28" s="148"/>
     </row>
     <row r="29" spans="2:29" s="34" customFormat="1" ht="33" customHeight="1">
       <c r="B29" s="123"/>
       <c r="C29" s="123"/>
       <c r="D29" s="123"/>
       <c r="E29" s="123"/>
-      <c r="F29" s="196" t="s">
+      <c r="F29" s="149" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="196"/>
-      <c r="H29" s="196"/>
-      <c r="I29" s="196"/>
-      <c r="J29" s="196"/>
-      <c r="K29" s="196"/>
-      <c r="L29" s="196"/>
-      <c r="M29" s="196"/>
-      <c r="N29" s="196"/>
-      <c r="O29" s="196"/>
-      <c r="P29" s="196"/>
-      <c r="Q29" s="196"/>
-      <c r="R29" s="196"/>
-      <c r="S29" s="196"/>
-      <c r="T29" s="196"/>
-      <c r="U29" s="196"/>
-      <c r="V29" s="196"/>
-      <c r="W29" s="196"/>
-      <c r="X29" s="196"/>
-      <c r="Y29" s="196"/>
-      <c r="Z29" s="196"/>
-      <c r="AA29" s="196"/>
-      <c r="AB29" s="196"/>
-      <c r="AC29" s="196"/>
+      <c r="G29" s="149"/>
+      <c r="H29" s="149"/>
+      <c r="I29" s="149"/>
+      <c r="J29" s="149"/>
+      <c r="K29" s="149"/>
+      <c r="L29" s="149"/>
+      <c r="M29" s="149"/>
+      <c r="N29" s="149"/>
+      <c r="O29" s="149"/>
+      <c r="P29" s="149"/>
+      <c r="Q29" s="149"/>
+      <c r="R29" s="149"/>
+      <c r="S29" s="149"/>
+      <c r="T29" s="149"/>
+      <c r="U29" s="149"/>
+      <c r="V29" s="149"/>
+      <c r="W29" s="149"/>
+      <c r="X29" s="149"/>
+      <c r="Y29" s="149"/>
+      <c r="Z29" s="149"/>
+      <c r="AA29" s="149"/>
+      <c r="AB29" s="149"/>
+      <c r="AC29" s="149"/>
     </row>
     <row r="30" spans="2:29" s="34" customFormat="1" ht="10" customHeight="1">
       <c r="B30" s="123"/>
@@ -15918,39 +15924,39 @@
       <c r="AC30" s="124"/>
     </row>
     <row r="31" spans="2:29" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B31" s="199" t="s">
+      <c r="B31" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="199"/>
-      <c r="D31" s="199"/>
-      <c r="E31" s="199"/>
-      <c r="F31" s="199"/>
-      <c r="G31" s="199"/>
-      <c r="H31" s="199"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="199"/>
-      <c r="K31" s="199"/>
-      <c r="L31" s="197" t="str">
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="150" t="str">
         <f>대가산출!D3</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="M31" s="197"/>
-      <c r="N31" s="197"/>
-      <c r="O31" s="197"/>
-      <c r="P31" s="197"/>
-      <c r="Q31" s="197"/>
-      <c r="R31" s="197"/>
-      <c r="S31" s="197"/>
-      <c r="T31" s="197"/>
-      <c r="U31" s="197"/>
-      <c r="V31" s="197"/>
-      <c r="W31" s="197"/>
-      <c r="X31" s="197"/>
-      <c r="Y31" s="197"/>
-      <c r="Z31" s="197"/>
-      <c r="AA31" s="197"/>
-      <c r="AB31" s="197"/>
-      <c r="AC31" s="197"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="150"/>
+      <c r="Q31" s="150"/>
+      <c r="R31" s="150"/>
+      <c r="S31" s="150"/>
+      <c r="T31" s="150"/>
+      <c r="U31" s="150"/>
+      <c r="V31" s="150"/>
+      <c r="W31" s="150"/>
+      <c r="X31" s="150"/>
+      <c r="Y31" s="150"/>
+      <c r="Z31" s="150"/>
+      <c r="AA31" s="150"/>
+      <c r="AB31" s="150"/>
+      <c r="AC31" s="150"/>
     </row>
     <row r="32" spans="2:29" s="34" customFormat="1" ht="10" customHeight="1">
       <c r="B32" s="123"/>
@@ -15983,18 +15989,18 @@
       <c r="AC32" s="124"/>
     </row>
     <row r="33" spans="2:33" s="34" customFormat="1" ht="20" customHeight="1">
-      <c r="B33" s="192" t="s">
+      <c r="B33" s="142" t="s">
         <v>167</v>
       </c>
-      <c r="C33" s="192"/>
-      <c r="D33" s="192"/>
-      <c r="E33" s="192"/>
-      <c r="F33" s="192"/>
-      <c r="G33" s="192"/>
-      <c r="H33" s="192"/>
-      <c r="I33" s="192"/>
-      <c r="J33" s="192"/>
-      <c r="K33" s="192"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="142"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="142"/>
       <c r="L33" s="123"/>
       <c r="M33" s="123"/>
       <c r="N33" s="123"/>
@@ -16045,36 +16051,36 @@
       <c r="AC34" s="41"/>
     </row>
     <row r="35" spans="2:33" s="34" customFormat="1" ht="19.5" customHeight="1">
-      <c r="B35" s="192" t="s">
+      <c r="B35" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="C35" s="193"/>
-      <c r="D35" s="193"/>
-      <c r="E35" s="193"/>
-      <c r="F35" s="193"/>
-      <c r="G35" s="193"/>
-      <c r="H35" s="193"/>
-      <c r="I35" s="193"/>
-      <c r="J35" s="193"/>
-      <c r="K35" s="193"/>
-      <c r="L35" s="193"/>
-      <c r="M35" s="193"/>
-      <c r="N35" s="193"/>
-      <c r="O35" s="193"/>
-      <c r="P35" s="193"/>
-      <c r="Q35" s="193"/>
-      <c r="R35" s="193"/>
-      <c r="S35" s="193"/>
-      <c r="T35" s="193"/>
-      <c r="U35" s="193"/>
-      <c r="V35" s="193"/>
-      <c r="W35" s="193"/>
-      <c r="X35" s="193"/>
-      <c r="Y35" s="193"/>
-      <c r="Z35" s="193"/>
-      <c r="AA35" s="193"/>
-      <c r="AB35" s="193"/>
-      <c r="AC35" s="193"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="146"/>
+      <c r="H35" s="146"/>
+      <c r="I35" s="146"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="146"/>
+      <c r="L35" s="146"/>
+      <c r="M35" s="146"/>
+      <c r="N35" s="146"/>
+      <c r="O35" s="146"/>
+      <c r="P35" s="146"/>
+      <c r="Q35" s="146"/>
+      <c r="R35" s="146"/>
+      <c r="S35" s="146"/>
+      <c r="T35" s="146"/>
+      <c r="U35" s="146"/>
+      <c r="V35" s="146"/>
+      <c r="W35" s="146"/>
+      <c r="X35" s="146"/>
+      <c r="Y35" s="146"/>
+      <c r="Z35" s="146"/>
+      <c r="AA35" s="146"/>
+      <c r="AB35" s="146"/>
+      <c r="AC35" s="146"/>
     </row>
     <row r="36" spans="2:33" s="34" customFormat="1" ht="19.5" customHeight="1">
       <c r="B36" s="36"/>
@@ -16092,36 +16098,36 @@
       <c r="N36" s="36"/>
     </row>
     <row r="37" spans="2:33" s="34" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B37" s="194" t="s">
+      <c r="B37" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="194"/>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="194"/>
-      <c r="K37" s="194"/>
-      <c r="L37" s="194"/>
-      <c r="M37" s="194"/>
-      <c r="N37" s="194"/>
-      <c r="O37" s="194"/>
-      <c r="P37" s="194"/>
-      <c r="Q37" s="194"/>
-      <c r="R37" s="194"/>
-      <c r="S37" s="194"/>
-      <c r="T37" s="194"/>
-      <c r="U37" s="194"/>
-      <c r="V37" s="194"/>
-      <c r="W37" s="194"/>
-      <c r="X37" s="194"/>
-      <c r="Y37" s="194"/>
-      <c r="Z37" s="194"/>
-      <c r="AA37" s="194"/>
-      <c r="AB37" s="194"/>
-      <c r="AC37" s="194"/>
+      <c r="C37" s="147"/>
+      <c r="D37" s="147"/>
+      <c r="E37" s="147"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="147"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="147"/>
+      <c r="J37" s="147"/>
+      <c r="K37" s="147"/>
+      <c r="L37" s="147"/>
+      <c r="M37" s="147"/>
+      <c r="N37" s="147"/>
+      <c r="O37" s="147"/>
+      <c r="P37" s="147"/>
+      <c r="Q37" s="147"/>
+      <c r="R37" s="147"/>
+      <c r="S37" s="147"/>
+      <c r="T37" s="147"/>
+      <c r="U37" s="147"/>
+      <c r="V37" s="147"/>
+      <c r="W37" s="147"/>
+      <c r="X37" s="147"/>
+      <c r="Y37" s="147"/>
+      <c r="Z37" s="147"/>
+      <c r="AA37" s="147"/>
+      <c r="AB37" s="147"/>
+      <c r="AC37" s="147"/>
       <c r="AG37" s="35"/>
     </row>
     <row r="38" spans="2:33">
@@ -33208,7 +33214,22 @@
       <c r="M1590" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="B35:AC35"/>
+    <mergeCell ref="B37:AC37"/>
+    <mergeCell ref="F28:AC28"/>
+    <mergeCell ref="F29:AC29"/>
+    <mergeCell ref="L31:AC31"/>
+    <mergeCell ref="B18:AC18"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="F21:K21"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="F24:K24"/>
+    <mergeCell ref="F25:K25"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
@@ -33219,21 +33240,7 @@
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B14:AC14"/>
-    <mergeCell ref="B18:AC18"/>
-    <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B27:K27"/>
-    <mergeCell ref="B31:K31"/>
-    <mergeCell ref="F21:K21"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F24:K24"/>
-    <mergeCell ref="F25:K25"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="B35:AC35"/>
-    <mergeCell ref="B37:AC37"/>
-    <mergeCell ref="F28:AC28"/>
-    <mergeCell ref="F29:AC29"/>
-    <mergeCell ref="L31:AC31"/>
+    <mergeCell ref="F10:AC10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33260,16 +33267,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="1" customFormat="1" ht="39" customHeight="1">
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="151" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
     </row>
     <row r="2" spans="2:9" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="B2" s="53"/>
@@ -33278,71 +33285,71 @@
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
       <c r="G2" s="53"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
     </row>
     <row r="3" spans="2:9" s="54" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="153" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="184" t="str">
+      <c r="C3" s="154"/>
+      <c r="D3" s="155" t="str">
         <f>"일금"&amp;NUMBERSTRING(H29,1)&amp;"원정 ("&amp;DOLLAR(H29,0)&amp;")-VAT별도"</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="186"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="157"/>
     </row>
     <row r="4" spans="2:9" s="54" customFormat="1" ht="38.25" hidden="1" customHeight="1">
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="158" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="188"/>
-      <c r="D4" s="189" t="str">
+      <c r="C4" s="159"/>
+      <c r="D4" s="160" t="str">
         <f>"일금 "&amp;NUMBERSTRING(H29,1)&amp;"원정"&amp;TEXT(H29,"(￦ #,##0)")&amp;" "</f>
         <v xml:space="preserve">일금 일백팔십만원정(₩ 1,800,000) </v>
       </c>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="191"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="162"/>
     </row>
     <row r="5" spans="2:9" s="54" customFormat="1" ht="38.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="168" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164" t="e">
+      <c r="C5" s="169"/>
+      <c r="D5" s="170" t="e">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="166"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="172"/>
     </row>
     <row r="6" spans="2:9" s="54" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B6" s="167" t="s">
+      <c r="B6" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="168"/>
-      <c r="D6" s="168"/>
-      <c r="E6" s="168"/>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="169"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="174"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="175"/>
     </row>
     <row r="7" spans="2:9" s="55" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="B7" s="170" t="s">
+      <c r="B7" s="176" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="171"/>
+      <c r="C7" s="177"/>
       <c r="D7" s="51" t="s">
         <v>73</v>
       </c>
@@ -33363,10 +33370,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B8" s="172" t="s">
+      <c r="B8" s="178" t="s">
         <v>185</v>
       </c>
-      <c r="C8" s="173"/>
+      <c r="C8" s="179"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -33552,10 +33559,10 @@
       <c r="I16" s="60"/>
     </row>
     <row r="17" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="180" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="175"/>
+      <c r="C17" s="181"/>
       <c r="D17" s="67"/>
       <c r="E17" s="69" t="s">
         <v>85</v>
@@ -33573,10 +33580,10 @@
       </c>
     </row>
     <row r="18" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B18" s="174" t="s">
+      <c r="B18" s="180" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="175"/>
+      <c r="C18" s="181"/>
       <c r="D18" s="67"/>
       <c r="E18" s="69" t="s">
         <v>85</v>
@@ -33594,10 +33601,10 @@
       </c>
     </row>
     <row r="19" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B19" s="174" t="s">
+      <c r="B19" s="180" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="175"/>
+      <c r="C19" s="181"/>
       <c r="D19" s="71"/>
       <c r="E19" s="73"/>
       <c r="F19" s="73"/>
@@ -33727,10 +33734,10 @@
       <c r="I25" s="60"/>
     </row>
     <row r="26" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B26" s="176" t="s">
+      <c r="B26" s="182" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="177"/>
+      <c r="C26" s="183"/>
       <c r="D26" s="67"/>
       <c r="E26" s="69"/>
       <c r="F26" s="69"/>
@@ -33744,15 +33751,15 @@
       </c>
     </row>
     <row r="27" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1">
-      <c r="B27" s="178" t="s">
+      <c r="B27" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="179"/>
-      <c r="D27" s="154" t="s">
+      <c r="C27" s="185"/>
+      <c r="D27" s="165" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="155"/>
-      <c r="F27" s="156"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="167"/>
       <c r="G27" s="114"/>
       <c r="H27" s="99">
         <f>H8+H17+H18+H19</f>
@@ -33761,13 +33768,13 @@
       <c r="I27" s="100"/>
     </row>
     <row r="28" spans="2:13" s="55" customFormat="1" ht="18" customHeight="1">
-      <c r="B28" s="152" t="s">
+      <c r="B28" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="153"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="155"/>
-      <c r="F28" s="156"/>
+      <c r="C28" s="164"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="167"/>
       <c r="G28" s="114"/>
       <c r="H28" s="99">
         <v>38097</v>
@@ -33775,13 +33782,13 @@
       <c r="I28" s="101"/>
     </row>
     <row r="29" spans="2:13" s="55" customFormat="1" ht="18" customHeight="1">
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="186" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="148"/>
-      <c r="D29" s="149"/>
-      <c r="E29" s="150"/>
-      <c r="F29" s="151"/>
+      <c r="C29" s="187"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="189"/>
+      <c r="F29" s="190"/>
       <c r="G29" s="115"/>
       <c r="H29" s="102">
         <f>H27-H28</f>
@@ -33790,13 +33797,13 @@
       <c r="I29" s="103"/>
     </row>
     <row r="30" spans="2:13" s="55" customFormat="1" ht="18" customHeight="1">
-      <c r="B30" s="152" t="s">
+      <c r="B30" s="163" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="153"/>
-      <c r="D30" s="154"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="156"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="165"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
       <c r="G30" s="114"/>
       <c r="H30" s="104" t="s">
         <v>102</v>
@@ -33804,13 +33811,13 @@
       <c r="I30" s="101"/>
     </row>
     <row r="31" spans="2:13" s="55" customFormat="1" ht="28" customHeight="1" thickBot="1">
-      <c r="B31" s="157" t="s">
+      <c r="B31" s="191" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="158"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="160"/>
-      <c r="F31" s="161"/>
+      <c r="C31" s="192"/>
+      <c r="D31" s="193"/>
+      <c r="E31" s="194"/>
+      <c r="F31" s="195"/>
       <c r="G31" s="116"/>
       <c r="H31" s="105">
         <f>H29</f>
@@ -33821,81 +33828,87 @@
       </c>
     </row>
     <row r="32" spans="2:13" s="108" customFormat="1" ht="23" customHeight="1">
-      <c r="B32" s="137"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="143" t="s">
+      <c r="B32" s="196"/>
+      <c r="C32" s="197"/>
+      <c r="D32" s="202" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="143"/>
-      <c r="F32" s="143"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="143"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="202"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="202"/>
       <c r="I32" s="107"/>
     </row>
     <row r="33" spans="2:9" s="108" customFormat="1" ht="23" customHeight="1">
-      <c r="B33" s="139"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="144" t="s">
+      <c r="B33" s="198"/>
+      <c r="C33" s="199"/>
+      <c r="D33" s="203" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="144"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="144"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="203"/>
       <c r="I33" s="109" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:9" s="108" customFormat="1" ht="23" customHeight="1">
-      <c r="B34" s="139"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="145" t="s">
+      <c r="B34" s="198"/>
+      <c r="C34" s="199"/>
+      <c r="D34" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="145"/>
-      <c r="F34" s="145"/>
-      <c r="G34" s="145"/>
-      <c r="H34" s="145"/>
+      <c r="E34" s="204"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="204"/>
+      <c r="H34" s="204"/>
       <c r="I34" s="109" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:9" s="108" customFormat="1" ht="23" customHeight="1">
-      <c r="B35" s="139"/>
-      <c r="C35" s="140"/>
-      <c r="D35" s="144" t="s">
+      <c r="B35" s="198"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="144"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="144"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="203"/>
       <c r="I35" s="109" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="2:9" s="108" customFormat="1" ht="23" customHeight="1" thickBot="1">
-      <c r="B36" s="141"/>
-      <c r="C36" s="142"/>
-      <c r="D36" s="146" t="s">
+      <c r="B36" s="200"/>
+      <c r="C36" s="201"/>
+      <c r="D36" s="205" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="146"/>
-      <c r="F36" s="146"/>
-      <c r="G36" s="146"/>
-      <c r="H36" s="146"/>
+      <c r="E36" s="205"/>
+      <c r="F36" s="205"/>
+      <c r="G36" s="205"/>
+      <c r="H36" s="205"/>
       <c r="I36" s="110" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="B32:C36"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B5:C5"/>
@@ -33909,18 +33922,12 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B32:C36"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -34416,99 +34423,99 @@
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="2:21" ht="4" customHeight="1">
-      <c r="B7" s="263" t="s">
+      <c r="B7" s="212" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="264"/>
-      <c r="D7" s="264"/>
-      <c r="E7" s="264"/>
-      <c r="F7" s="264"/>
-      <c r="G7" s="264"/>
-      <c r="H7" s="264"/>
-      <c r="I7" s="264"/>
-      <c r="J7" s="264"/>
-      <c r="K7" s="264"/>
-      <c r="L7" s="264"/>
-      <c r="M7" s="264"/>
-      <c r="N7" s="264"/>
-      <c r="O7" s="264"/>
-      <c r="P7" s="264"/>
-      <c r="Q7" s="264"/>
-      <c r="R7" s="264"/>
-      <c r="S7" s="264"/>
-      <c r="T7" s="264"/>
-      <c r="U7" s="264"/>
+      <c r="C7" s="213"/>
+      <c r="D7" s="213"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="213"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="213"/>
+      <c r="K7" s="213"/>
+      <c r="L7" s="213"/>
+      <c r="M7" s="213"/>
+      <c r="N7" s="213"/>
+      <c r="O7" s="213"/>
+      <c r="P7" s="213"/>
+      <c r="Q7" s="213"/>
+      <c r="R7" s="213"/>
+      <c r="S7" s="213"/>
+      <c r="T7" s="213"/>
+      <c r="U7" s="213"/>
     </row>
     <row r="8" spans="2:21" ht="66" customHeight="1">
-      <c r="B8" s="265" t="s">
+      <c r="B8" s="214" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="265"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
-      <c r="H8" s="265"/>
-      <c r="I8" s="265"/>
-      <c r="J8" s="265"/>
-      <c r="K8" s="265"/>
-      <c r="L8" s="265"/>
-      <c r="M8" s="265"/>
-      <c r="N8" s="265"/>
-      <c r="O8" s="265"/>
-      <c r="P8" s="265"/>
-      <c r="Q8" s="265"/>
-      <c r="R8" s="265"/>
-      <c r="S8" s="265"/>
-      <c r="T8" s="265"/>
-      <c r="U8" s="265"/>
+      <c r="C8" s="214"/>
+      <c r="D8" s="214"/>
+      <c r="E8" s="214"/>
+      <c r="F8" s="214"/>
+      <c r="G8" s="214"/>
+      <c r="H8" s="214"/>
+      <c r="I8" s="214"/>
+      <c r="J8" s="214"/>
+      <c r="K8" s="214"/>
+      <c r="L8" s="214"/>
+      <c r="M8" s="214"/>
+      <c r="N8" s="214"/>
+      <c r="O8" s="214"/>
+      <c r="P8" s="214"/>
+      <c r="Q8" s="214"/>
+      <c r="R8" s="214"/>
+      <c r="S8" s="214"/>
+      <c r="T8" s="214"/>
+      <c r="U8" s="214"/>
     </row>
     <row r="9" spans="2:21" ht="44" customHeight="1">
-      <c r="B9" s="266" t="str">
+      <c r="B9" s="215" t="str">
         <f>갑지!L21</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="C9" s="266"/>
-      <c r="D9" s="266"/>
-      <c r="E9" s="266"/>
-      <c r="F9" s="266"/>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266"/>
-      <c r="I9" s="266"/>
-      <c r="J9" s="266"/>
-      <c r="K9" s="266"/>
-      <c r="L9" s="266"/>
-      <c r="M9" s="266"/>
-      <c r="N9" s="266"/>
-      <c r="O9" s="266"/>
-      <c r="P9" s="266"/>
-      <c r="Q9" s="266"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
+      <c r="C9" s="215"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="215"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="215"/>
+      <c r="J9" s="215"/>
+      <c r="K9" s="215"/>
+      <c r="L9" s="215"/>
+      <c r="M9" s="215"/>
+      <c r="N9" s="215"/>
+      <c r="O9" s="215"/>
+      <c r="P9" s="215"/>
+      <c r="Q9" s="215"/>
+      <c r="R9" s="215"/>
+      <c r="S9" s="215"/>
+      <c r="T9" s="215"/>
+      <c r="U9" s="215"/>
     </row>
     <row r="10" spans="2:21" ht="4" customHeight="1">
-      <c r="B10" s="267"/>
-      <c r="C10" s="268"/>
-      <c r="D10" s="268"/>
-      <c r="E10" s="268"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
-      <c r="H10" s="268"/>
-      <c r="I10" s="268"/>
-      <c r="J10" s="268"/>
-      <c r="K10" s="268"/>
-      <c r="L10" s="268"/>
-      <c r="M10" s="268"/>
-      <c r="N10" s="268"/>
-      <c r="O10" s="268"/>
-      <c r="P10" s="268"/>
-      <c r="Q10" s="268"/>
-      <c r="R10" s="268"/>
-      <c r="S10" s="268"/>
-      <c r="T10" s="268"/>
-      <c r="U10" s="268"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="217"/>
+      <c r="D10" s="217"/>
+      <c r="E10" s="217"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="217"/>
+      <c r="K10" s="217"/>
+      <c r="L10" s="217"/>
+      <c r="M10" s="217"/>
+      <c r="N10" s="217"/>
+      <c r="O10" s="217"/>
+      <c r="P10" s="217"/>
+      <c r="Q10" s="217"/>
+      <c r="R10" s="217"/>
+      <c r="S10" s="217"/>
+      <c r="T10" s="217"/>
+      <c r="U10" s="217"/>
     </row>
     <row r="11" spans="2:21" ht="40" customHeight="1">
       <c r="B11" s="18"/>
@@ -34531,29 +34538,29 @@
       <c r="C15" s="18"/>
     </row>
     <row r="16" spans="2:21" ht="24">
-      <c r="B16" s="269">
+      <c r="B16" s="218">
         <f>갑지!F7</f>
         <v>46072</v>
       </c>
-      <c r="C16" s="269"/>
-      <c r="D16" s="269"/>
-      <c r="E16" s="269"/>
-      <c r="F16" s="269"/>
-      <c r="G16" s="269"/>
-      <c r="H16" s="269"/>
-      <c r="I16" s="269"/>
-      <c r="J16" s="269"/>
-      <c r="K16" s="269"/>
-      <c r="L16" s="269"/>
-      <c r="M16" s="269"/>
-      <c r="N16" s="269"/>
-      <c r="O16" s="269"/>
-      <c r="P16" s="269"/>
-      <c r="Q16" s="269"/>
-      <c r="R16" s="269"/>
-      <c r="S16" s="269"/>
-      <c r="T16" s="269"/>
-      <c r="U16" s="269"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="218"/>
+      <c r="G16" s="218"/>
+      <c r="H16" s="218"/>
+      <c r="I16" s="218"/>
+      <c r="J16" s="218"/>
+      <c r="K16" s="218"/>
+      <c r="L16" s="218"/>
+      <c r="M16" s="218"/>
+      <c r="N16" s="218"/>
+      <c r="O16" s="218"/>
+      <c r="P16" s="218"/>
+      <c r="Q16" s="218"/>
+      <c r="R16" s="218"/>
+      <c r="S16" s="218"/>
+      <c r="T16" s="218"/>
+      <c r="U16" s="218"/>
     </row>
     <row r="17" spans="2:21" ht="40" customHeight="1">
       <c r="B17" s="18"/>
@@ -34576,45 +34583,45 @@
       <c r="C21" s="18"/>
     </row>
     <row r="22" spans="2:21" ht="4" customHeight="1">
-      <c r="B22" s="274" t="s">
+      <c r="B22" s="223" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="274"/>
-      <c r="I22" s="274"/>
-      <c r="J22" s="274"/>
-      <c r="K22" s="274"/>
-      <c r="L22" s="274"/>
-      <c r="M22" s="274"/>
-      <c r="N22" s="274"/>
-      <c r="O22" s="274"/>
-      <c r="P22" s="274"/>
-      <c r="Q22" s="274"/>
-      <c r="R22" s="274"/>
-      <c r="S22" s="274"/>
-      <c r="T22" s="274"/>
-      <c r="U22" s="274"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="223"/>
+      <c r="I22" s="223"/>
+      <c r="J22" s="223"/>
+      <c r="K22" s="223"/>
+      <c r="L22" s="223"/>
+      <c r="M22" s="223"/>
+      <c r="N22" s="223"/>
+      <c r="O22" s="223"/>
+      <c r="P22" s="223"/>
+      <c r="Q22" s="223"/>
+      <c r="R22" s="223"/>
+      <c r="S22" s="223"/>
+      <c r="T22" s="223"/>
+      <c r="U22" s="223"/>
     </row>
     <row r="23" spans="2:21" ht="53.25" customHeight="1">
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
-      <c r="I23" s="273" t="s">
+      <c r="I23" s="222" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="273"/>
-      <c r="K23" s="273"/>
-      <c r="L23" s="273"/>
-      <c r="M23" s="273"/>
-      <c r="N23" s="273"/>
-      <c r="O23" s="273"/>
-      <c r="P23" s="273"/>
-      <c r="Q23" s="273"/>
-      <c r="R23" s="273"/>
-      <c r="S23" s="273"/>
+      <c r="J23" s="222"/>
+      <c r="K23" s="222"/>
+      <c r="L23" s="222"/>
+      <c r="M23" s="222"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="222"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="222"/>
       <c r="T23" s="50"/>
       <c r="U23" s="50"/>
     </row>
@@ -34622,40 +34629,40 @@
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
-      <c r="I24" s="258" t="s">
+      <c r="I24" s="224" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="258"/>
-      <c r="K24" s="258"/>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
+      <c r="J24" s="224"/>
+      <c r="K24" s="224"/>
+      <c r="L24" s="224"/>
+      <c r="M24" s="224"/>
+      <c r="N24" s="224"/>
+      <c r="O24" s="224"/>
+      <c r="P24" s="224"/>
+      <c r="Q24" s="224"/>
+      <c r="R24" s="224"/>
+      <c r="S24" s="224"/>
+      <c r="T24" s="224"/>
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="2:21" ht="24" customHeight="1">
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
-      <c r="I25" s="258" t="s">
+      <c r="I25" s="224" t="s">
         <v>67</v>
       </c>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
-      <c r="M25" s="258"/>
-      <c r="N25" s="258"/>
-      <c r="O25" s="258"/>
-      <c r="P25" s="258"/>
-      <c r="Q25" s="258"/>
-      <c r="R25" s="258"/>
-      <c r="S25" s="258"/>
-      <c r="T25" s="258"/>
+      <c r="J25" s="224"/>
+      <c r="K25" s="224"/>
+      <c r="L25" s="224"/>
+      <c r="M25" s="224"/>
+      <c r="N25" s="224"/>
+      <c r="O25" s="224"/>
+      <c r="P25" s="224"/>
+      <c r="Q25" s="224"/>
+      <c r="R25" s="224"/>
+      <c r="S25" s="224"/>
+      <c r="T25" s="224"/>
       <c r="U25" s="19"/>
     </row>
     <row r="26" spans="2:21" ht="24" customHeight="1">
@@ -34693,452 +34700,452 @@
       <c r="U27" s="21"/>
     </row>
     <row r="28" spans="2:21" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B28" s="270" t="s">
+      <c r="B28" s="219" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="271"/>
-      <c r="D28" s="271"/>
-      <c r="E28" s="271"/>
-      <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="271"/>
-      <c r="J28" s="271"/>
-      <c r="K28" s="271"/>
-      <c r="L28" s="271"/>
-      <c r="M28" s="271"/>
-      <c r="N28" s="271"/>
-      <c r="O28" s="271"/>
-      <c r="P28" s="271"/>
-      <c r="Q28" s="271"/>
-      <c r="R28" s="271"/>
-      <c r="S28" s="271"/>
-      <c r="T28" s="271"/>
-      <c r="U28" s="272"/>
+      <c r="C28" s="220"/>
+      <c r="D28" s="220"/>
+      <c r="E28" s="220"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="220"/>
+      <c r="H28" s="220"/>
+      <c r="I28" s="220"/>
+      <c r="J28" s="220"/>
+      <c r="K28" s="220"/>
+      <c r="L28" s="220"/>
+      <c r="M28" s="220"/>
+      <c r="N28" s="220"/>
+      <c r="O28" s="220"/>
+      <c r="P28" s="220"/>
+      <c r="Q28" s="220"/>
+      <c r="R28" s="220"/>
+      <c r="S28" s="220"/>
+      <c r="T28" s="220"/>
+      <c r="U28" s="221"/>
     </row>
     <row r="29" spans="2:21" ht="25" customHeight="1">
-      <c r="B29" s="275" t="s">
+      <c r="B29" s="225" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="276"/>
-      <c r="D29" s="277" t="s">
+      <c r="C29" s="226"/>
+      <c r="D29" s="229" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="277"/>
-      <c r="F29" s="277"/>
-      <c r="G29" s="278" t="str">
+      <c r="E29" s="229"/>
+      <c r="F29" s="229"/>
+      <c r="G29" s="230" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="H29" s="278"/>
-      <c r="I29" s="278"/>
-      <c r="J29" s="278"/>
-      <c r="K29" s="278"/>
-      <c r="L29" s="278"/>
-      <c r="M29" s="278"/>
-      <c r="N29" s="278"/>
-      <c r="O29" s="278"/>
-      <c r="P29" s="278"/>
-      <c r="Q29" s="278"/>
-      <c r="R29" s="278"/>
-      <c r="S29" s="278"/>
-      <c r="T29" s="278"/>
-      <c r="U29" s="279"/>
+      <c r="H29" s="230"/>
+      <c r="I29" s="230"/>
+      <c r="J29" s="230"/>
+      <c r="K29" s="230"/>
+      <c r="L29" s="230"/>
+      <c r="M29" s="230"/>
+      <c r="N29" s="230"/>
+      <c r="O29" s="230"/>
+      <c r="P29" s="230"/>
+      <c r="Q29" s="230"/>
+      <c r="R29" s="230"/>
+      <c r="S29" s="230"/>
+      <c r="T29" s="230"/>
+      <c r="U29" s="231"/>
     </row>
     <row r="30" spans="2:21" ht="25" customHeight="1">
-      <c r="B30" s="236"/>
-      <c r="C30" s="237"/>
-      <c r="D30" s="242" t="s">
+      <c r="B30" s="227"/>
+      <c r="C30" s="228"/>
+      <c r="D30" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="242"/>
-      <c r="F30" s="242"/>
-      <c r="G30" s="280" t="s">
+      <c r="E30" s="208"/>
+      <c r="F30" s="208"/>
+      <c r="G30" s="232" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="280"/>
-      <c r="I30" s="280"/>
-      <c r="J30" s="280"/>
-      <c r="K30" s="280"/>
-      <c r="L30" s="280"/>
-      <c r="M30" s="280"/>
-      <c r="N30" s="280"/>
-      <c r="O30" s="280"/>
-      <c r="P30" s="280"/>
-      <c r="Q30" s="280"/>
-      <c r="R30" s="280"/>
-      <c r="S30" s="280"/>
-      <c r="T30" s="280"/>
-      <c r="U30" s="281"/>
+      <c r="H30" s="232"/>
+      <c r="I30" s="232"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="232"/>
+      <c r="O30" s="232"/>
+      <c r="P30" s="232"/>
+      <c r="Q30" s="232"/>
+      <c r="R30" s="232"/>
+      <c r="S30" s="232"/>
+      <c r="T30" s="232"/>
+      <c r="U30" s="233"/>
     </row>
     <row r="31" spans="2:21" ht="25" customHeight="1">
-      <c r="B31" s="236"/>
-      <c r="C31" s="237"/>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="280" t="s">
+      <c r="B31" s="227"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="208"/>
+      <c r="G31" s="232" t="s">
         <v>180</v>
       </c>
-      <c r="H31" s="280"/>
-      <c r="I31" s="280"/>
-      <c r="J31" s="280"/>
-      <c r="K31" s="280"/>
-      <c r="L31" s="280"/>
-      <c r="M31" s="280"/>
-      <c r="N31" s="280"/>
-      <c r="O31" s="280"/>
-      <c r="P31" s="280"/>
-      <c r="Q31" s="280"/>
-      <c r="R31" s="280"/>
-      <c r="S31" s="280"/>
-      <c r="T31" s="280"/>
-      <c r="U31" s="281"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="232"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="232"/>
+      <c r="O31" s="232"/>
+      <c r="P31" s="232"/>
+      <c r="Q31" s="232"/>
+      <c r="R31" s="232"/>
+      <c r="S31" s="232"/>
+      <c r="T31" s="232"/>
+      <c r="U31" s="233"/>
     </row>
     <row r="32" spans="2:21" ht="25" customHeight="1">
-      <c r="B32" s="236"/>
-      <c r="C32" s="237"/>
-      <c r="D32" s="242"/>
-      <c r="E32" s="242"/>
-      <c r="F32" s="242"/>
-      <c r="G32" s="280" t="s">
+      <c r="B32" s="227"/>
+      <c r="C32" s="228"/>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="208"/>
+      <c r="G32" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="H32" s="280"/>
-      <c r="I32" s="280"/>
-      <c r="J32" s="280"/>
-      <c r="K32" s="280"/>
-      <c r="L32" s="280"/>
-      <c r="M32" s="280"/>
-      <c r="N32" s="280"/>
-      <c r="O32" s="280"/>
-      <c r="P32" s="280"/>
-      <c r="Q32" s="280"/>
-      <c r="R32" s="280"/>
-      <c r="S32" s="280"/>
-      <c r="T32" s="280"/>
-      <c r="U32" s="281"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="232"/>
+      <c r="P32" s="232"/>
+      <c r="Q32" s="232"/>
+      <c r="R32" s="232"/>
+      <c r="S32" s="232"/>
+      <c r="T32" s="232"/>
+      <c r="U32" s="233"/>
     </row>
     <row r="33" spans="2:21" ht="25" customHeight="1">
-      <c r="B33" s="236"/>
-      <c r="C33" s="237"/>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="280" t="s">
+      <c r="B33" s="227"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="208"/>
+      <c r="E33" s="208"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="232" t="s">
         <v>182</v>
       </c>
-      <c r="H33" s="280"/>
-      <c r="I33" s="280"/>
-      <c r="J33" s="280"/>
-      <c r="K33" s="280"/>
-      <c r="L33" s="280"/>
-      <c r="M33" s="280"/>
-      <c r="N33" s="280"/>
-      <c r="O33" s="280"/>
-      <c r="P33" s="280"/>
-      <c r="Q33" s="280"/>
-      <c r="R33" s="280"/>
-      <c r="S33" s="280"/>
-      <c r="T33" s="280"/>
-      <c r="U33" s="281"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="232"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="232"/>
+      <c r="O33" s="232"/>
+      <c r="P33" s="232"/>
+      <c r="Q33" s="232"/>
+      <c r="R33" s="232"/>
+      <c r="S33" s="232"/>
+      <c r="T33" s="232"/>
+      <c r="U33" s="233"/>
     </row>
     <row r="34" spans="2:21" ht="25" customHeight="1">
-      <c r="B34" s="236"/>
-      <c r="C34" s="237"/>
-      <c r="D34" s="242"/>
-      <c r="E34" s="242"/>
-      <c r="F34" s="242"/>
-      <c r="G34" s="282" t="s">
+      <c r="B34" s="227"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="208"/>
+      <c r="E34" s="208"/>
+      <c r="F34" s="208"/>
+      <c r="G34" s="236" t="s">
         <v>183</v>
       </c>
-      <c r="H34" s="282"/>
-      <c r="I34" s="282"/>
-      <c r="J34" s="282"/>
-      <c r="K34" s="282"/>
-      <c r="L34" s="282"/>
-      <c r="M34" s="282"/>
-      <c r="N34" s="282"/>
-      <c r="O34" s="282"/>
-      <c r="P34" s="282"/>
-      <c r="Q34" s="282"/>
-      <c r="R34" s="282"/>
-      <c r="S34" s="282"/>
-      <c r="T34" s="282"/>
-      <c r="U34" s="283"/>
+      <c r="H34" s="236"/>
+      <c r="I34" s="236"/>
+      <c r="J34" s="236"/>
+      <c r="K34" s="236"/>
+      <c r="L34" s="236"/>
+      <c r="M34" s="236"/>
+      <c r="N34" s="236"/>
+      <c r="O34" s="236"/>
+      <c r="P34" s="236"/>
+      <c r="Q34" s="236"/>
+      <c r="R34" s="236"/>
+      <c r="S34" s="236"/>
+      <c r="T34" s="236"/>
+      <c r="U34" s="237"/>
     </row>
     <row r="35" spans="2:21" ht="25" customHeight="1">
-      <c r="B35" s="236" t="s">
+      <c r="B35" s="227" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="237"/>
-      <c r="D35" s="242" t="s">
+      <c r="C35" s="228"/>
+      <c r="D35" s="208" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="242"/>
-      <c r="F35" s="242"/>
-      <c r="G35" s="253" t="str">
+      <c r="E35" s="208"/>
+      <c r="F35" s="208"/>
+      <c r="G35" s="256" t="str">
         <f>G29</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="H35" s="233"/>
-      <c r="I35" s="233"/>
-      <c r="J35" s="233"/>
-      <c r="K35" s="233"/>
-      <c r="L35" s="233"/>
-      <c r="M35" s="254" t="s">
+      <c r="H35" s="257"/>
+      <c r="I35" s="257"/>
+      <c r="J35" s="257"/>
+      <c r="K35" s="257"/>
+      <c r="L35" s="257"/>
+      <c r="M35" s="257" t="s">
         <v>147</v>
       </c>
-      <c r="N35" s="254"/>
-      <c r="O35" s="254"/>
-      <c r="P35" s="254"/>
-      <c r="Q35" s="254"/>
-      <c r="R35" s="254"/>
-      <c r="S35" s="254"/>
-      <c r="T35" s="129"/>
-      <c r="U35" s="130"/>
+      <c r="N35" s="257"/>
+      <c r="O35" s="257"/>
+      <c r="P35" s="257"/>
+      <c r="Q35" s="257"/>
+      <c r="R35" s="257"/>
+      <c r="S35" s="257"/>
+      <c r="T35" s="128"/>
+      <c r="U35" s="129"/>
     </row>
     <row r="36" spans="2:21" ht="25" customHeight="1">
-      <c r="B36" s="236"/>
-      <c r="C36" s="237"/>
-      <c r="D36" s="242" t="s">
+      <c r="B36" s="227"/>
+      <c r="C36" s="228"/>
+      <c r="D36" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="242"/>
-      <c r="F36" s="242"/>
-      <c r="G36" s="243" t="str">
+      <c r="E36" s="208"/>
+      <c r="F36" s="208"/>
+      <c r="G36" s="206" t="str">
         <f>갑지!L31</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="H36" s="243"/>
-      <c r="I36" s="243"/>
-      <c r="J36" s="243"/>
-      <c r="K36" s="243"/>
-      <c r="L36" s="243"/>
-      <c r="M36" s="243"/>
-      <c r="N36" s="243"/>
-      <c r="O36" s="243"/>
-      <c r="P36" s="243"/>
-      <c r="Q36" s="243"/>
-      <c r="R36" s="243"/>
-      <c r="S36" s="243"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="244"/>
+      <c r="H36" s="206"/>
+      <c r="I36" s="206"/>
+      <c r="J36" s="206"/>
+      <c r="K36" s="206"/>
+      <c r="L36" s="206"/>
+      <c r="M36" s="206"/>
+      <c r="N36" s="206"/>
+      <c r="O36" s="206"/>
+      <c r="P36" s="206"/>
+      <c r="Q36" s="206"/>
+      <c r="R36" s="206"/>
+      <c r="S36" s="206"/>
+      <c r="T36" s="206"/>
+      <c r="U36" s="207"/>
     </row>
     <row r="37" spans="2:21" ht="25" customHeight="1">
-      <c r="B37" s="236"/>
-      <c r="C37" s="237"/>
-      <c r="D37" s="242" t="s">
+      <c r="B37" s="227"/>
+      <c r="C37" s="228"/>
+      <c r="D37" s="208" t="s">
         <v>0</v>
       </c>
-      <c r="E37" s="242"/>
-      <c r="F37" s="242"/>
-      <c r="G37" s="245" t="str">
+      <c r="E37" s="208"/>
+      <c r="F37" s="208"/>
+      <c r="G37" s="246" t="str">
         <f>갑지!L31</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="H37" s="245"/>
-      <c r="I37" s="245"/>
-      <c r="J37" s="245"/>
-      <c r="K37" s="245"/>
-      <c r="L37" s="245"/>
-      <c r="M37" s="245"/>
-      <c r="N37" s="245"/>
-      <c r="O37" s="245"/>
-      <c r="P37" s="245"/>
-      <c r="Q37" s="245"/>
-      <c r="R37" s="245"/>
-      <c r="S37" s="245"/>
-      <c r="T37" s="245"/>
-      <c r="U37" s="246"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
+      <c r="M37" s="246"/>
+      <c r="N37" s="246"/>
+      <c r="O37" s="246"/>
+      <c r="P37" s="246"/>
+      <c r="Q37" s="246"/>
+      <c r="R37" s="246"/>
+      <c r="S37" s="246"/>
+      <c r="T37" s="246"/>
+      <c r="U37" s="247"/>
     </row>
     <row r="38" spans="2:21" ht="25" customHeight="1">
-      <c r="B38" s="236"/>
-      <c r="C38" s="237"/>
-      <c r="D38" s="242" t="s">
+      <c r="B38" s="227"/>
+      <c r="C38" s="228"/>
+      <c r="D38" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="242"/>
-      <c r="F38" s="242"/>
-      <c r="G38" s="243" t="s">
+      <c r="E38" s="208"/>
+      <c r="F38" s="208"/>
+      <c r="G38" s="206" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-      <c r="P38" s="243"/>
-      <c r="Q38" s="243"/>
-      <c r="R38" s="243"/>
-      <c r="S38" s="243"/>
-      <c r="T38" s="243"/>
-      <c r="U38" s="244"/>
+      <c r="H38" s="206"/>
+      <c r="I38" s="206"/>
+      <c r="J38" s="206"/>
+      <c r="K38" s="206"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="206"/>
+      <c r="O38" s="206"/>
+      <c r="P38" s="206"/>
+      <c r="Q38" s="206"/>
+      <c r="R38" s="206"/>
+      <c r="S38" s="206"/>
+      <c r="T38" s="206"/>
+      <c r="U38" s="207"/>
     </row>
     <row r="39" spans="2:21" ht="25" customHeight="1">
-      <c r="B39" s="236"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="242" t="s">
+      <c r="B39" s="227"/>
+      <c r="C39" s="228"/>
+      <c r="D39" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="242"/>
-      <c r="F39" s="242"/>
-      <c r="G39" s="243" t="s">
+      <c r="E39" s="208"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="206" t="s">
         <v>52</v>
       </c>
-      <c r="H39" s="243"/>
-      <c r="I39" s="243"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="243"/>
-      <c r="L39" s="243"/>
-      <c r="M39" s="243"/>
-      <c r="N39" s="243"/>
-      <c r="O39" s="243"/>
-      <c r="P39" s="243"/>
-      <c r="Q39" s="243"/>
-      <c r="R39" s="243"/>
-      <c r="S39" s="243"/>
-      <c r="T39" s="243"/>
-      <c r="U39" s="244"/>
+      <c r="H39" s="206"/>
+      <c r="I39" s="206"/>
+      <c r="J39" s="206"/>
+      <c r="K39" s="206"/>
+      <c r="L39" s="206"/>
+      <c r="M39" s="206"/>
+      <c r="N39" s="206"/>
+      <c r="O39" s="206"/>
+      <c r="P39" s="206"/>
+      <c r="Q39" s="206"/>
+      <c r="R39" s="206"/>
+      <c r="S39" s="206"/>
+      <c r="T39" s="206"/>
+      <c r="U39" s="207"/>
     </row>
     <row r="40" spans="2:21" ht="25" customHeight="1">
-      <c r="B40" s="236"/>
-      <c r="C40" s="237"/>
-      <c r="D40" s="242" t="s">
+      <c r="B40" s="227"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="208" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="243" t="str">
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="206" t="str">
         <f>갑지!L23</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="H40" s="243"/>
-      <c r="I40" s="243"/>
-      <c r="J40" s="243"/>
-      <c r="K40" s="243"/>
-      <c r="L40" s="243"/>
-      <c r="M40" s="243"/>
-      <c r="N40" s="243"/>
-      <c r="O40" s="243"/>
-      <c r="P40" s="243"/>
-      <c r="Q40" s="243"/>
-      <c r="R40" s="243"/>
-      <c r="S40" s="243"/>
-      <c r="T40" s="243"/>
-      <c r="U40" s="244"/>
+      <c r="H40" s="206"/>
+      <c r="I40" s="206"/>
+      <c r="J40" s="206"/>
+      <c r="K40" s="206"/>
+      <c r="L40" s="206"/>
+      <c r="M40" s="206"/>
+      <c r="N40" s="206"/>
+      <c r="O40" s="206"/>
+      <c r="P40" s="206"/>
+      <c r="Q40" s="206"/>
+      <c r="R40" s="206"/>
+      <c r="S40" s="206"/>
+      <c r="T40" s="206"/>
+      <c r="U40" s="207"/>
     </row>
     <row r="41" spans="2:21" ht="25" customHeight="1">
-      <c r="B41" s="236"/>
-      <c r="C41" s="237"/>
-      <c r="D41" s="242"/>
-      <c r="E41" s="242"/>
-      <c r="F41" s="242"/>
-      <c r="G41" s="253" t="s">
+      <c r="B41" s="227"/>
+      <c r="C41" s="228"/>
+      <c r="D41" s="208"/>
+      <c r="E41" s="208"/>
+      <c r="F41" s="208"/>
+      <c r="G41" s="260" t="s">
         <v>170</v>
       </c>
-      <c r="H41" s="233"/>
-      <c r="I41" s="233"/>
-      <c r="J41" s="233"/>
-      <c r="K41" s="233"/>
-      <c r="L41" s="233"/>
-      <c r="M41" s="233"/>
-      <c r="N41" s="128" t="s">
+      <c r="H41" s="234"/>
+      <c r="I41" s="234"/>
+      <c r="J41" s="234"/>
+      <c r="K41" s="234"/>
+      <c r="L41" s="234"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="136" t="s">
         <v>171</v>
       </c>
-      <c r="O41" s="233" t="s">
+      <c r="O41" s="234" t="s">
         <v>172</v>
       </c>
-      <c r="P41" s="233"/>
-      <c r="Q41" s="233"/>
-      <c r="R41" s="233"/>
-      <c r="S41" s="233"/>
-      <c r="T41" s="233"/>
-      <c r="U41" s="234"/>
+      <c r="P41" s="234"/>
+      <c r="Q41" s="234"/>
+      <c r="R41" s="234"/>
+      <c r="S41" s="234"/>
+      <c r="T41" s="234"/>
+      <c r="U41" s="235"/>
     </row>
     <row r="42" spans="2:21" ht="25" customHeight="1">
-      <c r="B42" s="238"/>
-      <c r="C42" s="239"/>
-      <c r="D42" s="247" t="s">
+      <c r="B42" s="242"/>
+      <c r="C42" s="243"/>
+      <c r="D42" s="248" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="248"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="250"/>
-      <c r="H42" s="251"/>
-      <c r="I42" s="251"/>
-      <c r="J42" s="251"/>
-      <c r="K42" s="251"/>
-      <c r="L42" s="251"/>
-      <c r="M42" s="251"/>
-      <c r="N42" s="251"/>
-      <c r="O42" s="251"/>
-      <c r="P42" s="251"/>
-      <c r="Q42" s="251"/>
-      <c r="R42" s="251"/>
-      <c r="S42" s="251"/>
-      <c r="T42" s="251"/>
-      <c r="U42" s="252"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="250"/>
+      <c r="G42" s="251"/>
+      <c r="H42" s="252"/>
+      <c r="I42" s="252"/>
+      <c r="J42" s="252"/>
+      <c r="K42" s="252"/>
+      <c r="L42" s="252"/>
+      <c r="M42" s="252"/>
+      <c r="N42" s="252"/>
+      <c r="O42" s="252"/>
+      <c r="P42" s="252"/>
+      <c r="Q42" s="252"/>
+      <c r="R42" s="252"/>
+      <c r="S42" s="252"/>
+      <c r="T42" s="252"/>
+      <c r="U42" s="253"/>
     </row>
     <row r="43" spans="2:21" ht="25" customHeight="1" thickBot="1">
-      <c r="B43" s="240"/>
-      <c r="C43" s="241"/>
-      <c r="D43" s="284" t="s">
+      <c r="B43" s="244"/>
+      <c r="C43" s="245"/>
+      <c r="D43" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="284"/>
-      <c r="F43" s="284"/>
-      <c r="G43" s="223" t="s">
+      <c r="E43" s="238"/>
+      <c r="F43" s="238"/>
+      <c r="G43" s="254" t="s">
         <v>146</v>
       </c>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="223"/>
-      <c r="M43" s="223"/>
-      <c r="N43" s="223"/>
-      <c r="O43" s="223"/>
-      <c r="P43" s="223"/>
-      <c r="Q43" s="223"/>
-      <c r="R43" s="223"/>
-      <c r="S43" s="223"/>
-      <c r="T43" s="223"/>
-      <c r="U43" s="224"/>
+      <c r="H43" s="254"/>
+      <c r="I43" s="254"/>
+      <c r="J43" s="254"/>
+      <c r="K43" s="254"/>
+      <c r="L43" s="254"/>
+      <c r="M43" s="254"/>
+      <c r="N43" s="254"/>
+      <c r="O43" s="254"/>
+      <c r="P43" s="254"/>
+      <c r="Q43" s="254"/>
+      <c r="R43" s="254"/>
+      <c r="S43" s="254"/>
+      <c r="T43" s="254"/>
+      <c r="U43" s="255"/>
     </row>
     <row r="44" spans="2:21">
-      <c r="B44" s="255"/>
-      <c r="C44" s="256"/>
-      <c r="D44" s="256"/>
-      <c r="E44" s="256"/>
+      <c r="B44" s="258"/>
+      <c r="C44" s="259"/>
+      <c r="D44" s="259"/>
+      <c r="E44" s="259"/>
       <c r="U44" s="2"/>
     </row>
     <row r="45" spans="2:21" ht="67.5" customHeight="1">
-      <c r="B45" s="262" t="s">
+      <c r="B45" s="211" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="217"/>
-      <c r="D45" s="217"/>
-      <c r="E45" s="217"/>
-      <c r="F45" s="217"/>
-      <c r="G45" s="217"/>
-      <c r="H45" s="217"/>
-      <c r="I45" s="217"/>
-      <c r="J45" s="217"/>
-      <c r="K45" s="217"/>
-      <c r="L45" s="217"/>
-      <c r="M45" s="217"/>
-      <c r="N45" s="217"/>
-      <c r="O45" s="217"/>
-      <c r="P45" s="217"/>
-      <c r="Q45" s="217"/>
-      <c r="R45" s="217"/>
-      <c r="S45" s="217"/>
-      <c r="T45" s="217"/>
-      <c r="U45" s="259"/>
+      <c r="C45" s="209"/>
+      <c r="D45" s="209"/>
+      <c r="E45" s="209"/>
+      <c r="F45" s="209"/>
+      <c r="G45" s="209"/>
+      <c r="H45" s="209"/>
+      <c r="I45" s="209"/>
+      <c r="J45" s="209"/>
+      <c r="K45" s="209"/>
+      <c r="L45" s="209"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="209"/>
+      <c r="O45" s="209"/>
+      <c r="P45" s="209"/>
+      <c r="Q45" s="209"/>
+      <c r="R45" s="209"/>
+      <c r="S45" s="209"/>
+      <c r="T45" s="209"/>
+      <c r="U45" s="210"/>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="22"/>
@@ -35148,273 +35155,273 @@
       <c r="U46" s="2"/>
     </row>
     <row r="47" spans="2:21" ht="25" customHeight="1">
-      <c r="B47" s="257" t="s">
+      <c r="B47" s="261" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="258"/>
-      <c r="D47" s="258"/>
-      <c r="E47" s="217" t="s">
+      <c r="C47" s="224"/>
+      <c r="D47" s="224"/>
+      <c r="E47" s="209" t="s">
         <v>178</v>
       </c>
-      <c r="F47" s="217"/>
-      <c r="G47" s="217"/>
-      <c r="H47" s="217"/>
-      <c r="I47" s="217"/>
-      <c r="J47" s="217"/>
-      <c r="K47" s="217"/>
-      <c r="L47" s="217"/>
-      <c r="M47" s="217"/>
-      <c r="N47" s="217"/>
-      <c r="O47" s="217"/>
-      <c r="P47" s="217"/>
-      <c r="Q47" s="217"/>
-      <c r="R47" s="217"/>
-      <c r="S47" s="217"/>
-      <c r="T47" s="217"/>
-      <c r="U47" s="259"/>
+      <c r="F47" s="209"/>
+      <c r="G47" s="209"/>
+      <c r="H47" s="209"/>
+      <c r="I47" s="209"/>
+      <c r="J47" s="209"/>
+      <c r="K47" s="209"/>
+      <c r="L47" s="209"/>
+      <c r="M47" s="209"/>
+      <c r="N47" s="209"/>
+      <c r="O47" s="209"/>
+      <c r="P47" s="209"/>
+      <c r="Q47" s="209"/>
+      <c r="R47" s="209"/>
+      <c r="S47" s="209"/>
+      <c r="T47" s="209"/>
+      <c r="U47" s="210"/>
     </row>
     <row r="48" spans="2:21" ht="25" customHeight="1">
       <c r="B48" s="24"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
-      <c r="E48" s="217"/>
-      <c r="F48" s="217"/>
-      <c r="G48" s="217"/>
-      <c r="H48" s="217"/>
-      <c r="I48" s="217"/>
-      <c r="J48" s="217"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="217"/>
-      <c r="M48" s="217"/>
-      <c r="N48" s="217"/>
-      <c r="O48" s="217"/>
-      <c r="P48" s="217"/>
-      <c r="Q48" s="217"/>
-      <c r="R48" s="217"/>
-      <c r="S48" s="217"/>
-      <c r="T48" s="217"/>
-      <c r="U48" s="259"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="209"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="209"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="209"/>
+      <c r="O48" s="209"/>
+      <c r="P48" s="209"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="209"/>
+      <c r="S48" s="209"/>
+      <c r="T48" s="209"/>
+      <c r="U48" s="210"/>
     </row>
     <row r="49" spans="2:21" ht="25" customHeight="1">
       <c r="B49" s="24"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
-      <c r="E49" s="217"/>
-      <c r="F49" s="217"/>
-      <c r="G49" s="217"/>
-      <c r="H49" s="217"/>
-      <c r="I49" s="217"/>
-      <c r="J49" s="217"/>
-      <c r="K49" s="217"/>
-      <c r="L49" s="217"/>
-      <c r="M49" s="217"/>
-      <c r="N49" s="217"/>
-      <c r="O49" s="217"/>
-      <c r="P49" s="217"/>
-      <c r="Q49" s="217"/>
-      <c r="R49" s="217"/>
-      <c r="S49" s="217"/>
-      <c r="T49" s="217"/>
-      <c r="U49" s="259"/>
+      <c r="E49" s="209"/>
+      <c r="F49" s="209"/>
+      <c r="G49" s="209"/>
+      <c r="H49" s="209"/>
+      <c r="I49" s="209"/>
+      <c r="J49" s="209"/>
+      <c r="K49" s="209"/>
+      <c r="L49" s="209"/>
+      <c r="M49" s="209"/>
+      <c r="N49" s="209"/>
+      <c r="O49" s="209"/>
+      <c r="P49" s="209"/>
+      <c r="Q49" s="209"/>
+      <c r="R49" s="209"/>
+      <c r="S49" s="209"/>
+      <c r="T49" s="209"/>
+      <c r="U49" s="210"/>
     </row>
     <row r="50" spans="2:21">
-      <c r="B50" s="255"/>
-      <c r="C50" s="256"/>
-      <c r="D50" s="256"/>
-      <c r="E50" s="256"/>
+      <c r="B50" s="258"/>
+      <c r="C50" s="259"/>
+      <c r="D50" s="259"/>
+      <c r="E50" s="259"/>
       <c r="U50" s="2"/>
     </row>
     <row r="51" spans="2:21" ht="25" customHeight="1">
-      <c r="B51" s="262" t="s">
+      <c r="B51" s="211" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="217"/>
-      <c r="D51" s="217"/>
-      <c r="E51" s="260" t="s">
+      <c r="C51" s="209"/>
+      <c r="D51" s="209"/>
+      <c r="E51" s="262" t="s">
         <v>48</v>
       </c>
-      <c r="F51" s="260"/>
-      <c r="G51" s="260"/>
-      <c r="H51" s="260"/>
-      <c r="I51" s="260"/>
-      <c r="J51" s="260"/>
-      <c r="K51" s="260"/>
-      <c r="L51" s="260"/>
-      <c r="M51" s="260"/>
-      <c r="N51" s="260"/>
-      <c r="O51" s="260"/>
-      <c r="P51" s="260"/>
-      <c r="Q51" s="260"/>
-      <c r="R51" s="260"/>
-      <c r="S51" s="260"/>
-      <c r="T51" s="260"/>
-      <c r="U51" s="261"/>
+      <c r="F51" s="262"/>
+      <c r="G51" s="262"/>
+      <c r="H51" s="262"/>
+      <c r="I51" s="262"/>
+      <c r="J51" s="262"/>
+      <c r="K51" s="262"/>
+      <c r="L51" s="262"/>
+      <c r="M51" s="262"/>
+      <c r="N51" s="262"/>
+      <c r="O51" s="262"/>
+      <c r="P51" s="262"/>
+      <c r="Q51" s="262"/>
+      <c r="R51" s="262"/>
+      <c r="S51" s="262"/>
+      <c r="T51" s="262"/>
+      <c r="U51" s="263"/>
     </row>
     <row r="52" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B52" s="225" t="s">
+      <c r="B52" s="239" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="226"/>
-      <c r="D52" s="226"/>
-      <c r="E52" s="226"/>
-      <c r="F52" s="226"/>
-      <c r="G52" s="226"/>
-      <c r="H52" s="226"/>
-      <c r="I52" s="226"/>
-      <c r="J52" s="226"/>
-      <c r="K52" s="226"/>
-      <c r="L52" s="226" t="s">
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
+      <c r="H52" s="240"/>
+      <c r="I52" s="240"/>
+      <c r="J52" s="240"/>
+      <c r="K52" s="240"/>
+      <c r="L52" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="M52" s="226"/>
-      <c r="N52" s="226"/>
-      <c r="O52" s="226"/>
-      <c r="P52" s="226"/>
-      <c r="Q52" s="226"/>
-      <c r="R52" s="226"/>
-      <c r="S52" s="226"/>
-      <c r="T52" s="226"/>
-      <c r="U52" s="235"/>
+      <c r="M52" s="240"/>
+      <c r="N52" s="240"/>
+      <c r="O52" s="240"/>
+      <c r="P52" s="240"/>
+      <c r="Q52" s="240"/>
+      <c r="R52" s="240"/>
+      <c r="S52" s="240"/>
+      <c r="T52" s="240"/>
+      <c r="U52" s="241"/>
     </row>
     <row r="53" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B53" s="225" t="s">
+      <c r="B53" s="239" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="226"/>
-      <c r="D53" s="226"/>
-      <c r="E53" s="227" t="str">
+      <c r="C53" s="240"/>
+      <c r="D53" s="240"/>
+      <c r="E53" s="268" t="str">
         <f>G29</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="F53" s="227"/>
-      <c r="G53" s="227"/>
-      <c r="H53" s="227"/>
-      <c r="I53" s="227"/>
-      <c r="J53" s="227"/>
-      <c r="K53" s="227"/>
-      <c r="L53" s="226" t="s">
+      <c r="F53" s="268"/>
+      <c r="G53" s="268"/>
+      <c r="H53" s="268"/>
+      <c r="I53" s="268"/>
+      <c r="J53" s="268"/>
+      <c r="K53" s="268"/>
+      <c r="L53" s="240" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="226"/>
-      <c r="N53" s="226"/>
-      <c r="O53" s="228" t="s">
+      <c r="M53" s="240"/>
+      <c r="N53" s="240"/>
+      <c r="O53" s="269" t="s">
         <v>32</v>
       </c>
-      <c r="P53" s="228"/>
-      <c r="Q53" s="228"/>
-      <c r="R53" s="228"/>
-      <c r="S53" s="228"/>
-      <c r="T53" s="228"/>
-      <c r="U53" s="229"/>
+      <c r="P53" s="269"/>
+      <c r="Q53" s="269"/>
+      <c r="R53" s="269"/>
+      <c r="S53" s="269"/>
+      <c r="T53" s="269"/>
+      <c r="U53" s="270"/>
     </row>
     <row r="54" spans="2:21" ht="40.5" customHeight="1">
-      <c r="B54" s="225" t="s">
+      <c r="B54" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="226"/>
-      <c r="D54" s="226"/>
-      <c r="E54" s="227" t="str">
+      <c r="C54" s="240"/>
+      <c r="D54" s="240"/>
+      <c r="E54" s="268" t="str">
         <f>G40</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="F54" s="227"/>
-      <c r="G54" s="227"/>
-      <c r="H54" s="227"/>
-      <c r="I54" s="227"/>
-      <c r="J54" s="227"/>
-      <c r="K54" s="227"/>
-      <c r="L54" s="226" t="s">
+      <c r="F54" s="268"/>
+      <c r="G54" s="268"/>
+      <c r="H54" s="268"/>
+      <c r="I54" s="268"/>
+      <c r="J54" s="268"/>
+      <c r="K54" s="268"/>
+      <c r="L54" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="M54" s="226"/>
-      <c r="N54" s="226"/>
-      <c r="O54" s="230" t="s">
+      <c r="M54" s="240"/>
+      <c r="N54" s="240"/>
+      <c r="O54" s="272" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="231"/>
-      <c r="Q54" s="231"/>
-      <c r="R54" s="231"/>
-      <c r="S54" s="231"/>
-      <c r="T54" s="231"/>
-      <c r="U54" s="232"/>
+      <c r="P54" s="273"/>
+      <c r="Q54" s="273"/>
+      <c r="R54" s="273"/>
+      <c r="S54" s="273"/>
+      <c r="T54" s="273"/>
+      <c r="U54" s="274"/>
     </row>
     <row r="55" spans="2:21" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B55" s="220" t="s">
+      <c r="B55" s="265" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="221"/>
-      <c r="D55" s="221"/>
-      <c r="E55" s="222" t="s">
+      <c r="C55" s="266"/>
+      <c r="D55" s="266"/>
+      <c r="E55" s="267" t="s">
         <v>37</v>
       </c>
-      <c r="F55" s="222"/>
-      <c r="G55" s="222"/>
-      <c r="H55" s="222"/>
-      <c r="I55" s="222"/>
-      <c r="J55" s="222"/>
-      <c r="K55" s="222"/>
-      <c r="L55" s="221" t="s">
+      <c r="F55" s="267"/>
+      <c r="G55" s="267"/>
+      <c r="H55" s="267"/>
+      <c r="I55" s="267"/>
+      <c r="J55" s="267"/>
+      <c r="K55" s="267"/>
+      <c r="L55" s="266" t="s">
         <v>38</v>
       </c>
-      <c r="M55" s="221"/>
-      <c r="N55" s="221"/>
-      <c r="O55" s="223" t="s">
+      <c r="M55" s="266"/>
+      <c r="N55" s="266"/>
+      <c r="O55" s="254" t="s">
         <v>39</v>
       </c>
-      <c r="P55" s="223"/>
-      <c r="Q55" s="223"/>
-      <c r="R55" s="223"/>
-      <c r="S55" s="223"/>
-      <c r="T55" s="223"/>
-      <c r="U55" s="224"/>
+      <c r="P55" s="254"/>
+      <c r="Q55" s="254"/>
+      <c r="R55" s="254"/>
+      <c r="S55" s="254"/>
+      <c r="T55" s="254"/>
+      <c r="U55" s="255"/>
     </row>
     <row r="56" spans="2:21" ht="16">
-      <c r="B56" s="211" t="s">
+      <c r="B56" s="275" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="211"/>
-      <c r="D56" s="211"/>
-      <c r="E56" s="211"/>
-      <c r="F56" s="211"/>
-      <c r="G56" s="211"/>
-      <c r="H56" s="211"/>
-      <c r="I56" s="211"/>
-      <c r="J56" s="211"/>
-      <c r="K56" s="211"/>
-      <c r="L56" s="211"/>
-      <c r="M56" s="211"/>
-      <c r="N56" s="211"/>
-      <c r="O56" s="211"/>
-      <c r="P56" s="211"/>
-      <c r="Q56" s="211"/>
-      <c r="R56" s="211"/>
-      <c r="S56" s="211"/>
-      <c r="T56" s="211"/>
-      <c r="U56" s="211"/>
+      <c r="C56" s="275"/>
+      <c r="D56" s="275"/>
+      <c r="E56" s="275"/>
+      <c r="F56" s="275"/>
+      <c r="G56" s="275"/>
+      <c r="H56" s="275"/>
+      <c r="I56" s="275"/>
+      <c r="J56" s="275"/>
+      <c r="K56" s="275"/>
+      <c r="L56" s="275"/>
+      <c r="M56" s="275"/>
+      <c r="N56" s="275"/>
+      <c r="O56" s="275"/>
+      <c r="P56" s="275"/>
+      <c r="Q56" s="275"/>
+      <c r="R56" s="275"/>
+      <c r="S56" s="275"/>
+      <c r="T56" s="275"/>
+      <c r="U56" s="275"/>
     </row>
     <row r="57" spans="2:21" ht="26">
-      <c r="B57" s="212" t="s">
+      <c r="B57" s="276" t="s">
         <v>148</v>
       </c>
-      <c r="C57" s="212"/>
-      <c r="D57" s="212"/>
-      <c r="E57" s="212"/>
-      <c r="F57" s="212"/>
-      <c r="G57" s="212"/>
-      <c r="H57" s="212"/>
-      <c r="I57" s="212"/>
-      <c r="J57" s="212"/>
-      <c r="K57" s="212"/>
-      <c r="L57" s="212"/>
-      <c r="M57" s="212"/>
-      <c r="N57" s="212"/>
-      <c r="O57" s="212"/>
-      <c r="P57" s="212"/>
-      <c r="Q57" s="212"/>
-      <c r="R57" s="212"/>
-      <c r="S57" s="212"/>
-      <c r="T57" s="212"/>
-      <c r="U57" s="212"/>
+      <c r="C57" s="276"/>
+      <c r="D57" s="276"/>
+      <c r="E57" s="276"/>
+      <c r="F57" s="276"/>
+      <c r="G57" s="276"/>
+      <c r="H57" s="276"/>
+      <c r="I57" s="276"/>
+      <c r="J57" s="276"/>
+      <c r="K57" s="276"/>
+      <c r="L57" s="276"/>
+      <c r="M57" s="276"/>
+      <c r="N57" s="276"/>
+      <c r="O57" s="276"/>
+      <c r="P57" s="276"/>
+      <c r="Q57" s="276"/>
+      <c r="R57" s="276"/>
+      <c r="S57" s="276"/>
+      <c r="T57" s="276"/>
+      <c r="U57" s="276"/>
     </row>
     <row r="58" spans="2:21" ht="15">
       <c r="B58" s="25"/>
@@ -35423,81 +35430,81 @@
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="2:21" ht="25" customHeight="1">
-      <c r="B59" s="213" t="s">
+      <c r="B59" s="277" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="213"/>
-      <c r="D59" s="213"/>
-      <c r="E59" s="213"/>
-      <c r="F59" s="213"/>
-      <c r="G59" s="213"/>
-      <c r="H59" s="213"/>
-      <c r="I59" s="213"/>
-      <c r="J59" s="213"/>
-      <c r="K59" s="213"/>
-      <c r="L59" s="213"/>
-      <c r="M59" s="213"/>
-      <c r="N59" s="213"/>
-      <c r="O59" s="213"/>
-      <c r="P59" s="213"/>
-      <c r="Q59" s="213"/>
-      <c r="R59" s="213"/>
-      <c r="S59" s="213"/>
-      <c r="T59" s="213"/>
-      <c r="U59" s="213"/>
+      <c r="C59" s="277"/>
+      <c r="D59" s="277"/>
+      <c r="E59" s="277"/>
+      <c r="F59" s="277"/>
+      <c r="G59" s="277"/>
+      <c r="H59" s="277"/>
+      <c r="I59" s="277"/>
+      <c r="J59" s="277"/>
+      <c r="K59" s="277"/>
+      <c r="L59" s="277"/>
+      <c r="M59" s="277"/>
+      <c r="N59" s="277"/>
+      <c r="O59" s="277"/>
+      <c r="P59" s="277"/>
+      <c r="Q59" s="277"/>
+      <c r="R59" s="277"/>
+      <c r="S59" s="277"/>
+      <c r="T59" s="277"/>
+      <c r="U59" s="277"/>
     </row>
     <row r="60" spans="2:21" ht="28.5" customHeight="1">
-      <c r="B60" s="214" t="s">
+      <c r="B60" s="279" t="s">
         <v>160</v>
       </c>
-      <c r="C60" s="214"/>
-      <c r="D60" s="214"/>
-      <c r="E60" s="214"/>
-      <c r="F60" s="214"/>
-      <c r="G60" s="214"/>
-      <c r="H60" s="214"/>
-      <c r="I60" s="215" t="str">
+      <c r="C60" s="279"/>
+      <c r="D60" s="279"/>
+      <c r="E60" s="279"/>
+      <c r="F60" s="279"/>
+      <c r="G60" s="279"/>
+      <c r="H60" s="279"/>
+      <c r="I60" s="280" t="str">
         <f>E53</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="J60" s="215"/>
-      <c r="K60" s="215"/>
-      <c r="L60" s="215"/>
-      <c r="M60" s="215"/>
-      <c r="N60" s="215"/>
-      <c r="O60" s="214" t="s">
+      <c r="J60" s="280"/>
+      <c r="K60" s="280"/>
+      <c r="L60" s="280"/>
+      <c r="M60" s="280"/>
+      <c r="N60" s="280"/>
+      <c r="O60" s="279" t="s">
         <v>47</v>
       </c>
-      <c r="P60" s="214"/>
-      <c r="Q60" s="214"/>
-      <c r="R60" s="214"/>
-      <c r="S60" s="214"/>
-      <c r="T60" s="214"/>
-      <c r="U60" s="214"/>
+      <c r="P60" s="279"/>
+      <c r="Q60" s="279"/>
+      <c r="R60" s="279"/>
+      <c r="S60" s="279"/>
+      <c r="T60" s="279"/>
+      <c r="U60" s="279"/>
     </row>
     <row r="61" spans="2:21" ht="25" customHeight="1">
-      <c r="B61" s="213" t="s">
+      <c r="B61" s="277" t="s">
         <v>162</v>
       </c>
-      <c r="C61" s="213"/>
-      <c r="D61" s="213"/>
-      <c r="E61" s="213"/>
-      <c r="F61" s="213"/>
-      <c r="G61" s="213"/>
-      <c r="H61" s="213"/>
-      <c r="I61" s="213"/>
-      <c r="J61" s="213"/>
-      <c r="K61" s="213"/>
-      <c r="L61" s="213"/>
-      <c r="M61" s="213"/>
-      <c r="N61" s="213"/>
-      <c r="O61" s="213"/>
-      <c r="P61" s="213"/>
-      <c r="Q61" s="213"/>
-      <c r="R61" s="213"/>
-      <c r="S61" s="213"/>
-      <c r="T61" s="213"/>
-      <c r="U61" s="213"/>
+      <c r="C61" s="277"/>
+      <c r="D61" s="277"/>
+      <c r="E61" s="277"/>
+      <c r="F61" s="277"/>
+      <c r="G61" s="277"/>
+      <c r="H61" s="277"/>
+      <c r="I61" s="277"/>
+      <c r="J61" s="277"/>
+      <c r="K61" s="277"/>
+      <c r="L61" s="277"/>
+      <c r="M61" s="277"/>
+      <c r="N61" s="277"/>
+      <c r="O61" s="277"/>
+      <c r="P61" s="277"/>
+      <c r="Q61" s="277"/>
+      <c r="R61" s="277"/>
+      <c r="S61" s="277"/>
+      <c r="T61" s="277"/>
+      <c r="U61" s="277"/>
     </row>
     <row r="62" spans="2:21" ht="20" customHeight="1">
       <c r="B62" s="20"/>
@@ -35511,40 +35518,40 @@
       <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:21" ht="20" customHeight="1">
-      <c r="B63" s="208" t="s">
+      <c r="B63" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="C63" s="218"/>
-      <c r="D63" s="218"/>
-      <c r="E63" s="218"/>
-      <c r="F63" s="218"/>
-      <c r="G63" s="218"/>
-      <c r="H63" s="218"/>
-      <c r="I63" s="218"/>
-      <c r="J63" s="218"/>
+      <c r="C63" s="283"/>
+      <c r="D63" s="283"/>
+      <c r="E63" s="283"/>
+      <c r="F63" s="283"/>
+      <c r="G63" s="283"/>
+      <c r="H63" s="283"/>
+      <c r="I63" s="283"/>
+      <c r="J63" s="283"/>
     </row>
     <row r="64" spans="2:21" ht="94.5" customHeight="1">
-      <c r="C64" s="217" t="s">
+      <c r="C64" s="209" t="s">
         <v>149</v>
       </c>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
-      <c r="F64" s="217"/>
-      <c r="G64" s="217"/>
-      <c r="H64" s="217"/>
-      <c r="I64" s="217"/>
-      <c r="J64" s="217"/>
-      <c r="K64" s="217"/>
-      <c r="L64" s="217"/>
-      <c r="M64" s="217"/>
-      <c r="N64" s="217"/>
-      <c r="O64" s="217"/>
-      <c r="P64" s="217"/>
-      <c r="Q64" s="217"/>
-      <c r="R64" s="217"/>
-      <c r="S64" s="217"/>
-      <c r="T64" s="217"/>
-      <c r="U64" s="217"/>
+      <c r="D64" s="209"/>
+      <c r="E64" s="209"/>
+      <c r="F64" s="209"/>
+      <c r="G64" s="209"/>
+      <c r="H64" s="209"/>
+      <c r="I64" s="209"/>
+      <c r="J64" s="209"/>
+      <c r="K64" s="209"/>
+      <c r="L64" s="209"/>
+      <c r="M64" s="209"/>
+      <c r="N64" s="209"/>
+      <c r="O64" s="209"/>
+      <c r="P64" s="209"/>
+      <c r="Q64" s="209"/>
+      <c r="R64" s="209"/>
+      <c r="S64" s="209"/>
+      <c r="T64" s="209"/>
+      <c r="U64" s="209"/>
     </row>
     <row r="65" spans="2:21" ht="20" customHeight="1">
       <c r="B65" s="26"/>
@@ -35553,28 +35560,28 @@
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="2:21" ht="20" customHeight="1">
-      <c r="B66" s="208" t="s">
+      <c r="B66" s="282" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="208"/>
-      <c r="D66" s="208"/>
-      <c r="E66" s="208"/>
-      <c r="F66" s="208"/>
-      <c r="G66" s="208"/>
-      <c r="H66" s="208"/>
-      <c r="I66" s="208"/>
-      <c r="J66" s="208"/>
-      <c r="K66" s="208"/>
-      <c r="L66" s="208"/>
-      <c r="M66" s="208"/>
-      <c r="N66" s="208"/>
-      <c r="O66" s="208"/>
-      <c r="P66" s="208"/>
-      <c r="Q66" s="208"/>
-      <c r="R66" s="208"/>
-      <c r="S66" s="208"/>
-      <c r="T66" s="208"/>
-      <c r="U66" s="208"/>
+      <c r="C66" s="282"/>
+      <c r="D66" s="282"/>
+      <c r="E66" s="282"/>
+      <c r="F66" s="282"/>
+      <c r="G66" s="282"/>
+      <c r="H66" s="282"/>
+      <c r="I66" s="282"/>
+      <c r="J66" s="282"/>
+      <c r="K66" s="282"/>
+      <c r="L66" s="282"/>
+      <c r="M66" s="282"/>
+      <c r="N66" s="282"/>
+      <c r="O66" s="282"/>
+      <c r="P66" s="282"/>
+      <c r="Q66" s="282"/>
+      <c r="R66" s="282"/>
+      <c r="S66" s="282"/>
+      <c r="T66" s="282"/>
+      <c r="U66" s="282"/>
     </row>
     <row r="67" spans="2:21" ht="20" customHeight="1">
       <c r="C67" s="27" t="s">
@@ -35582,25 +35589,25 @@
       </c>
       <c r="D67" s="27"/>
       <c r="E67" s="27"/>
-      <c r="F67" s="219" t="str">
+      <c r="F67" s="284" t="str">
         <f>E53</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="G67" s="219"/>
-      <c r="H67" s="219"/>
-      <c r="I67" s="219"/>
-      <c r="J67" s="219"/>
-      <c r="K67" s="219"/>
-      <c r="L67" s="219"/>
-      <c r="M67" s="219"/>
-      <c r="N67" s="219"/>
-      <c r="O67" s="219"/>
-      <c r="P67" s="219"/>
-      <c r="Q67" s="219"/>
-      <c r="R67" s="219"/>
-      <c r="S67" s="219"/>
-      <c r="T67" s="219"/>
-      <c r="U67" s="219"/>
+      <c r="G67" s="284"/>
+      <c r="H67" s="284"/>
+      <c r="I67" s="284"/>
+      <c r="J67" s="284"/>
+      <c r="K67" s="284"/>
+      <c r="L67" s="284"/>
+      <c r="M67" s="284"/>
+      <c r="N67" s="284"/>
+      <c r="O67" s="284"/>
+      <c r="P67" s="284"/>
+      <c r="Q67" s="284"/>
+      <c r="R67" s="284"/>
+      <c r="S67" s="284"/>
+      <c r="T67" s="284"/>
+      <c r="U67" s="284"/>
     </row>
     <row r="68" spans="2:21" ht="20" customHeight="1">
       <c r="C68" s="27" t="s">
@@ -35608,25 +35615,25 @@
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="27"/>
-      <c r="F68" s="131" t="str">
+      <c r="F68" s="130" t="str">
         <f>E54</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="G68" s="131"/>
-      <c r="H68" s="131"/>
-      <c r="I68" s="131"/>
-      <c r="J68" s="131"/>
-      <c r="K68" s="132"/>
-      <c r="L68" s="133"/>
-      <c r="M68" s="133"/>
-      <c r="N68" s="133"/>
-      <c r="O68" s="133"/>
-      <c r="P68" s="133"/>
-      <c r="Q68" s="133"/>
-      <c r="R68" s="133"/>
-      <c r="S68" s="133"/>
-      <c r="T68" s="133"/>
-      <c r="U68" s="133"/>
+      <c r="G68" s="130"/>
+      <c r="H68" s="130"/>
+      <c r="I68" s="130"/>
+      <c r="J68" s="130"/>
+      <c r="K68" s="131"/>
+      <c r="L68" s="132"/>
+      <c r="M68" s="132"/>
+      <c r="N68" s="132"/>
+      <c r="O68" s="132"/>
+      <c r="P68" s="132"/>
+      <c r="Q68" s="132"/>
+      <c r="R68" s="132"/>
+      <c r="S68" s="132"/>
+      <c r="T68" s="132"/>
+      <c r="U68" s="132"/>
     </row>
     <row r="69" spans="2:21" ht="20" customHeight="1">
       <c r="C69" s="27" t="s">
@@ -35673,28 +35680,28 @@
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="2:21" ht="20" customHeight="1">
-      <c r="B72" s="208" t="s">
+      <c r="B72" s="282" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="208"/>
-      <c r="D72" s="208"/>
-      <c r="E72" s="208"/>
-      <c r="F72" s="208"/>
-      <c r="G72" s="208"/>
-      <c r="H72" s="208"/>
-      <c r="I72" s="208"/>
-      <c r="J72" s="208"/>
-      <c r="K72" s="208"/>
-      <c r="L72" s="208"/>
-      <c r="M72" s="208"/>
-      <c r="N72" s="208"/>
-      <c r="O72" s="208"/>
-      <c r="P72" s="208"/>
-      <c r="Q72" s="208"/>
-      <c r="R72" s="208"/>
-      <c r="S72" s="208"/>
-      <c r="T72" s="208"/>
-      <c r="U72" s="208"/>
+      <c r="C72" s="282"/>
+      <c r="D72" s="282"/>
+      <c r="E72" s="282"/>
+      <c r="F72" s="282"/>
+      <c r="G72" s="282"/>
+      <c r="H72" s="282"/>
+      <c r="I72" s="282"/>
+      <c r="J72" s="282"/>
+      <c r="K72" s="282"/>
+      <c r="L72" s="282"/>
+      <c r="M72" s="282"/>
+      <c r="N72" s="282"/>
+      <c r="O72" s="282"/>
+      <c r="P72" s="282"/>
+      <c r="Q72" s="282"/>
+      <c r="R72" s="282"/>
+      <c r="S72" s="282"/>
+      <c r="T72" s="282"/>
+      <c r="U72" s="282"/>
     </row>
     <row r="73" spans="2:21" ht="20" customHeight="1">
       <c r="C73" s="27" t="s">
@@ -35721,187 +35728,187 @@
     </row>
     <row r="74" spans="2:21" ht="20" customHeight="1">
       <c r="C74" s="27"/>
-      <c r="D74" s="210" t="s">
+      <c r="D74" s="271" t="s">
         <v>108</v>
       </c>
-      <c r="E74" s="210"/>
-      <c r="F74" s="210"/>
-      <c r="G74" s="210"/>
-      <c r="H74" s="210"/>
-      <c r="I74" s="210"/>
-      <c r="J74" s="210"/>
-      <c r="K74" s="210"/>
-      <c r="L74" s="210"/>
-      <c r="M74" s="210"/>
-      <c r="N74" s="210"/>
-      <c r="O74" s="210"/>
-      <c r="P74" s="210"/>
-      <c r="Q74" s="210"/>
-      <c r="R74" s="210"/>
-      <c r="S74" s="210"/>
-      <c r="T74" s="210"/>
-      <c r="U74" s="210"/>
+      <c r="E74" s="271"/>
+      <c r="F74" s="271"/>
+      <c r="G74" s="271"/>
+      <c r="H74" s="271"/>
+      <c r="I74" s="271"/>
+      <c r="J74" s="271"/>
+      <c r="K74" s="271"/>
+      <c r="L74" s="271"/>
+      <c r="M74" s="271"/>
+      <c r="N74" s="271"/>
+      <c r="O74" s="271"/>
+      <c r="P74" s="271"/>
+      <c r="Q74" s="271"/>
+      <c r="R74" s="271"/>
+      <c r="S74" s="271"/>
+      <c r="T74" s="271"/>
+      <c r="U74" s="271"/>
     </row>
     <row r="75" spans="2:21" ht="20" customHeight="1">
       <c r="C75" s="27"/>
-      <c r="D75" s="210" t="s">
+      <c r="D75" s="271" t="s">
         <v>109</v>
       </c>
-      <c r="E75" s="210"/>
-      <c r="F75" s="210"/>
-      <c r="G75" s="210"/>
-      <c r="H75" s="210"/>
-      <c r="I75" s="210"/>
-      <c r="J75" s="210"/>
-      <c r="K75" s="210"/>
-      <c r="L75" s="210"/>
-      <c r="M75" s="210"/>
-      <c r="N75" s="210"/>
-      <c r="O75" s="210"/>
-      <c r="P75" s="210"/>
-      <c r="Q75" s="210"/>
-      <c r="R75" s="210"/>
-      <c r="S75" s="210"/>
-      <c r="T75" s="210"/>
-      <c r="U75" s="210"/>
+      <c r="E75" s="271"/>
+      <c r="F75" s="271"/>
+      <c r="G75" s="271"/>
+      <c r="H75" s="271"/>
+      <c r="I75" s="271"/>
+      <c r="J75" s="271"/>
+      <c r="K75" s="271"/>
+      <c r="L75" s="271"/>
+      <c r="M75" s="271"/>
+      <c r="N75" s="271"/>
+      <c r="O75" s="271"/>
+      <c r="P75" s="271"/>
+      <c r="Q75" s="271"/>
+      <c r="R75" s="271"/>
+      <c r="S75" s="271"/>
+      <c r="T75" s="271"/>
+      <c r="U75" s="271"/>
     </row>
     <row r="76" spans="2:21" ht="20" customHeight="1">
       <c r="C76" s="27"/>
-      <c r="D76" s="210" t="s">
+      <c r="D76" s="271" t="s">
         <v>110</v>
       </c>
-      <c r="E76" s="210"/>
-      <c r="F76" s="210"/>
-      <c r="G76" s="210"/>
-      <c r="H76" s="210"/>
-      <c r="I76" s="210"/>
-      <c r="J76" s="210"/>
-      <c r="K76" s="210"/>
-      <c r="L76" s="210"/>
-      <c r="M76" s="210"/>
-      <c r="N76" s="210"/>
-      <c r="O76" s="210"/>
-      <c r="P76" s="210"/>
-      <c r="Q76" s="210"/>
-      <c r="R76" s="210"/>
-      <c r="S76" s="210"/>
-      <c r="T76" s="210"/>
-      <c r="U76" s="210"/>
+      <c r="E76" s="271"/>
+      <c r="F76" s="271"/>
+      <c r="G76" s="271"/>
+      <c r="H76" s="271"/>
+      <c r="I76" s="271"/>
+      <c r="J76" s="271"/>
+      <c r="K76" s="271"/>
+      <c r="L76" s="271"/>
+      <c r="M76" s="271"/>
+      <c r="N76" s="271"/>
+      <c r="O76" s="271"/>
+      <c r="P76" s="271"/>
+      <c r="Q76" s="271"/>
+      <c r="R76" s="271"/>
+      <c r="S76" s="271"/>
+      <c r="T76" s="271"/>
+      <c r="U76" s="271"/>
     </row>
     <row r="77" spans="2:21" ht="20" customHeight="1">
       <c r="C77" s="27"/>
-      <c r="D77" s="210" t="s">
+      <c r="D77" s="271" t="s">
         <v>111</v>
       </c>
-      <c r="E77" s="210"/>
-      <c r="F77" s="210"/>
-      <c r="G77" s="210"/>
-      <c r="H77" s="210"/>
-      <c r="I77" s="210"/>
-      <c r="J77" s="210"/>
-      <c r="K77" s="210"/>
-      <c r="L77" s="210"/>
-      <c r="M77" s="210"/>
-      <c r="N77" s="210"/>
-      <c r="O77" s="210"/>
-      <c r="P77" s="210"/>
-      <c r="Q77" s="210"/>
-      <c r="R77" s="210"/>
-      <c r="S77" s="210"/>
-      <c r="T77" s="210"/>
-      <c r="U77" s="210"/>
+      <c r="E77" s="271"/>
+      <c r="F77" s="271"/>
+      <c r="G77" s="271"/>
+      <c r="H77" s="271"/>
+      <c r="I77" s="271"/>
+      <c r="J77" s="271"/>
+      <c r="K77" s="271"/>
+      <c r="L77" s="271"/>
+      <c r="M77" s="271"/>
+      <c r="N77" s="271"/>
+      <c r="O77" s="271"/>
+      <c r="P77" s="271"/>
+      <c r="Q77" s="271"/>
+      <c r="R77" s="271"/>
+      <c r="S77" s="271"/>
+      <c r="T77" s="271"/>
+      <c r="U77" s="271"/>
     </row>
     <row r="78" spans="2:21" ht="20" customHeight="1">
       <c r="B78" s="26"/>
-      <c r="D78" s="210" t="s">
+      <c r="D78" s="271" t="s">
         <v>112</v>
       </c>
-      <c r="E78" s="210"/>
-      <c r="F78" s="210"/>
-      <c r="G78" s="210"/>
-      <c r="H78" s="210"/>
-      <c r="I78" s="210"/>
-      <c r="J78" s="210"/>
-      <c r="K78" s="210"/>
-      <c r="L78" s="210"/>
-      <c r="M78" s="210"/>
-      <c r="N78" s="210"/>
-      <c r="O78" s="210"/>
-      <c r="P78" s="210"/>
-      <c r="Q78" s="210"/>
-      <c r="R78" s="210"/>
-      <c r="S78" s="210"/>
-      <c r="T78" s="210"/>
-      <c r="U78" s="210"/>
+      <c r="E78" s="271"/>
+      <c r="F78" s="271"/>
+      <c r="G78" s="271"/>
+      <c r="H78" s="271"/>
+      <c r="I78" s="271"/>
+      <c r="J78" s="271"/>
+      <c r="K78" s="271"/>
+      <c r="L78" s="271"/>
+      <c r="M78" s="271"/>
+      <c r="N78" s="271"/>
+      <c r="O78" s="271"/>
+      <c r="P78" s="271"/>
+      <c r="Q78" s="271"/>
+      <c r="R78" s="271"/>
+      <c r="S78" s="271"/>
+      <c r="T78" s="271"/>
+      <c r="U78" s="271"/>
     </row>
     <row r="79" spans="2:21" ht="20" customHeight="1">
       <c r="B79" s="26"/>
-      <c r="D79" s="210" t="s">
+      <c r="D79" s="271" t="s">
         <v>113</v>
       </c>
-      <c r="E79" s="210"/>
-      <c r="F79" s="210"/>
-      <c r="G79" s="210"/>
-      <c r="H79" s="210"/>
-      <c r="I79" s="210"/>
-      <c r="J79" s="210"/>
-      <c r="K79" s="210"/>
-      <c r="L79" s="210"/>
-      <c r="M79" s="210"/>
-      <c r="N79" s="210"/>
-      <c r="O79" s="210"/>
-      <c r="P79" s="210"/>
-      <c r="Q79" s="210"/>
-      <c r="R79" s="210"/>
-      <c r="S79" s="210"/>
-      <c r="T79" s="210"/>
-      <c r="U79" s="210"/>
+      <c r="E79" s="271"/>
+      <c r="F79" s="271"/>
+      <c r="G79" s="271"/>
+      <c r="H79" s="271"/>
+      <c r="I79" s="271"/>
+      <c r="J79" s="271"/>
+      <c r="K79" s="271"/>
+      <c r="L79" s="271"/>
+      <c r="M79" s="271"/>
+      <c r="N79" s="271"/>
+      <c r="O79" s="271"/>
+      <c r="P79" s="271"/>
+      <c r="Q79" s="271"/>
+      <c r="R79" s="271"/>
+      <c r="S79" s="271"/>
+      <c r="T79" s="271"/>
+      <c r="U79" s="271"/>
     </row>
     <row r="80" spans="2:21" ht="20" customHeight="1">
       <c r="B80" s="26"/>
-      <c r="D80" s="210" t="s">
+      <c r="D80" s="271" t="s">
         <v>114</v>
       </c>
-      <c r="E80" s="210"/>
-      <c r="F80" s="210"/>
-      <c r="G80" s="210"/>
-      <c r="H80" s="210"/>
-      <c r="I80" s="210"/>
-      <c r="J80" s="210"/>
-      <c r="K80" s="210"/>
-      <c r="L80" s="210"/>
-      <c r="M80" s="210"/>
-      <c r="N80" s="210"/>
-      <c r="O80" s="210"/>
-      <c r="P80" s="210"/>
-      <c r="Q80" s="210"/>
-      <c r="R80" s="210"/>
-      <c r="S80" s="210"/>
-      <c r="T80" s="210"/>
-      <c r="U80" s="210"/>
+      <c r="E80" s="271"/>
+      <c r="F80" s="271"/>
+      <c r="G80" s="271"/>
+      <c r="H80" s="271"/>
+      <c r="I80" s="271"/>
+      <c r="J80" s="271"/>
+      <c r="K80" s="271"/>
+      <c r="L80" s="271"/>
+      <c r="M80" s="271"/>
+      <c r="N80" s="271"/>
+      <c r="O80" s="271"/>
+      <c r="P80" s="271"/>
+      <c r="Q80" s="271"/>
+      <c r="R80" s="271"/>
+      <c r="S80" s="271"/>
+      <c r="T80" s="271"/>
+      <c r="U80" s="271"/>
     </row>
     <row r="81" spans="2:21" ht="20" customHeight="1">
       <c r="B81" s="26"/>
-      <c r="D81" s="210" t="s">
+      <c r="D81" s="271" t="s">
         <v>115</v>
       </c>
-      <c r="E81" s="210"/>
-      <c r="F81" s="210"/>
-      <c r="G81" s="210"/>
-      <c r="H81" s="210"/>
-      <c r="I81" s="210"/>
-      <c r="J81" s="210"/>
-      <c r="K81" s="210"/>
-      <c r="L81" s="210"/>
-      <c r="M81" s="210"/>
-      <c r="N81" s="210"/>
-      <c r="O81" s="210"/>
-      <c r="P81" s="210"/>
-      <c r="Q81" s="210"/>
-      <c r="R81" s="210"/>
-      <c r="S81" s="210"/>
-      <c r="T81" s="210"/>
-      <c r="U81" s="210"/>
+      <c r="E81" s="271"/>
+      <c r="F81" s="271"/>
+      <c r="G81" s="271"/>
+      <c r="H81" s="271"/>
+      <c r="I81" s="271"/>
+      <c r="J81" s="271"/>
+      <c r="K81" s="271"/>
+      <c r="L81" s="271"/>
+      <c r="M81" s="271"/>
+      <c r="N81" s="271"/>
+      <c r="O81" s="271"/>
+      <c r="P81" s="271"/>
+      <c r="Q81" s="271"/>
+      <c r="R81" s="271"/>
+      <c r="S81" s="271"/>
+      <c r="T81" s="271"/>
+      <c r="U81" s="271"/>
     </row>
     <row r="82" spans="2:21" ht="20" customHeight="1">
       <c r="B82" s="26"/>
@@ -35925,52 +35932,52 @@
       <c r="U82" s="52"/>
     </row>
     <row r="83" spans="2:21" ht="17">
-      <c r="B83" s="208" t="s">
+      <c r="B83" s="282" t="s">
         <v>120</v>
       </c>
-      <c r="C83" s="208"/>
-      <c r="D83" s="208"/>
-      <c r="E83" s="208"/>
-      <c r="F83" s="208"/>
-      <c r="G83" s="208"/>
-      <c r="H83" s="208"/>
-      <c r="I83" s="208"/>
-      <c r="J83" s="208"/>
-      <c r="K83" s="208"/>
-      <c r="L83" s="208"/>
-      <c r="M83" s="208"/>
-      <c r="N83" s="208"/>
-      <c r="O83" s="208"/>
-      <c r="P83" s="208"/>
-      <c r="Q83" s="208"/>
-      <c r="R83" s="208"/>
-      <c r="S83" s="208"/>
-      <c r="T83" s="208"/>
-      <c r="U83" s="208"/>
+      <c r="C83" s="282"/>
+      <c r="D83" s="282"/>
+      <c r="E83" s="282"/>
+      <c r="F83" s="282"/>
+      <c r="G83" s="282"/>
+      <c r="H83" s="282"/>
+      <c r="I83" s="282"/>
+      <c r="J83" s="282"/>
+      <c r="K83" s="282"/>
+      <c r="L83" s="282"/>
+      <c r="M83" s="282"/>
+      <c r="N83" s="282"/>
+      <c r="O83" s="282"/>
+      <c r="P83" s="282"/>
+      <c r="Q83" s="282"/>
+      <c r="R83" s="282"/>
+      <c r="S83" s="282"/>
+      <c r="T83" s="282"/>
+      <c r="U83" s="282"/>
     </row>
     <row r="84" spans="2:21" ht="20" customHeight="1">
       <c r="B84" s="117"/>
-      <c r="C84" s="210" t="s">
+      <c r="C84" s="271" t="s">
         <v>151</v>
       </c>
-      <c r="D84" s="210"/>
-      <c r="E84" s="210"/>
-      <c r="F84" s="210"/>
-      <c r="G84" s="210"/>
-      <c r="H84" s="210"/>
-      <c r="I84" s="210"/>
-      <c r="J84" s="210"/>
-      <c r="K84" s="210"/>
-      <c r="L84" s="210"/>
-      <c r="M84" s="210"/>
-      <c r="N84" s="210"/>
-      <c r="O84" s="210"/>
-      <c r="P84" s="210"/>
-      <c r="Q84" s="210"/>
-      <c r="R84" s="210"/>
-      <c r="S84" s="210"/>
-      <c r="T84" s="210"/>
-      <c r="U84" s="210"/>
+      <c r="D84" s="271"/>
+      <c r="E84" s="271"/>
+      <c r="F84" s="271"/>
+      <c r="G84" s="271"/>
+      <c r="H84" s="271"/>
+      <c r="I84" s="271"/>
+      <c r="J84" s="271"/>
+      <c r="K84" s="271"/>
+      <c r="L84" s="271"/>
+      <c r="M84" s="271"/>
+      <c r="N84" s="271"/>
+      <c r="O84" s="271"/>
+      <c r="P84" s="271"/>
+      <c r="Q84" s="271"/>
+      <c r="R84" s="271"/>
+      <c r="S84" s="271"/>
+      <c r="T84" s="271"/>
+      <c r="U84" s="271"/>
     </row>
     <row r="85" spans="2:21" ht="20" customHeight="1">
       <c r="B85" s="26"/>
@@ -35979,51 +35986,51 @@
       <c r="I85" s="3"/>
     </row>
     <row r="86" spans="2:21" ht="20" customHeight="1">
-      <c r="B86" s="208" t="s">
+      <c r="B86" s="282" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="208"/>
-      <c r="D86" s="208"/>
-      <c r="E86" s="208"/>
-      <c r="F86" s="208"/>
-      <c r="G86" s="208"/>
-      <c r="H86" s="208"/>
-      <c r="I86" s="208"/>
-      <c r="J86" s="208"/>
-      <c r="K86" s="208"/>
-      <c r="L86" s="208"/>
-      <c r="M86" s="208"/>
-      <c r="N86" s="208"/>
-      <c r="O86" s="208"/>
-      <c r="P86" s="208"/>
-      <c r="Q86" s="208"/>
-      <c r="R86" s="208"/>
-      <c r="S86" s="208"/>
-      <c r="T86" s="208"/>
-      <c r="U86" s="208"/>
+      <c r="C86" s="282"/>
+      <c r="D86" s="282"/>
+      <c r="E86" s="282"/>
+      <c r="F86" s="282"/>
+      <c r="G86" s="282"/>
+      <c r="H86" s="282"/>
+      <c r="I86" s="282"/>
+      <c r="J86" s="282"/>
+      <c r="K86" s="282"/>
+      <c r="L86" s="282"/>
+      <c r="M86" s="282"/>
+      <c r="N86" s="282"/>
+      <c r="O86" s="282"/>
+      <c r="P86" s="282"/>
+      <c r="Q86" s="282"/>
+      <c r="R86" s="282"/>
+      <c r="S86" s="282"/>
+      <c r="T86" s="282"/>
+      <c r="U86" s="282"/>
     </row>
     <row r="87" spans="2:21" ht="49.5" customHeight="1">
-      <c r="C87" s="217" t="s">
+      <c r="C87" s="209" t="s">
         <v>116</v>
       </c>
-      <c r="D87" s="217"/>
-      <c r="E87" s="217"/>
-      <c r="F87" s="217"/>
-      <c r="G87" s="217"/>
-      <c r="H87" s="217"/>
-      <c r="I87" s="217"/>
-      <c r="J87" s="217"/>
-      <c r="K87" s="217"/>
-      <c r="L87" s="217"/>
-      <c r="M87" s="217"/>
-      <c r="N87" s="217"/>
-      <c r="O87" s="217"/>
-      <c r="P87" s="217"/>
-      <c r="Q87" s="217"/>
-      <c r="R87" s="217"/>
-      <c r="S87" s="217"/>
-      <c r="T87" s="217"/>
-      <c r="U87" s="217"/>
+      <c r="D87" s="209"/>
+      <c r="E87" s="209"/>
+      <c r="F87" s="209"/>
+      <c r="G87" s="209"/>
+      <c r="H87" s="209"/>
+      <c r="I87" s="209"/>
+      <c r="J87" s="209"/>
+      <c r="K87" s="209"/>
+      <c r="L87" s="209"/>
+      <c r="M87" s="209"/>
+      <c r="N87" s="209"/>
+      <c r="O87" s="209"/>
+      <c r="P87" s="209"/>
+      <c r="Q87" s="209"/>
+      <c r="R87" s="209"/>
+      <c r="S87" s="209"/>
+      <c r="T87" s="209"/>
+      <c r="U87" s="209"/>
     </row>
     <row r="88" spans="2:21" ht="20" customHeight="1">
       <c r="C88" s="27"/>
@@ -36036,97 +36043,97 @@
       <c r="J88" s="27"/>
     </row>
     <row r="89" spans="2:21" ht="20" customHeight="1">
-      <c r="B89" s="207" t="s">
+      <c r="B89" s="264" t="s">
         <v>122</v>
       </c>
-      <c r="C89" s="207"/>
-      <c r="D89" s="207"/>
-      <c r="E89" s="207"/>
-      <c r="F89" s="207"/>
-      <c r="G89" s="207"/>
-      <c r="H89" s="207"/>
-      <c r="I89" s="207"/>
-      <c r="J89" s="207"/>
-      <c r="K89" s="207"/>
-      <c r="L89" s="207"/>
-      <c r="M89" s="207"/>
-      <c r="N89" s="207"/>
-      <c r="O89" s="207"/>
-      <c r="P89" s="207"/>
-      <c r="Q89" s="207"/>
-      <c r="R89" s="207"/>
-      <c r="S89" s="207"/>
-      <c r="T89" s="207"/>
-      <c r="U89" s="207"/>
+      <c r="C89" s="264"/>
+      <c r="D89" s="264"/>
+      <c r="E89" s="264"/>
+      <c r="F89" s="264"/>
+      <c r="G89" s="264"/>
+      <c r="H89" s="264"/>
+      <c r="I89" s="264"/>
+      <c r="J89" s="264"/>
+      <c r="K89" s="264"/>
+      <c r="L89" s="264"/>
+      <c r="M89" s="264"/>
+      <c r="N89" s="264"/>
+      <c r="O89" s="264"/>
+      <c r="P89" s="264"/>
+      <c r="Q89" s="264"/>
+      <c r="R89" s="264"/>
+      <c r="S89" s="264"/>
+      <c r="T89" s="264"/>
+      <c r="U89" s="264"/>
     </row>
     <row r="90" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C90" s="205" t="s">
+      <c r="C90" s="278" t="s">
         <v>117</v>
       </c>
-      <c r="D90" s="205"/>
-      <c r="E90" s="205"/>
-      <c r="F90" s="205"/>
-      <c r="G90" s="205"/>
-      <c r="H90" s="205"/>
-      <c r="I90" s="205"/>
-      <c r="J90" s="205"/>
-      <c r="K90" s="205"/>
-      <c r="L90" s="205"/>
-      <c r="M90" s="205"/>
-      <c r="N90" s="205"/>
-      <c r="O90" s="205"/>
-      <c r="P90" s="205"/>
-      <c r="Q90" s="205"/>
-      <c r="R90" s="205"/>
-      <c r="S90" s="205"/>
-      <c r="T90" s="205"/>
-      <c r="U90" s="205"/>
+      <c r="D90" s="278"/>
+      <c r="E90" s="278"/>
+      <c r="F90" s="278"/>
+      <c r="G90" s="278"/>
+      <c r="H90" s="278"/>
+      <c r="I90" s="278"/>
+      <c r="J90" s="278"/>
+      <c r="K90" s="278"/>
+      <c r="L90" s="278"/>
+      <c r="M90" s="278"/>
+      <c r="N90" s="278"/>
+      <c r="O90" s="278"/>
+      <c r="P90" s="278"/>
+      <c r="Q90" s="278"/>
+      <c r="R90" s="278"/>
+      <c r="S90" s="278"/>
+      <c r="T90" s="278"/>
+      <c r="U90" s="278"/>
     </row>
     <row r="91" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C91" s="205" t="s">
+      <c r="C91" s="278" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="205"/>
-      <c r="E91" s="205"/>
-      <c r="F91" s="205"/>
-      <c r="G91" s="205"/>
-      <c r="H91" s="205"/>
-      <c r="I91" s="205"/>
-      <c r="J91" s="205"/>
-      <c r="K91" s="205"/>
-      <c r="L91" s="205"/>
-      <c r="M91" s="205"/>
-      <c r="N91" s="205"/>
-      <c r="O91" s="205"/>
-      <c r="P91" s="205"/>
-      <c r="Q91" s="205"/>
-      <c r="R91" s="205"/>
-      <c r="S91" s="205"/>
-      <c r="T91" s="205"/>
-      <c r="U91" s="205"/>
+      <c r="D91" s="278"/>
+      <c r="E91" s="278"/>
+      <c r="F91" s="278"/>
+      <c r="G91" s="278"/>
+      <c r="H91" s="278"/>
+      <c r="I91" s="278"/>
+      <c r="J91" s="278"/>
+      <c r="K91" s="278"/>
+      <c r="L91" s="278"/>
+      <c r="M91" s="278"/>
+      <c r="N91" s="278"/>
+      <c r="O91" s="278"/>
+      <c r="P91" s="278"/>
+      <c r="Q91" s="278"/>
+      <c r="R91" s="278"/>
+      <c r="S91" s="278"/>
+      <c r="T91" s="278"/>
+      <c r="U91" s="278"/>
     </row>
     <row r="92" spans="2:21" ht="47" customHeight="1">
-      <c r="C92" s="205" t="s">
+      <c r="C92" s="278" t="s">
         <v>119</v>
       </c>
-      <c r="D92" s="205"/>
-      <c r="E92" s="205"/>
-      <c r="F92" s="205"/>
-      <c r="G92" s="205"/>
-      <c r="H92" s="205"/>
-      <c r="I92" s="205"/>
-      <c r="J92" s="205"/>
-      <c r="K92" s="205"/>
-      <c r="L92" s="205"/>
-      <c r="M92" s="205"/>
-      <c r="N92" s="205"/>
-      <c r="O92" s="205"/>
-      <c r="P92" s="205"/>
-      <c r="Q92" s="205"/>
-      <c r="R92" s="205"/>
-      <c r="S92" s="205"/>
-      <c r="T92" s="205"/>
-      <c r="U92" s="205"/>
+      <c r="D92" s="278"/>
+      <c r="E92" s="278"/>
+      <c r="F92" s="278"/>
+      <c r="G92" s="278"/>
+      <c r="H92" s="278"/>
+      <c r="I92" s="278"/>
+      <c r="J92" s="278"/>
+      <c r="K92" s="278"/>
+      <c r="L92" s="278"/>
+      <c r="M92" s="278"/>
+      <c r="N92" s="278"/>
+      <c r="O92" s="278"/>
+      <c r="P92" s="278"/>
+      <c r="Q92" s="278"/>
+      <c r="R92" s="278"/>
+      <c r="S92" s="278"/>
+      <c r="T92" s="278"/>
+      <c r="U92" s="278"/>
     </row>
     <row r="93" spans="2:21" ht="20" customHeight="1">
       <c r="B93" s="118"/>
@@ -36151,98 +36158,98 @@
       <c r="U93" s="48"/>
     </row>
     <row r="94" spans="2:21" ht="20" customHeight="1">
-      <c r="B94" s="207" t="s">
+      <c r="B94" s="264" t="s">
         <v>123</v>
       </c>
-      <c r="C94" s="207"/>
-      <c r="D94" s="207"/>
-      <c r="E94" s="207"/>
-      <c r="F94" s="207"/>
-      <c r="G94" s="207"/>
-      <c r="H94" s="207"/>
-      <c r="I94" s="207"/>
-      <c r="J94" s="207"/>
-      <c r="K94" s="207"/>
-      <c r="L94" s="207"/>
-      <c r="M94" s="207"/>
-      <c r="N94" s="207"/>
-      <c r="O94" s="207"/>
-      <c r="P94" s="207"/>
-      <c r="Q94" s="207"/>
-      <c r="R94" s="207"/>
-      <c r="S94" s="207"/>
-      <c r="T94" s="207"/>
-      <c r="U94" s="207"/>
+      <c r="C94" s="264"/>
+      <c r="D94" s="264"/>
+      <c r="E94" s="264"/>
+      <c r="F94" s="264"/>
+      <c r="G94" s="264"/>
+      <c r="H94" s="264"/>
+      <c r="I94" s="264"/>
+      <c r="J94" s="264"/>
+      <c r="K94" s="264"/>
+      <c r="L94" s="264"/>
+      <c r="M94" s="264"/>
+      <c r="N94" s="264"/>
+      <c r="O94" s="264"/>
+      <c r="P94" s="264"/>
+      <c r="Q94" s="264"/>
+      <c r="R94" s="264"/>
+      <c r="S94" s="264"/>
+      <c r="T94" s="264"/>
+      <c r="U94" s="264"/>
     </row>
     <row r="95" spans="2:21" ht="69" customHeight="1">
-      <c r="C95" s="205" t="s">
+      <c r="C95" s="278" t="s">
         <v>124</v>
       </c>
-      <c r="D95" s="205"/>
-      <c r="E95" s="205"/>
-      <c r="F95" s="205"/>
-      <c r="G95" s="205"/>
-      <c r="H95" s="205"/>
-      <c r="I95" s="205"/>
-      <c r="J95" s="205"/>
-      <c r="K95" s="205"/>
-      <c r="L95" s="205"/>
-      <c r="M95" s="205"/>
-      <c r="N95" s="205"/>
-      <c r="O95" s="205"/>
-      <c r="P95" s="205"/>
-      <c r="Q95" s="205"/>
-      <c r="R95" s="205"/>
-      <c r="S95" s="205"/>
-      <c r="T95" s="205"/>
-      <c r="U95" s="205"/>
+      <c r="D95" s="278"/>
+      <c r="E95" s="278"/>
+      <c r="F95" s="278"/>
+      <c r="G95" s="278"/>
+      <c r="H95" s="278"/>
+      <c r="I95" s="278"/>
+      <c r="J95" s="278"/>
+      <c r="K95" s="278"/>
+      <c r="L95" s="278"/>
+      <c r="M95" s="278"/>
+      <c r="N95" s="278"/>
+      <c r="O95" s="278"/>
+      <c r="P95" s="278"/>
+      <c r="Q95" s="278"/>
+      <c r="R95" s="278"/>
+      <c r="S95" s="278"/>
+      <c r="T95" s="278"/>
+      <c r="U95" s="278"/>
     </row>
     <row r="96" spans="2:21" ht="20" customHeight="1">
-      <c r="C96" s="205" t="s">
+      <c r="C96" s="278" t="s">
         <v>125</v>
       </c>
-      <c r="D96" s="205"/>
-      <c r="E96" s="205"/>
-      <c r="F96" s="205"/>
-      <c r="G96" s="205"/>
-      <c r="H96" s="205"/>
-      <c r="I96" s="205"/>
-      <c r="J96" s="205"/>
-      <c r="K96" s="205"/>
-      <c r="L96" s="205"/>
-      <c r="M96" s="205"/>
-      <c r="N96" s="205"/>
-      <c r="O96" s="205"/>
-      <c r="P96" s="205"/>
-      <c r="Q96" s="205"/>
-      <c r="R96" s="205"/>
-      <c r="S96" s="205"/>
-      <c r="T96" s="205"/>
-      <c r="U96" s="205"/>
+      <c r="D96" s="278"/>
+      <c r="E96" s="278"/>
+      <c r="F96" s="278"/>
+      <c r="G96" s="278"/>
+      <c r="H96" s="278"/>
+      <c r="I96" s="278"/>
+      <c r="J96" s="278"/>
+      <c r="K96" s="278"/>
+      <c r="L96" s="278"/>
+      <c r="M96" s="278"/>
+      <c r="N96" s="278"/>
+      <c r="O96" s="278"/>
+      <c r="P96" s="278"/>
+      <c r="Q96" s="278"/>
+      <c r="R96" s="278"/>
+      <c r="S96" s="278"/>
+      <c r="T96" s="278"/>
+      <c r="U96" s="278"/>
     </row>
     <row r="97" spans="2:21" ht="33" customHeight="1">
       <c r="B97" s="121"/>
-      <c r="C97" s="206" t="s">
+      <c r="C97" s="286" t="s">
         <v>126</v>
       </c>
-      <c r="D97" s="206"/>
-      <c r="E97" s="206"/>
-      <c r="F97" s="206"/>
-      <c r="G97" s="206"/>
-      <c r="H97" s="206"/>
-      <c r="I97" s="206"/>
-      <c r="J97" s="206"/>
-      <c r="K97" s="206"/>
-      <c r="L97" s="206"/>
-      <c r="M97" s="206"/>
-      <c r="N97" s="206"/>
-      <c r="O97" s="206"/>
-      <c r="P97" s="206"/>
-      <c r="Q97" s="206"/>
-      <c r="R97" s="206"/>
-      <c r="S97" s="206"/>
-      <c r="T97" s="206"/>
-      <c r="U97" s="206"/>
+      <c r="D97" s="286"/>
+      <c r="E97" s="286"/>
+      <c r="F97" s="286"/>
+      <c r="G97" s="286"/>
+      <c r="H97" s="286"/>
+      <c r="I97" s="286"/>
+      <c r="J97" s="286"/>
+      <c r="K97" s="286"/>
+      <c r="L97" s="286"/>
+      <c r="M97" s="286"/>
+      <c r="N97" s="286"/>
+      <c r="O97" s="286"/>
+      <c r="P97" s="286"/>
+      <c r="Q97" s="286"/>
+      <c r="R97" s="286"/>
+      <c r="S97" s="286"/>
+      <c r="T97" s="286"/>
+      <c r="U97" s="286"/>
     </row>
     <row r="98" spans="2:21" ht="20" customHeight="1">
       <c r="B98" s="118"/>
@@ -36267,74 +36274,74 @@
       <c r="U98" s="48"/>
     </row>
     <row r="99" spans="2:21" ht="20" customHeight="1">
-      <c r="B99" s="207" t="s">
+      <c r="B99" s="264" t="s">
         <v>127</v>
       </c>
-      <c r="C99" s="207"/>
-      <c r="D99" s="207"/>
-      <c r="E99" s="207"/>
-      <c r="F99" s="207"/>
-      <c r="G99" s="207"/>
-      <c r="H99" s="207"/>
-      <c r="I99" s="207"/>
-      <c r="J99" s="207"/>
-      <c r="K99" s="207"/>
-      <c r="L99" s="207"/>
-      <c r="M99" s="207"/>
-      <c r="N99" s="207"/>
-      <c r="O99" s="207"/>
-      <c r="P99" s="207"/>
-      <c r="Q99" s="207"/>
-      <c r="R99" s="207"/>
-      <c r="S99" s="207"/>
-      <c r="T99" s="207"/>
-      <c r="U99" s="207"/>
+      <c r="C99" s="264"/>
+      <c r="D99" s="264"/>
+      <c r="E99" s="264"/>
+      <c r="F99" s="264"/>
+      <c r="G99" s="264"/>
+      <c r="H99" s="264"/>
+      <c r="I99" s="264"/>
+      <c r="J99" s="264"/>
+      <c r="K99" s="264"/>
+      <c r="L99" s="264"/>
+      <c r="M99" s="264"/>
+      <c r="N99" s="264"/>
+      <c r="O99" s="264"/>
+      <c r="P99" s="264"/>
+      <c r="Q99" s="264"/>
+      <c r="R99" s="264"/>
+      <c r="S99" s="264"/>
+      <c r="T99" s="264"/>
+      <c r="U99" s="264"/>
     </row>
     <row r="100" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C100" s="205" t="s">
+      <c r="C100" s="278" t="s">
         <v>173</v>
       </c>
-      <c r="D100" s="205"/>
-      <c r="E100" s="205"/>
-      <c r="F100" s="205"/>
-      <c r="G100" s="205"/>
-      <c r="H100" s="205"/>
-      <c r="I100" s="205"/>
-      <c r="J100" s="205"/>
-      <c r="K100" s="205"/>
-      <c r="L100" s="205"/>
-      <c r="M100" s="205"/>
-      <c r="N100" s="205"/>
-      <c r="O100" s="205"/>
-      <c r="P100" s="205"/>
-      <c r="Q100" s="205"/>
-      <c r="R100" s="205"/>
-      <c r="S100" s="205"/>
-      <c r="T100" s="205"/>
-      <c r="U100" s="205"/>
+      <c r="D100" s="278"/>
+      <c r="E100" s="278"/>
+      <c r="F100" s="278"/>
+      <c r="G100" s="278"/>
+      <c r="H100" s="278"/>
+      <c r="I100" s="278"/>
+      <c r="J100" s="278"/>
+      <c r="K100" s="278"/>
+      <c r="L100" s="278"/>
+      <c r="M100" s="278"/>
+      <c r="N100" s="278"/>
+      <c r="O100" s="278"/>
+      <c r="P100" s="278"/>
+      <c r="Q100" s="278"/>
+      <c r="R100" s="278"/>
+      <c r="S100" s="278"/>
+      <c r="T100" s="278"/>
+      <c r="U100" s="278"/>
     </row>
     <row r="101" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C101" s="205" t="s">
+      <c r="C101" s="278" t="s">
         <v>130</v>
       </c>
-      <c r="D101" s="205"/>
-      <c r="E101" s="205"/>
-      <c r="F101" s="205"/>
-      <c r="G101" s="205"/>
-      <c r="H101" s="205"/>
-      <c r="I101" s="205"/>
-      <c r="J101" s="205"/>
-      <c r="K101" s="205"/>
-      <c r="L101" s="205"/>
-      <c r="M101" s="205"/>
-      <c r="N101" s="205"/>
-      <c r="O101" s="205"/>
-      <c r="P101" s="205"/>
-      <c r="Q101" s="205"/>
-      <c r="R101" s="205"/>
-      <c r="S101" s="205"/>
-      <c r="T101" s="205"/>
-      <c r="U101" s="205"/>
+      <c r="D101" s="278"/>
+      <c r="E101" s="278"/>
+      <c r="F101" s="278"/>
+      <c r="G101" s="278"/>
+      <c r="H101" s="278"/>
+      <c r="I101" s="278"/>
+      <c r="J101" s="278"/>
+      <c r="K101" s="278"/>
+      <c r="L101" s="278"/>
+      <c r="M101" s="278"/>
+      <c r="N101" s="278"/>
+      <c r="O101" s="278"/>
+      <c r="P101" s="278"/>
+      <c r="Q101" s="278"/>
+      <c r="R101" s="278"/>
+      <c r="S101" s="278"/>
+      <c r="T101" s="278"/>
+      <c r="U101" s="278"/>
     </row>
     <row r="102" spans="2:21" ht="20" customHeight="1">
       <c r="B102" s="118"/>
@@ -36359,74 +36366,74 @@
       <c r="U102" s="48"/>
     </row>
     <row r="103" spans="2:21" ht="20" customHeight="1">
-      <c r="B103" s="207" t="s">
+      <c r="B103" s="264" t="s">
         <v>128</v>
       </c>
-      <c r="C103" s="207"/>
-      <c r="D103" s="207"/>
-      <c r="E103" s="207"/>
-      <c r="F103" s="207"/>
-      <c r="G103" s="207"/>
-      <c r="H103" s="207"/>
-      <c r="I103" s="207"/>
-      <c r="J103" s="207"/>
-      <c r="K103" s="207"/>
-      <c r="L103" s="207"/>
-      <c r="M103" s="207"/>
-      <c r="N103" s="207"/>
-      <c r="O103" s="207"/>
-      <c r="P103" s="207"/>
-      <c r="Q103" s="207"/>
-      <c r="R103" s="207"/>
-      <c r="S103" s="207"/>
-      <c r="T103" s="207"/>
-      <c r="U103" s="207"/>
+      <c r="C103" s="264"/>
+      <c r="D103" s="264"/>
+      <c r="E103" s="264"/>
+      <c r="F103" s="264"/>
+      <c r="G103" s="264"/>
+      <c r="H103" s="264"/>
+      <c r="I103" s="264"/>
+      <c r="J103" s="264"/>
+      <c r="K103" s="264"/>
+      <c r="L103" s="264"/>
+      <c r="M103" s="264"/>
+      <c r="N103" s="264"/>
+      <c r="O103" s="264"/>
+      <c r="P103" s="264"/>
+      <c r="Q103" s="264"/>
+      <c r="R103" s="264"/>
+      <c r="S103" s="264"/>
+      <c r="T103" s="264"/>
+      <c r="U103" s="264"/>
     </row>
     <row r="104" spans="2:21" ht="49" customHeight="1">
-      <c r="C104" s="205" t="s">
+      <c r="C104" s="278" t="s">
         <v>161</v>
       </c>
-      <c r="D104" s="205"/>
-      <c r="E104" s="205"/>
-      <c r="F104" s="205"/>
-      <c r="G104" s="205"/>
-      <c r="H104" s="205"/>
-      <c r="I104" s="205"/>
-      <c r="J104" s="205"/>
-      <c r="K104" s="205"/>
-      <c r="L104" s="205"/>
-      <c r="M104" s="205"/>
-      <c r="N104" s="205"/>
-      <c r="O104" s="205"/>
-      <c r="P104" s="205"/>
-      <c r="Q104" s="205"/>
-      <c r="R104" s="205"/>
-      <c r="S104" s="205"/>
-      <c r="T104" s="205"/>
-      <c r="U104" s="205"/>
+      <c r="D104" s="278"/>
+      <c r="E104" s="278"/>
+      <c r="F104" s="278"/>
+      <c r="G104" s="278"/>
+      <c r="H104" s="278"/>
+      <c r="I104" s="278"/>
+      <c r="J104" s="278"/>
+      <c r="K104" s="278"/>
+      <c r="L104" s="278"/>
+      <c r="M104" s="278"/>
+      <c r="N104" s="278"/>
+      <c r="O104" s="278"/>
+      <c r="P104" s="278"/>
+      <c r="Q104" s="278"/>
+      <c r="R104" s="278"/>
+      <c r="S104" s="278"/>
+      <c r="T104" s="278"/>
+      <c r="U104" s="278"/>
     </row>
     <row r="105" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C105" s="205" t="s">
+      <c r="C105" s="278" t="s">
         <v>130</v>
       </c>
-      <c r="D105" s="205"/>
-      <c r="E105" s="205"/>
-      <c r="F105" s="205"/>
-      <c r="G105" s="205"/>
-      <c r="H105" s="205"/>
-      <c r="I105" s="205"/>
-      <c r="J105" s="205"/>
-      <c r="K105" s="205"/>
-      <c r="L105" s="205"/>
-      <c r="M105" s="205"/>
-      <c r="N105" s="205"/>
-      <c r="O105" s="205"/>
-      <c r="P105" s="205"/>
-      <c r="Q105" s="205"/>
-      <c r="R105" s="205"/>
-      <c r="S105" s="205"/>
-      <c r="T105" s="205"/>
-      <c r="U105" s="205"/>
+      <c r="D105" s="278"/>
+      <c r="E105" s="278"/>
+      <c r="F105" s="278"/>
+      <c r="G105" s="278"/>
+      <c r="H105" s="278"/>
+      <c r="I105" s="278"/>
+      <c r="J105" s="278"/>
+      <c r="K105" s="278"/>
+      <c r="L105" s="278"/>
+      <c r="M105" s="278"/>
+      <c r="N105" s="278"/>
+      <c r="O105" s="278"/>
+      <c r="P105" s="278"/>
+      <c r="Q105" s="278"/>
+      <c r="R105" s="278"/>
+      <c r="S105" s="278"/>
+      <c r="T105" s="278"/>
+      <c r="U105" s="278"/>
     </row>
     <row r="106" spans="2:21" ht="20" customHeight="1">
       <c r="B106" s="118"/>
@@ -36451,74 +36458,74 @@
       <c r="U106" s="48"/>
     </row>
     <row r="107" spans="2:21" ht="20" customHeight="1">
-      <c r="B107" s="207" t="s">
+      <c r="B107" s="264" t="s">
         <v>132</v>
       </c>
-      <c r="C107" s="207"/>
-      <c r="D107" s="207"/>
-      <c r="E107" s="207"/>
-      <c r="F107" s="207"/>
-      <c r="G107" s="207"/>
-      <c r="H107" s="207"/>
-      <c r="I107" s="207"/>
-      <c r="J107" s="207"/>
-      <c r="K107" s="207"/>
-      <c r="L107" s="207"/>
-      <c r="M107" s="207"/>
-      <c r="N107" s="207"/>
-      <c r="O107" s="207"/>
-      <c r="P107" s="207"/>
-      <c r="Q107" s="207"/>
-      <c r="R107" s="207"/>
-      <c r="S107" s="207"/>
-      <c r="T107" s="207"/>
-      <c r="U107" s="207"/>
+      <c r="C107" s="264"/>
+      <c r="D107" s="264"/>
+      <c r="E107" s="264"/>
+      <c r="F107" s="264"/>
+      <c r="G107" s="264"/>
+      <c r="H107" s="264"/>
+      <c r="I107" s="264"/>
+      <c r="J107" s="264"/>
+      <c r="K107" s="264"/>
+      <c r="L107" s="264"/>
+      <c r="M107" s="264"/>
+      <c r="N107" s="264"/>
+      <c r="O107" s="264"/>
+      <c r="P107" s="264"/>
+      <c r="Q107" s="264"/>
+      <c r="R107" s="264"/>
+      <c r="S107" s="264"/>
+      <c r="T107" s="264"/>
+      <c r="U107" s="264"/>
     </row>
     <row r="108" spans="2:21" ht="33" customHeight="1">
-      <c r="C108" s="205" t="s">
+      <c r="C108" s="278" t="s">
         <v>129</v>
       </c>
-      <c r="D108" s="205"/>
-      <c r="E108" s="205"/>
-      <c r="F108" s="205"/>
-      <c r="G108" s="205"/>
-      <c r="H108" s="205"/>
-      <c r="I108" s="205"/>
-      <c r="J108" s="205"/>
-      <c r="K108" s="205"/>
-      <c r="L108" s="205"/>
-      <c r="M108" s="205"/>
-      <c r="N108" s="205"/>
-      <c r="O108" s="205"/>
-      <c r="P108" s="205"/>
-      <c r="Q108" s="205"/>
-      <c r="R108" s="205"/>
-      <c r="S108" s="205"/>
-      <c r="T108" s="205"/>
-      <c r="U108" s="205"/>
+      <c r="D108" s="278"/>
+      <c r="E108" s="278"/>
+      <c r="F108" s="278"/>
+      <c r="G108" s="278"/>
+      <c r="H108" s="278"/>
+      <c r="I108" s="278"/>
+      <c r="J108" s="278"/>
+      <c r="K108" s="278"/>
+      <c r="L108" s="278"/>
+      <c r="M108" s="278"/>
+      <c r="N108" s="278"/>
+      <c r="O108" s="278"/>
+      <c r="P108" s="278"/>
+      <c r="Q108" s="278"/>
+      <c r="R108" s="278"/>
+      <c r="S108" s="278"/>
+      <c r="T108" s="278"/>
+      <c r="U108" s="278"/>
     </row>
     <row r="109" spans="2:21" ht="49" customHeight="1">
-      <c r="C109" s="205" t="s">
+      <c r="C109" s="278" t="s">
         <v>131</v>
       </c>
-      <c r="D109" s="205"/>
-      <c r="E109" s="205"/>
-      <c r="F109" s="205"/>
-      <c r="G109" s="205"/>
-      <c r="H109" s="205"/>
-      <c r="I109" s="205"/>
-      <c r="J109" s="205"/>
-      <c r="K109" s="205"/>
-      <c r="L109" s="205"/>
-      <c r="M109" s="205"/>
-      <c r="N109" s="205"/>
-      <c r="O109" s="205"/>
-      <c r="P109" s="205"/>
-      <c r="Q109" s="205"/>
-      <c r="R109" s="205"/>
-      <c r="S109" s="205"/>
-      <c r="T109" s="205"/>
-      <c r="U109" s="205"/>
+      <c r="D109" s="278"/>
+      <c r="E109" s="278"/>
+      <c r="F109" s="278"/>
+      <c r="G109" s="278"/>
+      <c r="H109" s="278"/>
+      <c r="I109" s="278"/>
+      <c r="J109" s="278"/>
+      <c r="K109" s="278"/>
+      <c r="L109" s="278"/>
+      <c r="M109" s="278"/>
+      <c r="N109" s="278"/>
+      <c r="O109" s="278"/>
+      <c r="P109" s="278"/>
+      <c r="Q109" s="278"/>
+      <c r="R109" s="278"/>
+      <c r="S109" s="278"/>
+      <c r="T109" s="278"/>
+      <c r="U109" s="278"/>
     </row>
     <row r="110" spans="2:21" ht="20" customHeight="1">
       <c r="B110" s="118"/>
@@ -36543,143 +36550,143 @@
       <c r="U110" s="48"/>
     </row>
     <row r="111" spans="2:21" ht="20" customHeight="1">
-      <c r="B111" s="207" t="s">
+      <c r="B111" s="264" t="s">
         <v>133</v>
       </c>
-      <c r="C111" s="207"/>
-      <c r="D111" s="207"/>
-      <c r="E111" s="207"/>
-      <c r="F111" s="207"/>
-      <c r="G111" s="207"/>
-      <c r="H111" s="207"/>
-      <c r="I111" s="207"/>
-      <c r="J111" s="207"/>
-      <c r="K111" s="207"/>
-      <c r="L111" s="207"/>
-      <c r="M111" s="207"/>
-      <c r="N111" s="207"/>
-      <c r="O111" s="207"/>
-      <c r="P111" s="207"/>
-      <c r="Q111" s="207"/>
-      <c r="R111" s="207"/>
-      <c r="S111" s="207"/>
-      <c r="T111" s="207"/>
-      <c r="U111" s="207"/>
+      <c r="C111" s="264"/>
+      <c r="D111" s="264"/>
+      <c r="E111" s="264"/>
+      <c r="F111" s="264"/>
+      <c r="G111" s="264"/>
+      <c r="H111" s="264"/>
+      <c r="I111" s="264"/>
+      <c r="J111" s="264"/>
+      <c r="K111" s="264"/>
+      <c r="L111" s="264"/>
+      <c r="M111" s="264"/>
+      <c r="N111" s="264"/>
+      <c r="O111" s="264"/>
+      <c r="P111" s="264"/>
+      <c r="Q111" s="264"/>
+      <c r="R111" s="264"/>
+      <c r="S111" s="264"/>
+      <c r="T111" s="264"/>
+      <c r="U111" s="264"/>
     </row>
     <row r="112" spans="2:21" ht="16.5" customHeight="1">
-      <c r="C112" s="205" t="s">
+      <c r="C112" s="278" t="s">
         <v>134</v>
       </c>
-      <c r="D112" s="205"/>
-      <c r="E112" s="205"/>
-      <c r="F112" s="205"/>
-      <c r="G112" s="205"/>
-      <c r="H112" s="205"/>
-      <c r="I112" s="205"/>
-      <c r="J112" s="205"/>
-      <c r="K112" s="205"/>
-      <c r="L112" s="205"/>
-      <c r="M112" s="205"/>
-      <c r="N112" s="205"/>
-      <c r="O112" s="205"/>
-      <c r="P112" s="205"/>
-      <c r="Q112" s="205"/>
-      <c r="R112" s="205"/>
-      <c r="S112" s="205"/>
-      <c r="T112" s="205"/>
-      <c r="U112" s="205"/>
+      <c r="D112" s="278"/>
+      <c r="E112" s="278"/>
+      <c r="F112" s="278"/>
+      <c r="G112" s="278"/>
+      <c r="H112" s="278"/>
+      <c r="I112" s="278"/>
+      <c r="J112" s="278"/>
+      <c r="K112" s="278"/>
+      <c r="L112" s="278"/>
+      <c r="M112" s="278"/>
+      <c r="N112" s="278"/>
+      <c r="O112" s="278"/>
+      <c r="P112" s="278"/>
+      <c r="Q112" s="278"/>
+      <c r="R112" s="278"/>
+      <c r="S112" s="278"/>
+      <c r="T112" s="278"/>
+      <c r="U112" s="278"/>
     </row>
     <row r="113" spans="2:21" ht="15">
       <c r="C113" s="122"/>
-      <c r="D113" s="205" t="s">
+      <c r="D113" s="278" t="s">
         <v>135</v>
       </c>
-      <c r="E113" s="205"/>
-      <c r="F113" s="205"/>
-      <c r="G113" s="205"/>
-      <c r="H113" s="205"/>
-      <c r="I113" s="205"/>
-      <c r="J113" s="205"/>
-      <c r="K113" s="205"/>
-      <c r="L113" s="205"/>
-      <c r="M113" s="205"/>
-      <c r="N113" s="205"/>
-      <c r="O113" s="205"/>
-      <c r="P113" s="205"/>
-      <c r="Q113" s="205"/>
-      <c r="R113" s="205"/>
-      <c r="S113" s="205"/>
-      <c r="T113" s="205"/>
-      <c r="U113" s="205"/>
+      <c r="E113" s="278"/>
+      <c r="F113" s="278"/>
+      <c r="G113" s="278"/>
+      <c r="H113" s="278"/>
+      <c r="I113" s="278"/>
+      <c r="J113" s="278"/>
+      <c r="K113" s="278"/>
+      <c r="L113" s="278"/>
+      <c r="M113" s="278"/>
+      <c r="N113" s="278"/>
+      <c r="O113" s="278"/>
+      <c r="P113" s="278"/>
+      <c r="Q113" s="278"/>
+      <c r="R113" s="278"/>
+      <c r="S113" s="278"/>
+      <c r="T113" s="278"/>
+      <c r="U113" s="278"/>
     </row>
     <row r="114" spans="2:21" ht="38" customHeight="1">
       <c r="C114" s="122"/>
-      <c r="D114" s="216" t="s">
+      <c r="D114" s="281" t="s">
         <v>136</v>
       </c>
-      <c r="E114" s="216"/>
-      <c r="F114" s="216"/>
-      <c r="G114" s="216"/>
-      <c r="H114" s="216"/>
-      <c r="I114" s="216"/>
-      <c r="J114" s="216"/>
-      <c r="K114" s="216"/>
-      <c r="L114" s="216"/>
-      <c r="M114" s="216"/>
-      <c r="N114" s="216"/>
-      <c r="O114" s="216"/>
-      <c r="P114" s="216"/>
-      <c r="Q114" s="216"/>
-      <c r="R114" s="216"/>
-      <c r="S114" s="216"/>
-      <c r="T114" s="216"/>
-      <c r="U114" s="216"/>
+      <c r="E114" s="281"/>
+      <c r="F114" s="281"/>
+      <c r="G114" s="281"/>
+      <c r="H114" s="281"/>
+      <c r="I114" s="281"/>
+      <c r="J114" s="281"/>
+      <c r="K114" s="281"/>
+      <c r="L114" s="281"/>
+      <c r="M114" s="281"/>
+      <c r="N114" s="281"/>
+      <c r="O114" s="281"/>
+      <c r="P114" s="281"/>
+      <c r="Q114" s="281"/>
+      <c r="R114" s="281"/>
+      <c r="S114" s="281"/>
+      <c r="T114" s="281"/>
+      <c r="U114" s="281"/>
     </row>
     <row r="115" spans="2:21" ht="33" customHeight="1">
       <c r="C115" s="122"/>
-      <c r="D115" s="205" t="s">
+      <c r="D115" s="278" t="s">
         <v>137</v>
       </c>
-      <c r="E115" s="205"/>
-      <c r="F115" s="205"/>
-      <c r="G115" s="205"/>
-      <c r="H115" s="205"/>
-      <c r="I115" s="205"/>
-      <c r="J115" s="205"/>
-      <c r="K115" s="205"/>
-      <c r="L115" s="205"/>
-      <c r="M115" s="205"/>
-      <c r="N115" s="205"/>
-      <c r="O115" s="205"/>
-      <c r="P115" s="205"/>
-      <c r="Q115" s="205"/>
-      <c r="R115" s="205"/>
-      <c r="S115" s="205"/>
-      <c r="T115" s="205"/>
-      <c r="U115" s="205"/>
+      <c r="E115" s="278"/>
+      <c r="F115" s="278"/>
+      <c r="G115" s="278"/>
+      <c r="H115" s="278"/>
+      <c r="I115" s="278"/>
+      <c r="J115" s="278"/>
+      <c r="K115" s="278"/>
+      <c r="L115" s="278"/>
+      <c r="M115" s="278"/>
+      <c r="N115" s="278"/>
+      <c r="O115" s="278"/>
+      <c r="P115" s="278"/>
+      <c r="Q115" s="278"/>
+      <c r="R115" s="278"/>
+      <c r="S115" s="278"/>
+      <c r="T115" s="278"/>
+      <c r="U115" s="278"/>
     </row>
     <row r="116" spans="2:21" ht="20" customHeight="1">
-      <c r="C116" s="205" t="s">
+      <c r="C116" s="278" t="s">
         <v>138</v>
       </c>
-      <c r="D116" s="205"/>
-      <c r="E116" s="205"/>
-      <c r="F116" s="205"/>
-      <c r="G116" s="205"/>
-      <c r="H116" s="205"/>
-      <c r="I116" s="205"/>
-      <c r="J116" s="205"/>
-      <c r="K116" s="205"/>
-      <c r="L116" s="205"/>
-      <c r="M116" s="205"/>
-      <c r="N116" s="205"/>
-      <c r="O116" s="205"/>
-      <c r="P116" s="205"/>
-      <c r="Q116" s="205"/>
-      <c r="R116" s="205"/>
-      <c r="S116" s="205"/>
-      <c r="T116" s="205"/>
-      <c r="U116" s="205"/>
+      <c r="D116" s="278"/>
+      <c r="E116" s="278"/>
+      <c r="F116" s="278"/>
+      <c r="G116" s="278"/>
+      <c r="H116" s="278"/>
+      <c r="I116" s="278"/>
+      <c r="J116" s="278"/>
+      <c r="K116" s="278"/>
+      <c r="L116" s="278"/>
+      <c r="M116" s="278"/>
+      <c r="N116" s="278"/>
+      <c r="O116" s="278"/>
+      <c r="P116" s="278"/>
+      <c r="Q116" s="278"/>
+      <c r="R116" s="278"/>
+      <c r="S116" s="278"/>
+      <c r="T116" s="278"/>
+      <c r="U116" s="278"/>
     </row>
     <row r="117" spans="2:21" ht="20" customHeight="1">
       <c r="B117" s="118"/>
@@ -36704,98 +36711,98 @@
       <c r="U117" s="48"/>
     </row>
     <row r="118" spans="2:21" ht="20" customHeight="1">
-      <c r="B118" s="207" t="s">
+      <c r="B118" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="C118" s="207"/>
-      <c r="D118" s="207"/>
-      <c r="E118" s="207"/>
-      <c r="F118" s="207"/>
-      <c r="G118" s="207"/>
-      <c r="H118" s="207"/>
-      <c r="I118" s="207"/>
-      <c r="J118" s="207"/>
-      <c r="K118" s="207"/>
-      <c r="L118" s="207"/>
-      <c r="M118" s="207"/>
-      <c r="N118" s="207"/>
-      <c r="O118" s="207"/>
-      <c r="P118" s="207"/>
-      <c r="Q118" s="207"/>
-      <c r="R118" s="207"/>
-      <c r="S118" s="207"/>
-      <c r="T118" s="207"/>
-      <c r="U118" s="207"/>
+      <c r="C118" s="264"/>
+      <c r="D118" s="264"/>
+      <c r="E118" s="264"/>
+      <c r="F118" s="264"/>
+      <c r="G118" s="264"/>
+      <c r="H118" s="264"/>
+      <c r="I118" s="264"/>
+      <c r="J118" s="264"/>
+      <c r="K118" s="264"/>
+      <c r="L118" s="264"/>
+      <c r="M118" s="264"/>
+      <c r="N118" s="264"/>
+      <c r="O118" s="264"/>
+      <c r="P118" s="264"/>
+      <c r="Q118" s="264"/>
+      <c r="R118" s="264"/>
+      <c r="S118" s="264"/>
+      <c r="T118" s="264"/>
+      <c r="U118" s="264"/>
     </row>
     <row r="119" spans="2:21" ht="33" customHeight="1">
-      <c r="C119" s="205" t="s">
+      <c r="C119" s="278" t="s">
         <v>140</v>
       </c>
-      <c r="D119" s="205"/>
-      <c r="E119" s="205"/>
-      <c r="F119" s="205"/>
-      <c r="G119" s="205"/>
-      <c r="H119" s="205"/>
-      <c r="I119" s="205"/>
-      <c r="J119" s="205"/>
-      <c r="K119" s="205"/>
-      <c r="L119" s="205"/>
-      <c r="M119" s="205"/>
-      <c r="N119" s="205"/>
-      <c r="O119" s="205"/>
-      <c r="P119" s="205"/>
-      <c r="Q119" s="205"/>
-      <c r="R119" s="205"/>
-      <c r="S119" s="205"/>
-      <c r="T119" s="205"/>
-      <c r="U119" s="205"/>
+      <c r="D119" s="278"/>
+      <c r="E119" s="278"/>
+      <c r="F119" s="278"/>
+      <c r="G119" s="278"/>
+      <c r="H119" s="278"/>
+      <c r="I119" s="278"/>
+      <c r="J119" s="278"/>
+      <c r="K119" s="278"/>
+      <c r="L119" s="278"/>
+      <c r="M119" s="278"/>
+      <c r="N119" s="278"/>
+      <c r="O119" s="278"/>
+      <c r="P119" s="278"/>
+      <c r="Q119" s="278"/>
+      <c r="R119" s="278"/>
+      <c r="S119" s="278"/>
+      <c r="T119" s="278"/>
+      <c r="U119" s="278"/>
     </row>
     <row r="120" spans="2:21" ht="32" customHeight="1">
-      <c r="C120" s="205" t="s">
+      <c r="C120" s="278" t="s">
         <v>141</v>
       </c>
-      <c r="D120" s="205"/>
-      <c r="E120" s="205"/>
-      <c r="F120" s="205"/>
-      <c r="G120" s="205"/>
-      <c r="H120" s="205"/>
-      <c r="I120" s="205"/>
-      <c r="J120" s="205"/>
-      <c r="K120" s="205"/>
-      <c r="L120" s="205"/>
-      <c r="M120" s="205"/>
-      <c r="N120" s="205"/>
-      <c r="O120" s="205"/>
-      <c r="P120" s="205"/>
-      <c r="Q120" s="205"/>
-      <c r="R120" s="205"/>
-      <c r="S120" s="205"/>
-      <c r="T120" s="205"/>
-      <c r="U120" s="205"/>
+      <c r="D120" s="278"/>
+      <c r="E120" s="278"/>
+      <c r="F120" s="278"/>
+      <c r="G120" s="278"/>
+      <c r="H120" s="278"/>
+      <c r="I120" s="278"/>
+      <c r="J120" s="278"/>
+      <c r="K120" s="278"/>
+      <c r="L120" s="278"/>
+      <c r="M120" s="278"/>
+      <c r="N120" s="278"/>
+      <c r="O120" s="278"/>
+      <c r="P120" s="278"/>
+      <c r="Q120" s="278"/>
+      <c r="R120" s="278"/>
+      <c r="S120" s="278"/>
+      <c r="T120" s="278"/>
+      <c r="U120" s="278"/>
     </row>
     <row r="121" spans="2:21" ht="33" customHeight="1">
       <c r="B121" s="118"/>
-      <c r="C121" s="205" t="s">
+      <c r="C121" s="278" t="s">
         <v>189</v>
       </c>
-      <c r="D121" s="205"/>
-      <c r="E121" s="205"/>
-      <c r="F121" s="205"/>
-      <c r="G121" s="205"/>
-      <c r="H121" s="205"/>
-      <c r="I121" s="205"/>
-      <c r="J121" s="205"/>
-      <c r="K121" s="205"/>
-      <c r="L121" s="205"/>
-      <c r="M121" s="205"/>
-      <c r="N121" s="205"/>
-      <c r="O121" s="205"/>
-      <c r="P121" s="205"/>
-      <c r="Q121" s="205"/>
-      <c r="R121" s="205"/>
-      <c r="S121" s="205"/>
-      <c r="T121" s="205"/>
-      <c r="U121" s="205"/>
+      <c r="D121" s="278"/>
+      <c r="E121" s="278"/>
+      <c r="F121" s="278"/>
+      <c r="G121" s="278"/>
+      <c r="H121" s="278"/>
+      <c r="I121" s="278"/>
+      <c r="J121" s="278"/>
+      <c r="K121" s="278"/>
+      <c r="L121" s="278"/>
+      <c r="M121" s="278"/>
+      <c r="N121" s="278"/>
+      <c r="O121" s="278"/>
+      <c r="P121" s="278"/>
+      <c r="Q121" s="278"/>
+      <c r="R121" s="278"/>
+      <c r="S121" s="278"/>
+      <c r="T121" s="278"/>
+      <c r="U121" s="278"/>
     </row>
     <row r="122" spans="2:21" ht="20" customHeight="1">
       <c r="B122" s="118"/>
@@ -36820,51 +36827,51 @@
       <c r="U122" s="48"/>
     </row>
     <row r="123" spans="2:21" ht="20" customHeight="1">
-      <c r="B123" s="207" t="s">
+      <c r="B123" s="264" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="207"/>
-      <c r="D123" s="207"/>
-      <c r="E123" s="207"/>
-      <c r="F123" s="207"/>
-      <c r="G123" s="207"/>
-      <c r="H123" s="207"/>
-      <c r="I123" s="207"/>
-      <c r="J123" s="207"/>
-      <c r="K123" s="207"/>
-      <c r="L123" s="207"/>
-      <c r="M123" s="207"/>
-      <c r="N123" s="207"/>
-      <c r="O123" s="207"/>
-      <c r="P123" s="207"/>
-      <c r="Q123" s="207"/>
-      <c r="R123" s="207"/>
-      <c r="S123" s="207"/>
-      <c r="T123" s="207"/>
-      <c r="U123" s="207"/>
+      <c r="C123" s="264"/>
+      <c r="D123" s="264"/>
+      <c r="E123" s="264"/>
+      <c r="F123" s="264"/>
+      <c r="G123" s="264"/>
+      <c r="H123" s="264"/>
+      <c r="I123" s="264"/>
+      <c r="J123" s="264"/>
+      <c r="K123" s="264"/>
+      <c r="L123" s="264"/>
+      <c r="M123" s="264"/>
+      <c r="N123" s="264"/>
+      <c r="O123" s="264"/>
+      <c r="P123" s="264"/>
+      <c r="Q123" s="264"/>
+      <c r="R123" s="264"/>
+      <c r="S123" s="264"/>
+      <c r="T123" s="264"/>
+      <c r="U123" s="264"/>
     </row>
     <row r="124" spans="2:21" ht="33" customHeight="1">
-      <c r="C124" s="205" t="s">
+      <c r="C124" s="278" t="s">
         <v>174</v>
       </c>
-      <c r="D124" s="205"/>
-      <c r="E124" s="205"/>
-      <c r="F124" s="205"/>
-      <c r="G124" s="205"/>
-      <c r="H124" s="205"/>
-      <c r="I124" s="205"/>
-      <c r="J124" s="205"/>
-      <c r="K124" s="205"/>
-      <c r="L124" s="205"/>
-      <c r="M124" s="205"/>
-      <c r="N124" s="205"/>
-      <c r="O124" s="205"/>
-      <c r="P124" s="205"/>
-      <c r="Q124" s="205"/>
-      <c r="R124" s="205"/>
-      <c r="S124" s="205"/>
-      <c r="T124" s="205"/>
-      <c r="U124" s="205"/>
+      <c r="D124" s="278"/>
+      <c r="E124" s="278"/>
+      <c r="F124" s="278"/>
+      <c r="G124" s="278"/>
+      <c r="H124" s="278"/>
+      <c r="I124" s="278"/>
+      <c r="J124" s="278"/>
+      <c r="K124" s="278"/>
+      <c r="L124" s="278"/>
+      <c r="M124" s="278"/>
+      <c r="N124" s="278"/>
+      <c r="O124" s="278"/>
+      <c r="P124" s="278"/>
+      <c r="Q124" s="278"/>
+      <c r="R124" s="278"/>
+      <c r="S124" s="278"/>
+      <c r="T124" s="278"/>
+      <c r="U124" s="278"/>
     </row>
     <row r="125" spans="2:21" ht="20" customHeight="1">
       <c r="B125" s="118"/>
@@ -36889,40 +36896,40 @@
       <c r="U125" s="48"/>
     </row>
     <row r="126" spans="2:21" ht="20" customHeight="1">
-      <c r="B126" s="207" t="s">
+      <c r="B126" s="264" t="s">
         <v>143</v>
       </c>
-      <c r="C126" s="209"/>
-      <c r="D126" s="209"/>
-      <c r="E126" s="209"/>
-      <c r="F126" s="209"/>
-      <c r="G126" s="209"/>
-      <c r="H126" s="209"/>
-      <c r="I126" s="209"/>
-      <c r="J126" s="209"/>
+      <c r="C126" s="285"/>
+      <c r="D126" s="285"/>
+      <c r="E126" s="285"/>
+      <c r="F126" s="285"/>
+      <c r="G126" s="285"/>
+      <c r="H126" s="285"/>
+      <c r="I126" s="285"/>
+      <c r="J126" s="285"/>
     </row>
     <row r="127" spans="2:21" ht="40" customHeight="1">
-      <c r="C127" s="205" t="s">
+      <c r="C127" s="278" t="s">
         <v>44</v>
       </c>
-      <c r="D127" s="205"/>
-      <c r="E127" s="205"/>
-      <c r="F127" s="205"/>
-      <c r="G127" s="205"/>
-      <c r="H127" s="205"/>
-      <c r="I127" s="205"/>
-      <c r="J127" s="205"/>
-      <c r="K127" s="205"/>
-      <c r="L127" s="205"/>
-      <c r="M127" s="205"/>
-      <c r="N127" s="205"/>
-      <c r="O127" s="205"/>
-      <c r="P127" s="205"/>
-      <c r="Q127" s="205"/>
-      <c r="R127" s="205"/>
-      <c r="S127" s="205"/>
-      <c r="T127" s="205"/>
-      <c r="U127" s="205"/>
+      <c r="D127" s="278"/>
+      <c r="E127" s="278"/>
+      <c r="F127" s="278"/>
+      <c r="G127" s="278"/>
+      <c r="H127" s="278"/>
+      <c r="I127" s="278"/>
+      <c r="J127" s="278"/>
+      <c r="K127" s="278"/>
+      <c r="L127" s="278"/>
+      <c r="M127" s="278"/>
+      <c r="N127" s="278"/>
+      <c r="O127" s="278"/>
+      <c r="P127" s="278"/>
+      <c r="Q127" s="278"/>
+      <c r="R127" s="278"/>
+      <c r="S127" s="278"/>
+      <c r="T127" s="278"/>
+      <c r="U127" s="278"/>
     </row>
     <row r="128" spans="2:21" ht="409.5" customHeight="1">
       <c r="B128" s="118"/>
@@ -36955,96 +36962,7 @@
     <row r="135" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="119">
-    <mergeCell ref="G32:U32"/>
-    <mergeCell ref="G33:U33"/>
-    <mergeCell ref="G34:U34"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:U39"/>
-    <mergeCell ref="D40:F41"/>
-    <mergeCell ref="G40:U40"/>
-    <mergeCell ref="E48:U48"/>
-    <mergeCell ref="E49:U49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B7:U7"/>
-    <mergeCell ref="B8:U8"/>
-    <mergeCell ref="B9:U9"/>
-    <mergeCell ref="B10:U10"/>
-    <mergeCell ref="B16:U16"/>
-    <mergeCell ref="B28:U28"/>
-    <mergeCell ref="I23:S23"/>
-    <mergeCell ref="B22:U22"/>
-    <mergeCell ref="I24:T24"/>
-    <mergeCell ref="I25:T25"/>
-    <mergeCell ref="B29:C34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:U29"/>
-    <mergeCell ref="D30:F34"/>
-    <mergeCell ref="G30:U30"/>
-    <mergeCell ref="G31:U31"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:U41"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="L52:U52"/>
-    <mergeCell ref="B35:C43"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:U36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:U37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:U42"/>
-    <mergeCell ref="G43:U43"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="M35:S35"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:M41"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:U47"/>
-    <mergeCell ref="E51:U51"/>
-    <mergeCell ref="B45:U45"/>
-    <mergeCell ref="G38:U38"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="E55:K55"/>
-    <mergeCell ref="L55:N55"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="E53:K53"/>
-    <mergeCell ref="L53:N53"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="D81:U81"/>
-    <mergeCell ref="D79:U79"/>
-    <mergeCell ref="D80:U80"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="L54:N54"/>
-    <mergeCell ref="O54:U54"/>
-    <mergeCell ref="B56:U56"/>
-    <mergeCell ref="B57:U57"/>
-    <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B99:U99"/>
-    <mergeCell ref="C100:U100"/>
-    <mergeCell ref="C90:U90"/>
-    <mergeCell ref="D115:U115"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="I60:N60"/>
-    <mergeCell ref="D114:U114"/>
-    <mergeCell ref="O60:U60"/>
-    <mergeCell ref="C87:U87"/>
-    <mergeCell ref="B61:U61"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="C64:U64"/>
-    <mergeCell ref="B66:U66"/>
-    <mergeCell ref="F67:U67"/>
-    <mergeCell ref="B72:U72"/>
-    <mergeCell ref="D74:U74"/>
-    <mergeCell ref="D75:U75"/>
-    <mergeCell ref="D76:U76"/>
-    <mergeCell ref="D77:U77"/>
-    <mergeCell ref="D78:U78"/>
+    <mergeCell ref="C124:U124"/>
     <mergeCell ref="B126:J126"/>
     <mergeCell ref="C127:U127"/>
     <mergeCell ref="C84:U84"/>
@@ -37069,11 +36987,100 @@
     <mergeCell ref="C97:U97"/>
     <mergeCell ref="C121:U121"/>
     <mergeCell ref="B123:U123"/>
+    <mergeCell ref="B99:U99"/>
+    <mergeCell ref="C100:U100"/>
+    <mergeCell ref="C90:U90"/>
+    <mergeCell ref="D115:U115"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="I60:N60"/>
+    <mergeCell ref="D114:U114"/>
+    <mergeCell ref="O60:U60"/>
+    <mergeCell ref="C87:U87"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="C64:U64"/>
+    <mergeCell ref="B66:U66"/>
+    <mergeCell ref="F67:U67"/>
+    <mergeCell ref="B72:U72"/>
+    <mergeCell ref="D74:U74"/>
+    <mergeCell ref="D75:U75"/>
+    <mergeCell ref="D76:U76"/>
+    <mergeCell ref="D77:U77"/>
+    <mergeCell ref="D78:U78"/>
     <mergeCell ref="B83:U83"/>
     <mergeCell ref="B86:U86"/>
     <mergeCell ref="B89:U89"/>
+    <mergeCell ref="B45:U45"/>
+    <mergeCell ref="G38:U38"/>
+    <mergeCell ref="E49:U49"/>
+    <mergeCell ref="B50:E50"/>
     <mergeCell ref="B94:U94"/>
-    <mergeCell ref="C124:U124"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="E55:K55"/>
+    <mergeCell ref="L55:N55"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="E53:K53"/>
+    <mergeCell ref="L53:N53"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="D81:U81"/>
+    <mergeCell ref="D79:U79"/>
+    <mergeCell ref="D80:U80"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="L54:N54"/>
+    <mergeCell ref="O54:U54"/>
+    <mergeCell ref="B56:U56"/>
+    <mergeCell ref="B57:U57"/>
+    <mergeCell ref="B59:U59"/>
+    <mergeCell ref="G33:U33"/>
+    <mergeCell ref="G34:U34"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="L52:U52"/>
+    <mergeCell ref="B35:C43"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:U36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:U37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:U42"/>
+    <mergeCell ref="G43:U43"/>
+    <mergeCell ref="G35:L35"/>
+    <mergeCell ref="M35:S35"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:U47"/>
+    <mergeCell ref="E51:U51"/>
+    <mergeCell ref="G39:U39"/>
+    <mergeCell ref="D40:F41"/>
+    <mergeCell ref="G40:U40"/>
+    <mergeCell ref="E48:U48"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B7:U7"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B9:U9"/>
+    <mergeCell ref="B10:U10"/>
+    <mergeCell ref="B16:U16"/>
+    <mergeCell ref="B28:U28"/>
+    <mergeCell ref="I23:S23"/>
+    <mergeCell ref="B22:U22"/>
+    <mergeCell ref="I24:T24"/>
+    <mergeCell ref="I25:T25"/>
+    <mergeCell ref="B29:C34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:U29"/>
+    <mergeCell ref="D30:F34"/>
+    <mergeCell ref="G30:U30"/>
+    <mergeCell ref="G31:U31"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:U41"/>
+    <mergeCell ref="G32:U32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/repair/back/doc/estimate/supervision.xlsx
+++ b/repair/back/doc/estimate/supervision.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="5" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -1404,7 +1404,7 @@
     <numFmt numFmtId="244" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="245" formatCode="0_ "/>
   </numFmts>
-  <fonts count="159">
+  <fonts count="153">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -1703,11 +1703,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="1.0"/>
-      <name val="Courier"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움체"/>
       <color rgb="FF000000"/>
@@ -1774,11 +1769,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="바탕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
       <color rgb="FF000000"/>
@@ -1834,16 +1824,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="한컴 솔잎 B"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <name val="한컴 솔잎 B"/>
@@ -1890,11 +1870,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="17.0"/>
       <name val="돋움"/>
@@ -1908,18 +1883,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
@@ -1996,20 +1960,9 @@
       <color rgb="FFFF0000"/>
     </font>
     <font>
-      <sz val="11.5"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="14.0"/>
       <name val="바탕체"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <name val="돋움"/>
       <color rgb="FF000000"/>
     </font>
     <font>
@@ -2178,16 +2131,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <b/>
       <sz val="24.0"/>
       <name val="바탕"/>
@@ -2196,11 +2139,6 @@
     <font>
       <b/>
       <sz val="36.0"/>
-      <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
@@ -2252,18 +2190,50 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="32.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="32.0"/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2336,12 +2306,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.150000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3410,7 +3374,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3419,7 +3382,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3428,7 +3390,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3437,7 +3398,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3452,7 +3412,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3467,7 +3426,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -3482,7 +3440,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3491,7 +3448,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3502,7 +3458,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3167">
@@ -11421,7 +11376,7 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="82" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="197" fontId="19" fillId="0" borderId="0">
@@ -11860,7 +11815,7 @@
     <xf numFmtId="10" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -11882,34 +11837,34 @@
     <xf numFmtId="226" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="227" fontId="58" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="227" fontId="57" fillId="0" borderId="14" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="60" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="59" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyBorder="0" applyFill="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="15">
+    <xf numFmtId="179" fontId="60" fillId="0" borderId="15">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="228" fontId="55" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="190" fontId="62" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="229" fontId="63" fillId="0" borderId="0">
+    <xf numFmtId="190" fontId="61" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="229" fontId="62" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12698,43 +12653,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="16">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="16">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="230" fontId="32" fillId="0" borderId="2" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="231" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
@@ -12749,20 +12704,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -12790,7 +12745,7 @@
     <xf numFmtId="38" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="228" fontId="57" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="228" fontId="56" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="235" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12799,7 +12754,7 @@
     <xf numFmtId="236" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="237" fontId="57" fillId="0" borderId="2">
+    <xf numFmtId="237" fontId="56" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="238" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12811,11 +12766,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -12826,17 +12781,17 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="222" fontId="56" fillId="0" borderId="0">
+    <xf numFmtId="222" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15">
       <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18">
@@ -12860,7 +12815,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -12887,10 +12842,10 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
@@ -12920,137 +12875,137 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="76" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="77" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="78" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="79" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="14" borderId="80" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="15" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="15" borderId="80" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="16" borderId="82" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="83" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="84" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="42" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="76" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="77" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="78" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="79" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="13" borderId="80" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="14" borderId="81" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="14" borderId="80" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="15" borderId="82" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="83" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="84" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3104">
       <alignment vertical="center"/>
@@ -13062,97 +13017,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="84" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="80" fillId="2" borderId="2" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="84" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="80" fillId="2" borderId="2" xfId="2792" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="34" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="36" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="38" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="38" xfId="2792" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="40" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="42" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="11" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="52" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="75" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="73" fillId="0" borderId="28" xfId="2792" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="2" xfId="3114">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="17" xfId="3114" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="3113" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="0" xfId="3114" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="2" xfId="3114">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="17" xfId="3114" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="17" xfId="3113" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" xfId="3114" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3113">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113">
@@ -13161,44 +13116,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="8" xfId="3113" applyBorder="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="8" xfId="3113" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3113" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="3113">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="3113">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="3113" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="12" borderId="0" xfId="3113" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="12" borderId="0" xfId="3113" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="33" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="243" fontId="78" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="243" fontId="76" fillId="0" borderId="8" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
@@ -13207,169 +13162,169 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="2" borderId="36" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="75" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="35" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="37" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="29" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="75" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="73" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="40" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="31" xfId="3102" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="39" xfId="3102" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="11" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="41" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="42" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="43" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="44" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="38" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="38" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="45" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="28" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="39" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="28" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="48" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="46" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="244" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="244" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="40" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="2" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="84" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="80" fillId="2" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="32" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="8" borderId="2" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="8" borderId="32" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="69" fillId="0" borderId="2" xfId="3102" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="70" fillId="8" borderId="8" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="51" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="23" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="25" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="27" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102"/>
@@ -13379,469 +13334,457 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="38" fontId="73" fillId="0" borderId="28" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="108" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="108" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="3113">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="245" fontId="104" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="71" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="72" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="70" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="71" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="71" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="72" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="71" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="68" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="69" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="75" fillId="0" borderId="28" xfId="2792" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="92" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="117" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="117" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="3113">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3113" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="245" fontId="112" fillId="0" borderId="0" xfId="3113" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="8" borderId="0" xfId="3102" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="71" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="72" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="56" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="6" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="8" borderId="54" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="59" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="60" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="65" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="66" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="67" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="49" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="7" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="68" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="69" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="72" fillId="7" borderId="70" xfId="3102" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="71" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="6" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="54" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="71" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="72" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="59" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="60" xfId="2637" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="75" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="50" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="75" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="8" borderId="50" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="49" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="7" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="73" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="68" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="69" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="74" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="21" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="22" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="24" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="0" xfId="3102" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="26" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="8" xfId="3102" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="22" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="3102" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="8" xfId="3102" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -18034,36 +17977,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:32" s="34" customFormat="1" ht="42.000000" customHeight="1">
-      <c r="B1" s="193" t="s">
+      <c r="B1" s="189" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
-      <c r="V1" s="193"/>
-      <c r="W1" s="193"/>
-      <c r="X1" s="193"/>
-      <c r="Y1" s="193"/>
-      <c r="Z1" s="193"/>
-      <c r="AA1" s="193"/>
-      <c r="AB1" s="193"/>
-      <c r="AC1" s="193"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+      <c r="J1" s="189"/>
+      <c r="K1" s="189"/>
+      <c r="L1" s="189"/>
+      <c r="M1" s="189"/>
+      <c r="N1" s="189"/>
+      <c r="O1" s="189"/>
+      <c r="P1" s="189"/>
+      <c r="Q1" s="189"/>
+      <c r="R1" s="189"/>
+      <c r="S1" s="189"/>
+      <c r="T1" s="189"/>
+      <c r="U1" s="189"/>
+      <c r="V1" s="189"/>
+      <c r="W1" s="189"/>
+      <c r="X1" s="189"/>
+      <c r="Y1" s="189"/>
+      <c r="Z1" s="189"/>
+      <c r="AA1" s="189"/>
+      <c r="AB1" s="189"/>
+      <c r="AC1" s="189"/>
     </row>
     <row r="2" spans="2:32" s="34" customFormat="1" ht="12.000000" customHeight="1">
       <c r="B2" s="36"/>
@@ -18096,36 +18039,36 @@
       <c r="AC2" s="38"/>
     </row>
     <row r="3" spans="2:32" s="34" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="194"/>
-      <c r="O3" s="194"/>
-      <c r="P3" s="194"/>
-      <c r="Q3" s="194"/>
-      <c r="R3" s="194"/>
-      <c r="S3" s="194"/>
-      <c r="T3" s="194"/>
-      <c r="U3" s="194"/>
-      <c r="V3" s="194"/>
-      <c r="W3" s="194"/>
-      <c r="X3" s="194"/>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="194"/>
-      <c r="AA3" s="194"/>
-      <c r="AB3" s="194"/>
-      <c r="AC3" s="194"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
+      <c r="L3" s="190"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
+      <c r="Q3" s="190"/>
+      <c r="R3" s="190"/>
+      <c r="S3" s="190"/>
+      <c r="T3" s="190"/>
+      <c r="U3" s="190"/>
+      <c r="V3" s="190"/>
+      <c r="W3" s="190"/>
+      <c r="X3" s="190"/>
+      <c r="Y3" s="190"/>
+      <c r="Z3" s="190"/>
+      <c r="AA3" s="190"/>
+      <c r="AB3" s="190"/>
+      <c r="AC3" s="190"/>
     </row>
     <row r="4" spans="2:32" s="34" customFormat="1" ht="7.500000" customHeight="1">
       <c r="B4" s="42"/>
@@ -18188,12 +18131,12 @@
       <c r="AC5" s="38"/>
     </row>
     <row r="6" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="192"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="192"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
       <c r="F6" s="36" t="s">
         <v>53</v>
       </c>
@@ -18222,23 +18165,23 @@
       <c r="AC6" s="38"/>
     </row>
     <row r="7" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B7" s="192" t="s">
+      <c r="B7" s="188" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="195">
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="191">
         <v>46072</v>
       </c>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
-      <c r="I7" s="195"/>
-      <c r="J7" s="195"/>
-      <c r="K7" s="195"/>
-      <c r="L7" s="195"/>
-      <c r="M7" s="195"/>
-      <c r="N7" s="195"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="191"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="191"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="191"/>
+      <c r="N7" s="191"/>
       <c r="O7" s="36"/>
       <c r="P7" s="36"/>
       <c r="Q7" s="36"/>
@@ -18256,21 +18199,21 @@
       <c r="AC7" s="38"/>
     </row>
     <row r="8" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B8" s="192" t="s">
+      <c r="B8" s="188" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="192"/>
-      <c r="D8" s="192"/>
-      <c r="E8" s="192"/>
-      <c r="F8" s="122" t="s">
+      <c r="C8" s="188"/>
+      <c r="D8" s="188"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="123"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
       <c r="M8" s="41"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
@@ -18290,75 +18233,54 @@
       <c r="AC8" s="38"/>
     </row>
     <row r="9" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B9" s="192" t="s">
+      <c r="B9" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="192"/>
-      <c r="D9" s="192"/>
-      <c r="E9" s="192"/>
-      <c r="F9" s="122" t="s">
+      <c r="C9" s="188"/>
+      <c r="D9" s="188"/>
+      <c r="E9" s="188"/>
+      <c r="F9" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="128"/>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="128"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="AD9" s="126"/>
+      <c r="AE9" s="126"/>
+      <c r="AF9" s="126"/>
     </row>
     <row r="10" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B10" s="192" t="s">
+      <c r="B10" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="127" t="s">
+      <c r="C10" s="188"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="125" t="s">
         <v>177</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="127"/>
-      <c r="T10" s="127"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="127"/>
-      <c r="W10" s="127"/>
-      <c r="X10" s="127"/>
-      <c r="Y10" s="127"/>
-      <c r="Z10" s="127"/>
-      <c r="AA10" s="127"/>
-      <c r="AB10" s="127"/>
-      <c r="AC10" s="127"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="125"/>
+      <c r="R10" s="125"/>
+      <c r="S10" s="125"/>
+      <c r="T10" s="125"/>
+      <c r="U10" s="125"/>
+      <c r="V10" s="125"/>
+      <c r="W10" s="125"/>
+      <c r="X10" s="125"/>
+      <c r="Y10" s="125"/>
+      <c r="Z10" s="125"/>
+      <c r="AA10" s="125"/>
+      <c r="AB10" s="125"/>
+      <c r="AC10" s="125"/>
     </row>
     <row r="11" spans="2:32" s="34" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="B11" s="40"/>
@@ -18451,706 +18373,703 @@
       <c r="AC13" s="38"/>
     </row>
     <row r="14" spans="2:32" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B14" s="125" t="s">
+      <c r="B14" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="125"/>
-      <c r="R14" s="125"/>
-      <c r="S14" s="125"/>
-      <c r="T14" s="125"/>
-      <c r="U14" s="125"/>
-      <c r="V14" s="125"/>
-      <c r="W14" s="125"/>
-      <c r="X14" s="125"/>
-      <c r="Y14" s="125"/>
-      <c r="Z14" s="125"/>
-      <c r="AA14" s="125"/>
-      <c r="AB14" s="125"/>
-      <c r="AC14" s="125"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="123"/>
+      <c r="S14" s="123"/>
+      <c r="T14" s="123"/>
+      <c r="U14" s="123"/>
+      <c r="V14" s="123"/>
+      <c r="W14" s="123"/>
+      <c r="X14" s="123"/>
+      <c r="Y14" s="123"/>
+      <c r="Z14" s="123"/>
+      <c r="AA14" s="123"/>
+      <c r="AB14" s="123"/>
+      <c r="AC14" s="123"/>
     </row>
     <row r="15" spans="2:32" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B15" s="125"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
-      <c r="U15" s="125"/>
-      <c r="V15" s="125"/>
-      <c r="W15" s="125"/>
-      <c r="X15" s="125"/>
-      <c r="Y15" s="125"/>
-      <c r="Z15" s="125"/>
-      <c r="AA15" s="125"/>
-      <c r="AB15" s="125"/>
-      <c r="AC15" s="125"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="123"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="123"/>
+      <c r="U15" s="123"/>
+      <c r="V15" s="123"/>
+      <c r="W15" s="123"/>
+      <c r="X15" s="123"/>
+      <c r="Y15" s="123"/>
+      <c r="Z15" s="123"/>
+      <c r="AA15" s="123"/>
+      <c r="AB15" s="123"/>
+      <c r="AC15" s="123"/>
     </row>
     <row r="16" spans="2:32" s="34" customFormat="1" ht="70.500000" customHeight="1">
-      <c r="B16" s="126" t="s">
+      <c r="B16" s="124" t="s">
         <v>179</v>
       </c>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
-      <c r="P16" s="126"/>
-      <c r="Q16" s="126"/>
-      <c r="R16" s="126"/>
-      <c r="S16" s="126"/>
-      <c r="T16" s="126"/>
-      <c r="U16" s="126"/>
-      <c r="V16" s="126"/>
-      <c r="W16" s="126"/>
-      <c r="X16" s="126"/>
-      <c r="Y16" s="126"/>
-      <c r="Z16" s="126"/>
-      <c r="AA16" s="126"/>
-      <c r="AB16" s="126"/>
-      <c r="AC16" s="126"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="124"/>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="124"/>
+      <c r="R16" s="124"/>
+      <c r="S16" s="124"/>
+      <c r="T16" s="124"/>
+      <c r="U16" s="124"/>
+      <c r="V16" s="124"/>
+      <c r="W16" s="124"/>
+      <c r="X16" s="124"/>
+      <c r="Y16" s="124"/>
+      <c r="Z16" s="124"/>
+      <c r="AA16" s="124"/>
+      <c r="AB16" s="124"/>
+      <c r="AC16" s="124"/>
     </row>
     <row r="17" spans="2:29" s="34" customFormat="1" ht="5.000000" customHeight="1">
-      <c r="B17" s="125"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="125"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="125"/>
-      <c r="J17" s="125"/>
-      <c r="K17" s="125"/>
-      <c r="L17" s="125"/>
-      <c r="M17" s="125"/>
-      <c r="N17" s="125"/>
-      <c r="O17" s="125"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="125"/>
-      <c r="R17" s="125"/>
-      <c r="S17" s="125"/>
-      <c r="T17" s="125"/>
-      <c r="U17" s="125"/>
-      <c r="V17" s="125"/>
-      <c r="W17" s="125"/>
-      <c r="X17" s="125"/>
-      <c r="Y17" s="125"/>
-      <c r="Z17" s="125"/>
-      <c r="AA17" s="125"/>
-      <c r="AB17" s="125"/>
-      <c r="AC17" s="125"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="123"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="123"/>
+      <c r="S17" s="123"/>
+      <c r="T17" s="123"/>
+      <c r="U17" s="123"/>
+      <c r="V17" s="123"/>
+      <c r="W17" s="123"/>
+      <c r="X17" s="123"/>
+      <c r="Y17" s="123"/>
+      <c r="Z17" s="123"/>
+      <c r="AA17" s="123"/>
+      <c r="AB17" s="123"/>
+      <c r="AC17" s="123"/>
     </row>
     <row r="18" spans="2:29" s="34" customFormat="1" ht="39.000000" customHeight="1">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="126"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="126"/>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="126"/>
-      <c r="N18" s="126"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="126"/>
-      <c r="Q18" s="126"/>
-      <c r="R18" s="126"/>
-      <c r="S18" s="126"/>
-      <c r="T18" s="126"/>
-      <c r="U18" s="126"/>
-      <c r="V18" s="126"/>
-      <c r="W18" s="126"/>
-      <c r="X18" s="126"/>
-      <c r="Y18" s="126"/>
-      <c r="Z18" s="126"/>
-      <c r="AA18" s="126"/>
-      <c r="AB18" s="126"/>
-      <c r="AC18" s="126"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="124"/>
+      <c r="T18" s="124"/>
+      <c r="U18" s="124"/>
+      <c r="V18" s="124"/>
+      <c r="W18" s="124"/>
+      <c r="X18" s="124"/>
+      <c r="Y18" s="124"/>
+      <c r="Z18" s="124"/>
+      <c r="AA18" s="124"/>
+      <c r="AB18" s="124"/>
+      <c r="AC18" s="124"/>
     </row>
     <row r="19" spans="2:29" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
-      <c r="P19" s="125"/>
-      <c r="Q19" s="125"/>
-      <c r="R19" s="125"/>
-      <c r="S19" s="125"/>
-      <c r="T19" s="125"/>
-      <c r="U19" s="125"/>
-      <c r="V19" s="125"/>
-      <c r="W19" s="125"/>
-      <c r="X19" s="125"/>
-      <c r="Y19" s="125"/>
-      <c r="Z19" s="125"/>
-      <c r="AA19" s="125"/>
-      <c r="AB19" s="125"/>
-      <c r="AC19" s="125"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="123"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="123"/>
+      <c r="U19" s="123"/>
+      <c r="V19" s="123"/>
+      <c r="W19" s="123"/>
+      <c r="X19" s="123"/>
+      <c r="Y19" s="123"/>
+      <c r="Z19" s="123"/>
+      <c r="AA19" s="123"/>
+      <c r="AB19" s="123"/>
+      <c r="AC19" s="123"/>
     </row>
     <row r="20" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="123" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="125"/>
-      <c r="T20" s="125"/>
-      <c r="U20" s="125"/>
-      <c r="V20" s="125"/>
-      <c r="W20" s="125"/>
-      <c r="X20" s="125"/>
-      <c r="Y20" s="125"/>
-      <c r="Z20" s="125"/>
-      <c r="AA20" s="125"/>
-      <c r="AB20" s="125"/>
-      <c r="AC20" s="125"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="123"/>
+      <c r="W20" s="123"/>
+      <c r="X20" s="123"/>
+      <c r="Y20" s="123"/>
+      <c r="Z20" s="123"/>
+      <c r="AA20" s="123"/>
+      <c r="AB20" s="123"/>
+      <c r="AC20" s="123"/>
     </row>
     <row r="21" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B21" s="125"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="125" t="s">
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123" t="s">
         <v>145</v>
       </c>
-      <c r="G21" s="125"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="125"/>
-      <c r="L21" s="127" t="str">
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="125" t="str">
         <f>F8</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="127"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="127"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="127"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="127"/>
-      <c r="W21" s="127"/>
-      <c r="X21" s="127"/>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-      <c r="AA21" s="128"/>
-      <c r="AB21" s="128"/>
-      <c r="AC21" s="128"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="125"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="125"/>
+      <c r="T21" s="125"/>
+      <c r="U21" s="125"/>
+      <c r="V21" s="125"/>
+      <c r="W21" s="125"/>
+      <c r="X21" s="125"/>
+      <c r="Y21" s="125"/>
+      <c r="Z21" s="125"/>
+      <c r="AA21" s="126"/>
+      <c r="AB21" s="126"/>
+      <c r="AC21" s="126"/>
     </row>
     <row r="22" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125" t="s">
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123" t="s">
         <v>193</v>
       </c>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="127" t="s">
+      <c r="G22" s="123"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="M22" s="127"/>
-      <c r="N22" s="127"/>
-      <c r="O22" s="127"/>
-      <c r="P22" s="127"/>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="127"/>
-      <c r="S22" s="127"/>
-      <c r="T22" s="127"/>
-      <c r="U22" s="127"/>
-      <c r="V22" s="127"/>
-      <c r="W22" s="127"/>
-      <c r="X22" s="127"/>
-      <c r="Y22" s="127"/>
-      <c r="Z22" s="127"/>
-      <c r="AA22" s="128"/>
-      <c r="AB22" s="128"/>
-      <c r="AC22" s="128"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="125"/>
+      <c r="O22" s="125"/>
+      <c r="P22" s="125"/>
+      <c r="Q22" s="125"/>
+      <c r="R22" s="125"/>
+      <c r="S22" s="125"/>
+      <c r="T22" s="125"/>
+      <c r="U22" s="125"/>
+      <c r="V22" s="125"/>
+      <c r="W22" s="125"/>
+      <c r="X22" s="125"/>
+      <c r="Y22" s="125"/>
+      <c r="Z22" s="125"/>
+      <c r="AA22" s="126"/>
+      <c r="AB22" s="126"/>
+      <c r="AC22" s="126"/>
     </row>
     <row r="23" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125" t="s">
+      <c r="B23" s="123"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123" t="s">
         <v>194</v>
       </c>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="127" t="s">
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="127"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="34"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="125"/>
+      <c r="S23" s="125"/>
+      <c r="T23" s="125"/>
+      <c r="U23" s="125"/>
+      <c r="V23" s="125"/>
+      <c r="W23" s="125"/>
+      <c r="X23" s="125"/>
+      <c r="Y23" s="125"/>
+      <c r="Z23" s="125"/>
     </row>
     <row r="24" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B24" s="125"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125" t="s">
+      <c r="B24" s="123"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="123" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="127" t="s">
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="123"/>
+      <c r="L24" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="M24" s="127"/>
-      <c r="N24" s="127"/>
-      <c r="O24" s="127"/>
-      <c r="P24" s="127"/>
-      <c r="Q24" s="127"/>
-      <c r="R24" s="127"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-      <c r="U24" s="127"/>
-      <c r="V24" s="127"/>
-      <c r="W24" s="127"/>
-      <c r="X24" s="127"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="127"/>
-      <c r="AA24" s="128"/>
-      <c r="AB24" s="128"/>
-      <c r="AC24" s="128"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="125"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="125"/>
+      <c r="T24" s="125"/>
+      <c r="U24" s="125"/>
+      <c r="V24" s="125"/>
+      <c r="W24" s="125"/>
+      <c r="X24" s="125"/>
+      <c r="Y24" s="125"/>
+      <c r="Z24" s="125"/>
+      <c r="AA24" s="126"/>
+      <c r="AB24" s="126"/>
+      <c r="AC24" s="126"/>
     </row>
     <row r="25" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B25" s="125"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125" t="s">
+      <c r="B25" s="123"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123" t="s">
         <v>149</v>
       </c>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="128"/>
-      <c r="N25" s="128"/>
-      <c r="O25" s="128"/>
-      <c r="P25" s="128"/>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="128"/>
-      <c r="S25" s="128"/>
-      <c r="T25" s="128"/>
-      <c r="U25" s="128"/>
-      <c r="V25" s="128"/>
-      <c r="W25" s="128"/>
-      <c r="X25" s="128"/>
-      <c r="Y25" s="128"/>
-      <c r="Z25" s="128"/>
-      <c r="AA25" s="128"/>
-      <c r="AB25" s="128"/>
-      <c r="AC25" s="128"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="126"/>
+      <c r="S25" s="126"/>
+      <c r="T25" s="126"/>
+      <c r="U25" s="126"/>
+      <c r="V25" s="126"/>
+      <c r="W25" s="126"/>
+      <c r="X25" s="126"/>
+      <c r="Y25" s="126"/>
+      <c r="Z25" s="126"/>
+      <c r="AA25" s="126"/>
+      <c r="AB25" s="126"/>
+      <c r="AC25" s="126"/>
     </row>
     <row r="26" spans="2:29" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B26" s="125"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="125"/>
-      <c r="G26" s="125"/>
-      <c r="H26" s="125"/>
-      <c r="I26" s="125"/>
-      <c r="J26" s="125"/>
-      <c r="K26" s="125"/>
-      <c r="L26" s="125"/>
-      <c r="M26" s="125"/>
-      <c r="N26" s="125"/>
-      <c r="O26" s="125"/>
-      <c r="P26" s="125"/>
-      <c r="Q26" s="125"/>
-      <c r="R26" s="125"/>
-      <c r="S26" s="125"/>
-      <c r="T26" s="125"/>
-      <c r="U26" s="125"/>
-      <c r="V26" s="125"/>
-      <c r="W26" s="125"/>
-      <c r="X26" s="125"/>
-      <c r="Y26" s="125"/>
-      <c r="Z26" s="125"/>
-      <c r="AA26" s="125"/>
-      <c r="AB26" s="125"/>
-      <c r="AC26" s="125"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="123"/>
+      <c r="L26" s="123"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123"/>
+      <c r="R26" s="123"/>
+      <c r="S26" s="123"/>
+      <c r="T26" s="123"/>
+      <c r="U26" s="123"/>
+      <c r="V26" s="123"/>
+      <c r="W26" s="123"/>
+      <c r="X26" s="123"/>
+      <c r="Y26" s="123"/>
+      <c r="Z26" s="123"/>
+      <c r="AA26" s="123"/>
+      <c r="AB26" s="123"/>
+      <c r="AC26" s="123"/>
     </row>
     <row r="27" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="125"/>
-      <c r="I27" s="125"/>
-      <c r="J27" s="125"/>
-      <c r="K27" s="125"/>
-      <c r="L27" s="125"/>
-      <c r="M27" s="125"/>
-      <c r="N27" s="125"/>
-      <c r="O27" s="125"/>
-      <c r="P27" s="125"/>
-      <c r="Q27" s="125"/>
-      <c r="R27" s="125"/>
-      <c r="S27" s="125"/>
-      <c r="T27" s="125"/>
-      <c r="U27" s="125"/>
-      <c r="V27" s="125"/>
-      <c r="W27" s="125"/>
-      <c r="X27" s="125"/>
-      <c r="Y27" s="125"/>
-      <c r="Z27" s="125"/>
-      <c r="AA27" s="125"/>
-      <c r="AB27" s="125"/>
-      <c r="AC27" s="125"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="123"/>
+      <c r="K27" s="123"/>
+      <c r="L27" s="123"/>
+      <c r="M27" s="123"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="123"/>
+      <c r="P27" s="123"/>
+      <c r="Q27" s="123"/>
+      <c r="R27" s="123"/>
+      <c r="S27" s="123"/>
+      <c r="T27" s="123"/>
+      <c r="U27" s="123"/>
+      <c r="V27" s="123"/>
+      <c r="W27" s="123"/>
+      <c r="X27" s="123"/>
+      <c r="Y27" s="123"/>
+      <c r="Z27" s="123"/>
+      <c r="AA27" s="123"/>
+      <c r="AB27" s="123"/>
+      <c r="AC27" s="123"/>
     </row>
     <row r="28" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="199" t="s">
+      <c r="B28" s="123"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="195" t="s">
         <v>150</v>
       </c>
-      <c r="G28" s="199"/>
-      <c r="H28" s="199"/>
-      <c r="I28" s="199"/>
-      <c r="J28" s="199"/>
-      <c r="K28" s="199"/>
-      <c r="L28" s="199"/>
-      <c r="M28" s="199"/>
-      <c r="N28" s="199"/>
-      <c r="O28" s="199"/>
-      <c r="P28" s="199"/>
-      <c r="Q28" s="199"/>
-      <c r="R28" s="199"/>
-      <c r="S28" s="199"/>
-      <c r="T28" s="199"/>
-      <c r="U28" s="199"/>
-      <c r="V28" s="199"/>
-      <c r="W28" s="199"/>
-      <c r="X28" s="199"/>
-      <c r="Y28" s="199"/>
-      <c r="Z28" s="199"/>
-      <c r="AA28" s="199"/>
-      <c r="AB28" s="199"/>
-      <c r="AC28" s="199"/>
+      <c r="G28" s="195"/>
+      <c r="H28" s="195"/>
+      <c r="I28" s="195"/>
+      <c r="J28" s="195"/>
+      <c r="K28" s="195"/>
+      <c r="L28" s="195"/>
+      <c r="M28" s="195"/>
+      <c r="N28" s="195"/>
+      <c r="O28" s="195"/>
+      <c r="P28" s="195"/>
+      <c r="Q28" s="195"/>
+      <c r="R28" s="195"/>
+      <c r="S28" s="195"/>
+      <c r="T28" s="195"/>
+      <c r="U28" s="195"/>
+      <c r="V28" s="195"/>
+      <c r="W28" s="195"/>
+      <c r="X28" s="195"/>
+      <c r="Y28" s="195"/>
+      <c r="Z28" s="195"/>
+      <c r="AA28" s="195"/>
+      <c r="AB28" s="195"/>
+      <c r="AC28" s="195"/>
     </row>
     <row r="29" spans="2:29" s="34" customFormat="1" ht="33.000000" customHeight="1">
-      <c r="B29" s="125"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="200" t="s">
+      <c r="B29" s="123"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="196" t="s">
         <v>151</v>
       </c>
-      <c r="G29" s="200"/>
-      <c r="H29" s="200"/>
-      <c r="I29" s="200"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="200"/>
-      <c r="L29" s="200"/>
-      <c r="M29" s="200"/>
-      <c r="N29" s="200"/>
-      <c r="O29" s="200"/>
-      <c r="P29" s="200"/>
-      <c r="Q29" s="200"/>
-      <c r="R29" s="200"/>
-      <c r="S29" s="200"/>
-      <c r="T29" s="200"/>
-      <c r="U29" s="200"/>
-      <c r="V29" s="200"/>
-      <c r="W29" s="200"/>
-      <c r="X29" s="200"/>
-      <c r="Y29" s="200"/>
-      <c r="Z29" s="200"/>
-      <c r="AA29" s="200"/>
-      <c r="AB29" s="200"/>
-      <c r="AC29" s="200"/>
+      <c r="G29" s="196"/>
+      <c r="H29" s="196"/>
+      <c r="I29" s="196"/>
+      <c r="J29" s="196"/>
+      <c r="K29" s="196"/>
+      <c r="L29" s="196"/>
+      <c r="M29" s="196"/>
+      <c r="N29" s="196"/>
+      <c r="O29" s="196"/>
+      <c r="P29" s="196"/>
+      <c r="Q29" s="196"/>
+      <c r="R29" s="196"/>
+      <c r="S29" s="196"/>
+      <c r="T29" s="196"/>
+      <c r="U29" s="196"/>
+      <c r="V29" s="196"/>
+      <c r="W29" s="196"/>
+      <c r="X29" s="196"/>
+      <c r="Y29" s="196"/>
+      <c r="Z29" s="196"/>
+      <c r="AA29" s="196"/>
+      <c r="AB29" s="196"/>
+      <c r="AC29" s="196"/>
     </row>
     <row r="30" spans="2:29" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B30" s="125"/>
-      <c r="C30" s="125"/>
-      <c r="D30" s="125"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="125"/>
-      <c r="G30" s="125"/>
-      <c r="H30" s="125"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="125"/>
-      <c r="K30" s="125"/>
-      <c r="L30" s="125"/>
-      <c r="M30" s="125"/>
-      <c r="N30" s="125"/>
-      <c r="O30" s="125"/>
-      <c r="P30" s="125"/>
-      <c r="Q30" s="125"/>
-      <c r="R30" s="125"/>
-      <c r="S30" s="125"/>
-      <c r="T30" s="125"/>
-      <c r="U30" s="125"/>
-      <c r="V30" s="125"/>
-      <c r="W30" s="125"/>
-      <c r="X30" s="125"/>
-      <c r="Y30" s="125"/>
-      <c r="Z30" s="125"/>
-      <c r="AA30" s="125"/>
-      <c r="AB30" s="125"/>
-      <c r="AC30" s="125"/>
+      <c r="B30" s="123"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="123"/>
+      <c r="K30" s="123"/>
+      <c r="L30" s="123"/>
+      <c r="M30" s="123"/>
+      <c r="N30" s="123"/>
+      <c r="O30" s="123"/>
+      <c r="P30" s="123"/>
+      <c r="Q30" s="123"/>
+      <c r="R30" s="123"/>
+      <c r="S30" s="123"/>
+      <c r="T30" s="123"/>
+      <c r="U30" s="123"/>
+      <c r="V30" s="123"/>
+      <c r="W30" s="123"/>
+      <c r="X30" s="123"/>
+      <c r="Y30" s="123"/>
+      <c r="Z30" s="123"/>
+      <c r="AA30" s="123"/>
+      <c r="AB30" s="123"/>
+      <c r="AC30" s="123"/>
     </row>
     <row r="31" spans="2:29" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="196"/>
-      <c r="D31" s="196"/>
-      <c r="E31" s="196"/>
-      <c r="F31" s="196"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="196"/>
-      <c r="I31" s="196"/>
-      <c r="J31" s="196"/>
-      <c r="K31" s="196"/>
-      <c r="L31" s="201" t="str">
+      <c r="C31" s="192"/>
+      <c r="D31" s="192"/>
+      <c r="E31" s="192"/>
+      <c r="F31" s="192"/>
+      <c r="G31" s="192"/>
+      <c r="H31" s="192"/>
+      <c r="I31" s="192"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="192"/>
+      <c r="L31" s="197" t="str">
         <f>대가산출!D3</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="M31" s="201"/>
-      <c r="N31" s="201"/>
-      <c r="O31" s="201"/>
-      <c r="P31" s="201"/>
-      <c r="Q31" s="201"/>
-      <c r="R31" s="201"/>
-      <c r="S31" s="201"/>
-      <c r="T31" s="201"/>
-      <c r="U31" s="201"/>
-      <c r="V31" s="201"/>
-      <c r="W31" s="201"/>
-      <c r="X31" s="201"/>
-      <c r="Y31" s="201"/>
-      <c r="Z31" s="201"/>
-      <c r="AA31" s="201"/>
-      <c r="AB31" s="201"/>
-      <c r="AC31" s="201"/>
+      <c r="M31" s="197"/>
+      <c r="N31" s="197"/>
+      <c r="O31" s="197"/>
+      <c r="P31" s="197"/>
+      <c r="Q31" s="197"/>
+      <c r="R31" s="197"/>
+      <c r="S31" s="197"/>
+      <c r="T31" s="197"/>
+      <c r="U31" s="197"/>
+      <c r="V31" s="197"/>
+      <c r="W31" s="197"/>
+      <c r="X31" s="197"/>
+      <c r="Y31" s="197"/>
+      <c r="Z31" s="197"/>
+      <c r="AA31" s="197"/>
+      <c r="AB31" s="197"/>
+      <c r="AC31" s="197"/>
     </row>
     <row r="32" spans="2:29" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B32" s="125"/>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="125"/>
-      <c r="H32" s="125"/>
-      <c r="I32" s="125"/>
-      <c r="J32" s="125"/>
-      <c r="K32" s="125"/>
-      <c r="L32" s="125"/>
-      <c r="M32" s="125"/>
-      <c r="N32" s="125"/>
-      <c r="O32" s="125"/>
-      <c r="P32" s="125"/>
-      <c r="Q32" s="125"/>
-      <c r="R32" s="125"/>
-      <c r="S32" s="125"/>
-      <c r="T32" s="125"/>
-      <c r="U32" s="125"/>
-      <c r="V32" s="125"/>
-      <c r="W32" s="125"/>
-      <c r="X32" s="125"/>
-      <c r="Y32" s="125"/>
-      <c r="Z32" s="125"/>
-      <c r="AA32" s="125"/>
-      <c r="AB32" s="125"/>
-      <c r="AC32" s="125"/>
+      <c r="B32" s="123"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="123"/>
+      <c r="H32" s="123"/>
+      <c r="I32" s="123"/>
+      <c r="J32" s="123"/>
+      <c r="K32" s="123"/>
+      <c r="L32" s="123"/>
+      <c r="M32" s="123"/>
+      <c r="N32" s="123"/>
+      <c r="O32" s="123"/>
+      <c r="P32" s="123"/>
+      <c r="Q32" s="123"/>
+      <c r="R32" s="123"/>
+      <c r="S32" s="123"/>
+      <c r="T32" s="123"/>
+      <c r="U32" s="123"/>
+      <c r="V32" s="123"/>
+      <c r="W32" s="123"/>
+      <c r="X32" s="123"/>
+      <c r="Y32" s="123"/>
+      <c r="Z32" s="123"/>
+      <c r="AA32" s="123"/>
+      <c r="AB32" s="123"/>
+      <c r="AC32" s="123"/>
     </row>
     <row r="33" spans="2:33" s="34" customFormat="1" ht="20.000000" customHeight="1">
-      <c r="B33" s="125" t="s">
+      <c r="B33" s="123" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="125"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="125"/>
-      <c r="S33" s="125"/>
-      <c r="T33" s="125"/>
-      <c r="U33" s="125"/>
-      <c r="V33" s="125"/>
-      <c r="W33" s="125"/>
-      <c r="X33" s="125"/>
-      <c r="Y33" s="125"/>
-      <c r="Z33" s="125"/>
-      <c r="AA33" s="125"/>
-      <c r="AB33" s="125"/>
-      <c r="AC33" s="125"/>
+      <c r="C33" s="123"/>
+      <c r="D33" s="123"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="123"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="123"/>
+      <c r="K33" s="123"/>
+      <c r="L33" s="123"/>
+      <c r="M33" s="123"/>
+      <c r="N33" s="123"/>
+      <c r="O33" s="123"/>
+      <c r="P33" s="123"/>
+      <c r="Q33" s="123"/>
+      <c r="R33" s="123"/>
+      <c r="S33" s="123"/>
+      <c r="T33" s="123"/>
+      <c r="U33" s="123"/>
+      <c r="V33" s="123"/>
+      <c r="W33" s="123"/>
+      <c r="X33" s="123"/>
+      <c r="Y33" s="123"/>
+      <c r="Z33" s="123"/>
+      <c r="AA33" s="123"/>
+      <c r="AB33" s="123"/>
+      <c r="AC33" s="123"/>
     </row>
     <row r="34" spans="2:33" s="34" customFormat="1" ht="10.000000" customHeight="1">
-      <c r="B34" s="126"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
-      <c r="H34" s="126"/>
-      <c r="I34" s="126"/>
-      <c r="J34" s="126"/>
-      <c r="K34" s="126"/>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
-      <c r="N34" s="126"/>
-      <c r="O34" s="126"/>
-      <c r="P34" s="126"/>
-      <c r="Q34" s="126"/>
-      <c r="R34" s="126"/>
-      <c r="S34" s="126"/>
-      <c r="T34" s="126"/>
-      <c r="U34" s="126"/>
-      <c r="V34" s="126"/>
-      <c r="W34" s="126"/>
-      <c r="X34" s="126"/>
-      <c r="Y34" s="126"/>
-      <c r="Z34" s="126"/>
-      <c r="AA34" s="126"/>
-      <c r="AB34" s="126"/>
-      <c r="AC34" s="126"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="124"/>
+      <c r="I34" s="124"/>
+      <c r="J34" s="124"/>
+      <c r="K34" s="124"/>
+      <c r="L34" s="124"/>
+      <c r="M34" s="124"/>
+      <c r="N34" s="124"/>
+      <c r="O34" s="124"/>
+      <c r="P34" s="124"/>
+      <c r="Q34" s="124"/>
+      <c r="R34" s="124"/>
+      <c r="S34" s="124"/>
+      <c r="T34" s="124"/>
+      <c r="U34" s="124"/>
+      <c r="V34" s="124"/>
+      <c r="W34" s="124"/>
+      <c r="X34" s="124"/>
+      <c r="Y34" s="124"/>
+      <c r="Z34" s="124"/>
+      <c r="AA34" s="124"/>
+      <c r="AB34" s="124"/>
+      <c r="AC34" s="124"/>
     </row>
     <row r="35" spans="2:33" s="34" customFormat="1" ht="19.500000" customHeight="1">
-      <c r="B35" s="125" t="s">
+      <c r="B35" s="123" t="s">
         <v>168</v>
       </c>
-      <c r="C35" s="197"/>
-      <c r="D35" s="197"/>
-      <c r="E35" s="197"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="197"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="197"/>
-      <c r="M35" s="197"/>
-      <c r="N35" s="197"/>
-      <c r="O35" s="197"/>
-      <c r="P35" s="197"/>
-      <c r="Q35" s="197"/>
-      <c r="R35" s="197"/>
-      <c r="S35" s="197"/>
-      <c r="T35" s="197"/>
-      <c r="U35" s="197"/>
-      <c r="V35" s="197"/>
-      <c r="W35" s="197"/>
-      <c r="X35" s="197"/>
-      <c r="Y35" s="197"/>
-      <c r="Z35" s="197"/>
-      <c r="AA35" s="197"/>
-      <c r="AB35" s="197"/>
-      <c r="AC35" s="197"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="193"/>
+      <c r="E35" s="193"/>
+      <c r="F35" s="193"/>
+      <c r="G35" s="193"/>
+      <c r="H35" s="193"/>
+      <c r="I35" s="193"/>
+      <c r="J35" s="193"/>
+      <c r="K35" s="193"/>
+      <c r="L35" s="193"/>
+      <c r="M35" s="193"/>
+      <c r="N35" s="193"/>
+      <c r="O35" s="193"/>
+      <c r="P35" s="193"/>
+      <c r="Q35" s="193"/>
+      <c r="R35" s="193"/>
+      <c r="S35" s="193"/>
+      <c r="T35" s="193"/>
+      <c r="U35" s="193"/>
+      <c r="V35" s="193"/>
+      <c r="W35" s="193"/>
+      <c r="X35" s="193"/>
+      <c r="Y35" s="193"/>
+      <c r="Z35" s="193"/>
+      <c r="AA35" s="193"/>
+      <c r="AB35" s="193"/>
+      <c r="AC35" s="193"/>
     </row>
     <row r="36" spans="2:33" s="34" customFormat="1" ht="19.500000" customHeight="1">
       <c r="B36" s="36"/>
@@ -19168,36 +19087,36 @@
       <c r="N36" s="36"/>
     </row>
     <row r="37" spans="2:33" s="34" customFormat="1" ht="46.500000" customHeight="1">
-      <c r="B37" s="198" t="s">
+      <c r="B37" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="198"/>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="198"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="198"/>
-      <c r="M37" s="198"/>
-      <c r="N37" s="198"/>
-      <c r="O37" s="198"/>
-      <c r="P37" s="198"/>
-      <c r="Q37" s="198"/>
-      <c r="R37" s="198"/>
-      <c r="S37" s="198"/>
-      <c r="T37" s="198"/>
-      <c r="U37" s="198"/>
-      <c r="V37" s="198"/>
-      <c r="W37" s="198"/>
-      <c r="X37" s="198"/>
-      <c r="Y37" s="198"/>
-      <c r="Z37" s="198"/>
-      <c r="AA37" s="198"/>
-      <c r="AB37" s="198"/>
-      <c r="AC37" s="198"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="194"/>
+      <c r="I37" s="194"/>
+      <c r="J37" s="194"/>
+      <c r="K37" s="194"/>
+      <c r="L37" s="194"/>
+      <c r="M37" s="194"/>
+      <c r="N37" s="194"/>
+      <c r="O37" s="194"/>
+      <c r="P37" s="194"/>
+      <c r="Q37" s="194"/>
+      <c r="R37" s="194"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="194"/>
+      <c r="U37" s="194"/>
+      <c r="V37" s="194"/>
+      <c r="W37" s="194"/>
+      <c r="X37" s="194"/>
+      <c r="Y37" s="194"/>
+      <c r="Z37" s="194"/>
+      <c r="AA37" s="194"/>
+      <c r="AB37" s="194"/>
+      <c r="AC37" s="194"/>
       <c r="AG37" s="35"/>
     </row>
     <row r="38" spans="2:33">
@@ -36299,8 +36218,8 @@
     <mergeCell ref="B18:AC18"/>
     <mergeCell ref="B20:K20"/>
     <mergeCell ref="F21:K21"/>
+    <mergeCell ref="F22:K22"/>
     <mergeCell ref="F23:K23"/>
-    <mergeCell ref="F22:K22"/>
     <mergeCell ref="F24:K24"/>
     <mergeCell ref="F25:K25"/>
     <mergeCell ref="B27:K27"/>
@@ -36337,16 +36256,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="1" customFormat="1" ht="39.000000" customHeight="1">
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="198" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="2" spans="2:9" s="1" customFormat="1" ht="18.000000" customHeight="1">
       <c r="B2" s="51"/>
@@ -36355,71 +36274,71 @@
       <c r="E2" s="51"/>
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
     </row>
     <row r="3" spans="2:9" s="52" customFormat="1" ht="34.500000" customHeight="1">
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="205"/>
-      <c r="D3" s="206" t="str">
+      <c r="C3" s="201"/>
+      <c r="D3" s="202" t="str">
         <f>"일금"&amp;NUMBERSTRING(H29,1)&amp;"원정 ("&amp;DOLLAR(H29,0)&amp;")-VAT별도"</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="208"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="203"/>
+      <c r="I3" s="204"/>
     </row>
     <row r="4" spans="2:9" s="52" customFormat="1" ht="38.250000" hidden="1" customHeight="1">
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="205" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="210"/>
-      <c r="D4" s="211" t="str">
+      <c r="C4" s="206"/>
+      <c r="D4" s="207" t="str">
         <f>"일금 "&amp;NUMBERSTRING(H29,1)&amp;"원정"&amp;TEXT(H29,"(￦ #,##0)")&amp;" "</f>
         <v xml:space="preserve">일금 일백팔십만원정(₩ 1,800,000) </v>
       </c>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="213"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="209"/>
     </row>
     <row r="5" spans="2:9" s="52" customFormat="1" ht="38.250000" hidden="1" customHeight="1">
-      <c r="B5" s="218" t="s">
+      <c r="B5" s="214" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="219"/>
-      <c r="D5" s="220" t="e">
+      <c r="C5" s="215"/>
+      <c r="D5" s="216">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
-      <c r="E5" s="221"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="221"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="222"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="218"/>
     </row>
     <row r="6" spans="2:9" s="52" customFormat="1" ht="31.500000" customHeight="1">
-      <c r="B6" s="223" t="s">
+      <c r="B6" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="224"/>
-      <c r="D6" s="224"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="224"/>
-      <c r="H6" s="224"/>
-      <c r="I6" s="225"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="220"/>
+      <c r="F6" s="220"/>
+      <c r="G6" s="220"/>
+      <c r="H6" s="220"/>
+      <c r="I6" s="221"/>
     </row>
     <row r="7" spans="2:9" s="53" customFormat="1" ht="30.000000" customHeight="1">
-      <c r="B7" s="226" t="s">
+      <c r="B7" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="227"/>
+      <c r="C7" s="223"/>
       <c r="D7" s="49" t="s">
         <v>67</v>
       </c>
@@ -36440,10 +36359,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B8" s="228" t="s">
+      <c r="B8" s="224" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="229"/>
+      <c r="C8" s="225"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -36629,10 +36548,10 @@
       <c r="I16" s="58"/>
     </row>
     <row r="17" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B17" s="230" t="s">
+      <c r="B17" s="226" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="231"/>
+      <c r="C17" s="227"/>
       <c r="D17" s="65"/>
       <c r="E17" s="67" t="s">
         <v>79</v>
@@ -36650,10 +36569,10 @@
       </c>
     </row>
     <row r="18" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="231"/>
+      <c r="C18" s="227"/>
       <c r="D18" s="65"/>
       <c r="E18" s="67" t="s">
         <v>79</v>
@@ -36671,10 +36590,10 @@
       </c>
     </row>
     <row r="19" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B19" s="230" t="s">
+      <c r="B19" s="226" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="231"/>
+      <c r="C19" s="227"/>
       <c r="D19" s="69"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -36712,7 +36631,7 @@
       <c r="G21" s="79">
         <v>20000</v>
       </c>
-      <c r="H21" s="121">
+      <c r="H21" s="119">
         <f>G21*F21</f>
         <v>40000</v>
       </c>
@@ -36804,10 +36723,10 @@
       <c r="I25" s="58"/>
     </row>
     <row r="26" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B26" s="232" t="s">
+      <c r="B26" s="228" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="233"/>
+      <c r="C26" s="229"/>
       <c r="D26" s="65"/>
       <c r="E26" s="67"/>
       <c r="F26" s="67"/>
@@ -36821,14 +36740,14 @@
       </c>
     </row>
     <row r="27" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B27" s="234" t="s">
+      <c r="B27" s="230" t="s">
         <v>170</v>
       </c>
-      <c r="C27" s="235"/>
-      <c r="D27" s="216" t="s">
+      <c r="C27" s="231"/>
+      <c r="D27" s="212" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="217"/>
+      <c r="E27" s="213"/>
       <c r="F27" s="112"/>
       <c r="G27" s="112"/>
       <c r="H27" s="97">
@@ -36838,12 +36757,12 @@
       <c r="I27" s="98"/>
     </row>
     <row r="28" spans="2:13" s="53" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B28" s="214" t="s">
+      <c r="B28" s="210" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="215"/>
-      <c r="D28" s="216"/>
-      <c r="E28" s="217"/>
+      <c r="C28" s="211"/>
+      <c r="D28" s="212"/>
+      <c r="E28" s="213"/>
       <c r="F28" s="112"/>
       <c r="G28" s="112"/>
       <c r="H28" s="97">
@@ -36852,12 +36771,12 @@
       <c r="I28" s="99"/>
     </row>
     <row r="29" spans="2:13" s="53" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B29" s="236" t="s">
+      <c r="B29" s="232" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="D29" s="238"/>
-      <c r="E29" s="239"/>
+      <c r="C29" s="233"/>
+      <c r="D29" s="234"/>
+      <c r="E29" s="235"/>
       <c r="F29" s="113"/>
       <c r="G29" s="113"/>
       <c r="H29" s="100">
@@ -36867,12 +36786,12 @@
       <c r="I29" s="101"/>
     </row>
     <row r="30" spans="2:13" s="53" customFormat="1" ht="18.000000" customHeight="1">
-      <c r="B30" s="214" t="s">
+      <c r="B30" s="210" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="215"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="217"/>
+      <c r="C30" s="211"/>
+      <c r="D30" s="212"/>
+      <c r="E30" s="213"/>
       <c r="F30" s="112"/>
       <c r="G30" s="112"/>
       <c r="H30" s="102" t="s">
@@ -36881,13 +36800,13 @@
       <c r="I30" s="99"/>
     </row>
     <row r="31" spans="2:13" s="53" customFormat="1" ht="28.000000" customHeight="1">
-      <c r="B31" s="240" t="s">
+      <c r="B31" s="236" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="241"/>
-      <c r="D31" s="242"/>
-      <c r="E31" s="243"/>
-      <c r="F31" s="244"/>
+      <c r="C31" s="237"/>
+      <c r="D31" s="238"/>
+      <c r="E31" s="239"/>
+      <c r="F31" s="240"/>
       <c r="G31" s="114"/>
       <c r="H31" s="103">
         <f>H29</f>
@@ -36898,69 +36817,69 @@
       </c>
     </row>
     <row r="32" spans="2:13" s="106" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B32" s="245"/>
-      <c r="C32" s="246"/>
-      <c r="D32" s="251" t="s">
+      <c r="B32" s="241"/>
+      <c r="C32" s="242"/>
+      <c r="D32" s="247" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="251"/>
-      <c r="F32" s="251"/>
-      <c r="G32" s="251"/>
-      <c r="H32" s="251"/>
+      <c r="E32" s="247"/>
+      <c r="F32" s="247"/>
+      <c r="G32" s="247"/>
+      <c r="H32" s="247"/>
       <c r="I32" s="105"/>
     </row>
     <row r="33" spans="2:9" s="106" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B33" s="247"/>
-      <c r="C33" s="248"/>
-      <c r="D33" s="252" t="s">
+      <c r="B33" s="243"/>
+      <c r="C33" s="244"/>
+      <c r="D33" s="248" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
       <c r="I33" s="107" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:9" s="106" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B34" s="247"/>
-      <c r="C34" s="248"/>
-      <c r="D34" s="253" t="s">
+      <c r="B34" s="243"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="249" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="253"/>
-      <c r="F34" s="253"/>
-      <c r="G34" s="253"/>
-      <c r="H34" s="253"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="249"/>
+      <c r="G34" s="249"/>
+      <c r="H34" s="249"/>
       <c r="I34" s="107" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:9" s="106" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B35" s="247"/>
-      <c r="C35" s="248"/>
-      <c r="D35" s="252" t="s">
+      <c r="B35" s="243"/>
+      <c r="C35" s="244"/>
+      <c r="D35" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="252"/>
-      <c r="F35" s="252"/>
-      <c r="G35" s="252"/>
-      <c r="H35" s="252"/>
+      <c r="E35" s="248"/>
+      <c r="F35" s="248"/>
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
       <c r="I35" s="107" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="2:9" s="106" customFormat="1" ht="23.000000" customHeight="1">
-      <c r="B36" s="249"/>
-      <c r="C36" s="250"/>
-      <c r="D36" s="254" t="s">
+      <c r="B36" s="245"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="250" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="254"/>
-      <c r="F36" s="254"/>
-      <c r="G36" s="254"/>
-      <c r="H36" s="254"/>
+      <c r="E36" s="250"/>
+      <c r="F36" s="250"/>
+      <c r="G36" s="250"/>
+      <c r="H36" s="250"/>
       <c r="I36" s="108" t="s">
         <v>9</v>
       </c>
@@ -37493,99 +37412,99 @@
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138"/>
+      <c r="T7" s="138"/>
+      <c r="U7" s="138"/>
     </row>
     <row r="8" spans="2:21" ht="66.000000" customHeight="1">
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="139" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="141"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="141"/>
-      <c r="P8" s="141"/>
-      <c r="Q8" s="141"/>
-      <c r="R8" s="141"/>
-      <c r="S8" s="141"/>
-      <c r="T8" s="141"/>
-      <c r="U8" s="141"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="139"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
+      <c r="T8" s="139"/>
+      <c r="U8" s="139"/>
     </row>
     <row r="9" spans="2:21" ht="44.000000" customHeight="1">
-      <c r="B9" s="142" t="str">
+      <c r="B9" s="140" t="str">
         <f>갑지!L21</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="142"/>
-      <c r="E9" s="142"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="142"/>
-      <c r="I9" s="142"/>
-      <c r="J9" s="142"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="142"/>
-      <c r="Q9" s="142"/>
-      <c r="R9" s="142"/>
-      <c r="S9" s="142"/>
-      <c r="T9" s="142"/>
-      <c r="U9" s="142"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="140"/>
+      <c r="O9" s="140"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="140"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="140"/>
+      <c r="T9" s="140"/>
+      <c r="U9" s="140"/>
     </row>
     <row r="10" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B10" s="143"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="144"/>
-      <c r="L10" s="144"/>
-      <c r="M10" s="144"/>
-      <c r="N10" s="144"/>
-      <c r="O10" s="144"/>
-      <c r="P10" s="144"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="144"/>
-      <c r="U10" s="144"/>
+      <c r="B10" s="141"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="142"/>
+      <c r="U10" s="142"/>
     </row>
     <row r="11" spans="2:21" ht="40.000000" customHeight="1">
       <c r="B11" s="18"/>
@@ -37608,29 +37527,29 @@
       <c r="C15" s="18"/>
     </row>
     <row r="16" spans="2:21" ht="22.500000">
-      <c r="B16" s="145">
+      <c r="B16" s="143">
         <f>갑지!F7</f>
         <v>46072</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="145"/>
-      <c r="H16" s="145"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="145"/>
-      <c r="K16" s="145"/>
-      <c r="L16" s="145"/>
-      <c r="M16" s="145"/>
-      <c r="N16" s="145"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="145"/>
-      <c r="Q16" s="145"/>
-      <c r="R16" s="145"/>
-      <c r="S16" s="145"/>
-      <c r="T16" s="145"/>
-      <c r="U16" s="145"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="143"/>
     </row>
     <row r="17" spans="2:21" ht="40.000000" customHeight="1">
       <c r="B17" s="18"/>
@@ -37653,45 +37572,45 @@
       <c r="C21" s="18"/>
     </row>
     <row r="22" spans="2:21" ht="4.000000" customHeight="1">
-      <c r="B22" s="150" t="s">
+      <c r="B22" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="150"/>
-      <c r="O22" s="150"/>
-      <c r="P22" s="150"/>
-      <c r="Q22" s="150"/>
-      <c r="R22" s="150"/>
-      <c r="S22" s="150"/>
-      <c r="T22" s="150"/>
-      <c r="U22" s="150"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="148"/>
+      <c r="L22" s="148"/>
+      <c r="M22" s="148"/>
+      <c r="N22" s="148"/>
+      <c r="O22" s="148"/>
+      <c r="P22" s="148"/>
+      <c r="Q22" s="148"/>
+      <c r="R22" s="148"/>
+      <c r="S22" s="148"/>
+      <c r="T22" s="148"/>
+      <c r="U22" s="148"/>
     </row>
     <row r="23" spans="2:21" ht="53.250000" customHeight="1">
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
-      <c r="I23" s="149" t="s">
+      <c r="I23" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="149"/>
-      <c r="K23" s="149"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="149"/>
-      <c r="N23" s="149"/>
-      <c r="O23" s="149"/>
-      <c r="P23" s="149"/>
-      <c r="Q23" s="149"/>
-      <c r="R23" s="149"/>
-      <c r="S23" s="149"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="147"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="147"/>
+      <c r="P23" s="147"/>
+      <c r="Q23" s="147"/>
+      <c r="R23" s="147"/>
+      <c r="S23" s="147"/>
       <c r="T23" s="48"/>
       <c r="U23" s="48"/>
     </row>
@@ -37770,429 +37689,429 @@
       <c r="U27" s="21"/>
     </row>
     <row r="28" spans="2:21" ht="43.500000" customHeight="1">
-      <c r="B28" s="146" t="s">
+      <c r="B28" s="144" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="147"/>
-      <c r="F28" s="147"/>
-      <c r="G28" s="147"/>
-      <c r="H28" s="147"/>
-      <c r="I28" s="147"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="147"/>
-      <c r="M28" s="147"/>
-      <c r="N28" s="147"/>
-      <c r="O28" s="147"/>
-      <c r="P28" s="147"/>
-      <c r="Q28" s="147"/>
-      <c r="R28" s="147"/>
-      <c r="S28" s="147"/>
-      <c r="T28" s="147"/>
-      <c r="U28" s="148"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="145"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="145"/>
+      <c r="R28" s="145"/>
+      <c r="S28" s="145"/>
+      <c r="T28" s="145"/>
+      <c r="U28" s="146"/>
     </row>
     <row r="29" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B29" s="129" t="s">
+      <c r="B29" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="130"/>
-      <c r="D29" s="133" t="s">
+      <c r="C29" s="128"/>
+      <c r="D29" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="134" t="str">
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="132" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="H29" s="134"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="134"/>
-      <c r="N29" s="134"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="134"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="134"/>
-      <c r="S29" s="134"/>
-      <c r="T29" s="134"/>
-      <c r="U29" s="135"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="132"/>
+      <c r="M29" s="132"/>
+      <c r="N29" s="132"/>
+      <c r="O29" s="132"/>
+      <c r="P29" s="132"/>
+      <c r="Q29" s="132"/>
+      <c r="R29" s="132"/>
+      <c r="S29" s="132"/>
+      <c r="T29" s="132"/>
+      <c r="U29" s="133"/>
     </row>
     <row r="30" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B30" s="131"/>
-      <c r="C30" s="132"/>
-      <c r="D30" s="136" t="s">
+      <c r="B30" s="129"/>
+      <c r="C30" s="130"/>
+      <c r="D30" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="136"/>
-      <c r="F30" s="136"/>
-      <c r="G30" s="137" t="s">
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="137"/>
-      <c r="Q30" s="137"/>
-      <c r="R30" s="137"/>
-      <c r="S30" s="137"/>
-      <c r="T30" s="137"/>
-      <c r="U30" s="138"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+      <c r="N30" s="135"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="135"/>
+      <c r="Q30" s="135"/>
+      <c r="R30" s="135"/>
+      <c r="S30" s="135"/>
+      <c r="T30" s="135"/>
+      <c r="U30" s="136"/>
     </row>
     <row r="31" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B31" s="131"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="137" t="s">
+      <c r="B31" s="129"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="135" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="137"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="137"/>
-      <c r="Q31" s="137"/>
-      <c r="R31" s="137"/>
-      <c r="S31" s="137"/>
-      <c r="T31" s="137"/>
-      <c r="U31" s="138"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="135"/>
+      <c r="N31" s="135"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="135"/>
+      <c r="Q31" s="135"/>
+      <c r="R31" s="135"/>
+      <c r="S31" s="135"/>
+      <c r="T31" s="135"/>
+      <c r="U31" s="136"/>
     </row>
     <row r="32" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B32" s="131"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="137" t="s">
+      <c r="B32" s="129"/>
+      <c r="C32" s="130"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="135" t="s">
         <v>165</v>
       </c>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="137"/>
-      <c r="K32" s="137"/>
-      <c r="L32" s="137"/>
-      <c r="M32" s="137"/>
-      <c r="N32" s="137"/>
-      <c r="O32" s="137"/>
-      <c r="P32" s="137"/>
-      <c r="Q32" s="137"/>
-      <c r="R32" s="137"/>
-      <c r="S32" s="137"/>
-      <c r="T32" s="137"/>
-      <c r="U32" s="138"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="135"/>
+      <c r="K32" s="135"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="135"/>
+      <c r="N32" s="135"/>
+      <c r="O32" s="135"/>
+      <c r="P32" s="135"/>
+      <c r="Q32" s="135"/>
+      <c r="R32" s="135"/>
+      <c r="S32" s="135"/>
+      <c r="T32" s="135"/>
+      <c r="U32" s="136"/>
     </row>
     <row r="33" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B33" s="131"/>
-      <c r="C33" s="132"/>
-      <c r="D33" s="136"/>
-      <c r="E33" s="136"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="137" t="s">
+      <c r="B33" s="129"/>
+      <c r="C33" s="130"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137"/>
-      <c r="M33" s="137"/>
-      <c r="N33" s="137"/>
-      <c r="O33" s="137"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="137"/>
-      <c r="R33" s="137"/>
-      <c r="S33" s="137"/>
-      <c r="T33" s="137"/>
-      <c r="U33" s="138"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="135"/>
+      <c r="K33" s="135"/>
+      <c r="L33" s="135"/>
+      <c r="M33" s="135"/>
+      <c r="N33" s="135"/>
+      <c r="O33" s="135"/>
+      <c r="P33" s="135"/>
+      <c r="Q33" s="135"/>
+      <c r="R33" s="135"/>
+      <c r="S33" s="135"/>
+      <c r="T33" s="135"/>
+      <c r="U33" s="136"/>
     </row>
     <row r="34" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B34" s="131"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="164" t="s">
+      <c r="B34" s="129"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="134"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="162" t="s">
         <v>167</v>
       </c>
-      <c r="H34" s="164"/>
-      <c r="I34" s="164"/>
-      <c r="J34" s="164"/>
-      <c r="K34" s="164"/>
-      <c r="L34" s="164"/>
-      <c r="M34" s="164"/>
-      <c r="N34" s="164"/>
-      <c r="O34" s="164"/>
-      <c r="P34" s="164"/>
-      <c r="Q34" s="164"/>
-      <c r="R34" s="164"/>
-      <c r="S34" s="164"/>
-      <c r="T34" s="164"/>
-      <c r="U34" s="165"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="162"/>
+      <c r="N34" s="162"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="162"/>
+      <c r="Q34" s="162"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="162"/>
+      <c r="T34" s="162"/>
+      <c r="U34" s="163"/>
     </row>
     <row r="35" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B35" s="131" t="s">
+      <c r="B35" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="136" t="s">
+      <c r="C35" s="130"/>
+      <c r="D35" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="136"/>
-      <c r="F35" s="136"/>
-      <c r="G35" s="155" t="str">
+      <c r="E35" s="134"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="153" t="str">
         <f>G29&amp;" 감리 용역"</f>
         <v>효성뉴서울5차아파트 감리 용역</v>
       </c>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="156"/>
-      <c r="K35" s="156"/>
-      <c r="L35" s="156"/>
-      <c r="M35" s="156"/>
-      <c r="N35" s="156"/>
-      <c r="O35" s="156"/>
-      <c r="P35" s="156"/>
-      <c r="Q35" s="156"/>
-      <c r="R35" s="156"/>
-      <c r="S35" s="156"/>
-      <c r="T35" s="156"/>
-      <c r="U35" s="157"/>
+      <c r="H35" s="154"/>
+      <c r="I35" s="154"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="154"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="154"/>
+      <c r="N35" s="154"/>
+      <c r="O35" s="154"/>
+      <c r="P35" s="154"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="154"/>
+      <c r="S35" s="154"/>
+      <c r="T35" s="154"/>
+      <c r="U35" s="155"/>
     </row>
     <row r="36" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B36" s="131"/>
-      <c r="C36" s="132"/>
-      <c r="D36" s="136" t="s">
+      <c r="B36" s="129"/>
+      <c r="C36" s="130"/>
+      <c r="D36" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="171" t="str">
+      <c r="E36" s="134"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="169" t="str">
         <f>갑지!L31</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="H36" s="171"/>
-      <c r="I36" s="171"/>
-      <c r="J36" s="171"/>
-      <c r="K36" s="171"/>
-      <c r="L36" s="171"/>
-      <c r="M36" s="171"/>
-      <c r="N36" s="171"/>
-      <c r="O36" s="171"/>
-      <c r="P36" s="171"/>
-      <c r="Q36" s="171"/>
-      <c r="R36" s="171"/>
-      <c r="S36" s="171"/>
-      <c r="T36" s="171"/>
-      <c r="U36" s="172"/>
+      <c r="H36" s="169"/>
+      <c r="I36" s="169"/>
+      <c r="J36" s="169"/>
+      <c r="K36" s="169"/>
+      <c r="L36" s="169"/>
+      <c r="M36" s="169"/>
+      <c r="N36" s="169"/>
+      <c r="O36" s="169"/>
+      <c r="P36" s="169"/>
+      <c r="Q36" s="169"/>
+      <c r="R36" s="169"/>
+      <c r="S36" s="169"/>
+      <c r="T36" s="169"/>
+      <c r="U36" s="170"/>
     </row>
     <row r="37" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B37" s="131"/>
-      <c r="C37" s="132"/>
-      <c r="D37" s="136" t="s">
+      <c r="B37" s="129"/>
+      <c r="C37" s="130"/>
+      <c r="D37" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="173" t="str">
+      <c r="E37" s="134"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="171" t="str">
         <f>갑지!L31</f>
         <v>일금일백팔십만원정 (₩1,800,000)-VAT별도</v>
       </c>
-      <c r="H37" s="173"/>
-      <c r="I37" s="173"/>
-      <c r="J37" s="173"/>
-      <c r="K37" s="173"/>
-      <c r="L37" s="173"/>
-      <c r="M37" s="173"/>
-      <c r="N37" s="173"/>
-      <c r="O37" s="173"/>
-      <c r="P37" s="173"/>
-      <c r="Q37" s="173"/>
-      <c r="R37" s="173"/>
-      <c r="S37" s="173"/>
-      <c r="T37" s="173"/>
-      <c r="U37" s="174"/>
+      <c r="H37" s="171"/>
+      <c r="I37" s="171"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="171"/>
+      <c r="L37" s="171"/>
+      <c r="M37" s="171"/>
+      <c r="N37" s="171"/>
+      <c r="O37" s="171"/>
+      <c r="P37" s="171"/>
+      <c r="Q37" s="171"/>
+      <c r="R37" s="171"/>
+      <c r="S37" s="171"/>
+      <c r="T37" s="171"/>
+      <c r="U37" s="172"/>
     </row>
     <row r="38" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B38" s="131"/>
-      <c r="C38" s="132"/>
-      <c r="D38" s="136" t="s">
+      <c r="B38" s="129"/>
+      <c r="C38" s="130"/>
+      <c r="D38" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="158" t="s">
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="158"/>
-      <c r="I38" s="158"/>
-      <c r="J38" s="158"/>
-      <c r="K38" s="158"/>
-      <c r="L38" s="158"/>
-      <c r="M38" s="158"/>
-      <c r="N38" s="158"/>
-      <c r="O38" s="158"/>
-      <c r="P38" s="158"/>
-      <c r="Q38" s="158"/>
-      <c r="R38" s="158"/>
-      <c r="S38" s="158"/>
-      <c r="T38" s="158"/>
-      <c r="U38" s="159"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="156"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="156"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="156"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="156"/>
+      <c r="P38" s="156"/>
+      <c r="Q38" s="156"/>
+      <c r="R38" s="156"/>
+      <c r="S38" s="156"/>
+      <c r="T38" s="156"/>
+      <c r="U38" s="157"/>
     </row>
     <row r="39" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B39" s="131"/>
-      <c r="C39" s="132"/>
-      <c r="D39" s="136" t="s">
+      <c r="B39" s="129"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="136"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="158" t="s">
+      <c r="E39" s="134"/>
+      <c r="F39" s="134"/>
+      <c r="G39" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="158"/>
-      <c r="I39" s="158"/>
-      <c r="J39" s="158"/>
-      <c r="K39" s="158"/>
-      <c r="L39" s="158"/>
-      <c r="M39" s="158"/>
-      <c r="N39" s="158"/>
-      <c r="O39" s="158"/>
-      <c r="P39" s="158"/>
-      <c r="Q39" s="158"/>
-      <c r="R39" s="158"/>
-      <c r="S39" s="158"/>
-      <c r="T39" s="158"/>
-      <c r="U39" s="159"/>
+      <c r="H39" s="156"/>
+      <c r="I39" s="156"/>
+      <c r="J39" s="156"/>
+      <c r="K39" s="156"/>
+      <c r="L39" s="156"/>
+      <c r="M39" s="156"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="156"/>
+      <c r="P39" s="156"/>
+      <c r="Q39" s="156"/>
+      <c r="R39" s="156"/>
+      <c r="S39" s="156"/>
+      <c r="T39" s="156"/>
+      <c r="U39" s="157"/>
     </row>
     <row r="40" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B40" s="131"/>
-      <c r="C40" s="132"/>
-      <c r="D40" s="136" t="s">
+      <c r="B40" s="129"/>
+      <c r="C40" s="130"/>
+      <c r="D40" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="136"/>
-      <c r="F40" s="136"/>
-      <c r="G40" s="158" t="str">
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="156" t="str">
         <f>갑지!L22</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="H40" s="158"/>
-      <c r="I40" s="158"/>
-      <c r="J40" s="158"/>
-      <c r="K40" s="158"/>
-      <c r="L40" s="158"/>
-      <c r="M40" s="158"/>
-      <c r="N40" s="158"/>
-      <c r="O40" s="158"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
-      <c r="R40" s="158"/>
-      <c r="S40" s="158"/>
-      <c r="T40" s="158"/>
-      <c r="U40" s="159"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="156"/>
+      <c r="M40" s="156"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="156"/>
+      <c r="P40" s="156"/>
+      <c r="Q40" s="156"/>
+      <c r="R40" s="156"/>
+      <c r="S40" s="156"/>
+      <c r="T40" s="156"/>
+      <c r="U40" s="157"/>
     </row>
     <row r="41" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B41" s="131"/>
-      <c r="C41" s="132"/>
-      <c r="D41" s="136"/>
-      <c r="E41" s="136"/>
-      <c r="F41" s="136"/>
-      <c r="G41" s="185" t="s">
+      <c r="B41" s="129"/>
+      <c r="C41" s="130"/>
+      <c r="D41" s="134"/>
+      <c r="E41" s="134"/>
+      <c r="F41" s="134"/>
+      <c r="G41" s="183" t="s">
         <v>156</v>
       </c>
-      <c r="H41" s="124"/>
-      <c r="I41" s="124"/>
-      <c r="J41" s="124"/>
-      <c r="K41" s="124"/>
-      <c r="L41" s="124"/>
-      <c r="M41" s="124"/>
-      <c r="N41" s="124" t="s">
+      <c r="H41" s="122"/>
+      <c r="I41" s="122"/>
+      <c r="J41" s="122"/>
+      <c r="K41" s="122"/>
+      <c r="L41" s="122"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="122" t="s">
         <v>157</v>
       </c>
-      <c r="O41" s="124" t="s">
+      <c r="O41" s="122" t="s">
         <v>158</v>
       </c>
-      <c r="P41" s="124"/>
-      <c r="Q41" s="124"/>
-      <c r="R41" s="124"/>
-      <c r="S41" s="124"/>
-      <c r="T41" s="124"/>
-      <c r="U41" s="152"/>
+      <c r="P41" s="122"/>
+      <c r="Q41" s="122"/>
+      <c r="R41" s="122"/>
+      <c r="S41" s="122"/>
+      <c r="T41" s="122"/>
+      <c r="U41" s="150"/>
     </row>
     <row r="42" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B42" s="167"/>
-      <c r="C42" s="168"/>
-      <c r="D42" s="175" t="s">
+      <c r="B42" s="165"/>
+      <c r="C42" s="166"/>
+      <c r="D42" s="173" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="176"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="178"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
-      <c r="L42" s="179"/>
-      <c r="M42" s="179"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="179"/>
-      <c r="P42" s="179"/>
-      <c r="Q42" s="179"/>
-      <c r="R42" s="179"/>
-      <c r="S42" s="179"/>
-      <c r="T42" s="179"/>
-      <c r="U42" s="180"/>
+      <c r="E42" s="174"/>
+      <c r="F42" s="175"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="177"/>
+      <c r="I42" s="177"/>
+      <c r="J42" s="177"/>
+      <c r="K42" s="177"/>
+      <c r="L42" s="177"/>
+      <c r="M42" s="177"/>
+      <c r="N42" s="177"/>
+      <c r="O42" s="177"/>
+      <c r="P42" s="177"/>
+      <c r="Q42" s="177"/>
+      <c r="R42" s="177"/>
+      <c r="S42" s="177"/>
+      <c r="T42" s="177"/>
+      <c r="U42" s="178"/>
     </row>
     <row r="43" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B43" s="169"/>
-      <c r="C43" s="170"/>
-      <c r="D43" s="166" t="s">
+      <c r="B43" s="167"/>
+      <c r="C43" s="168"/>
+      <c r="D43" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="166"/>
-      <c r="F43" s="166"/>
-      <c r="G43" s="181" t="s">
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="179" t="s">
         <v>140</v>
       </c>
-      <c r="H43" s="181"/>
-      <c r="I43" s="181"/>
-      <c r="J43" s="181"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="O43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="181"/>
-      <c r="T43" s="181"/>
-      <c r="U43" s="182"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
+      <c r="J43" s="179"/>
+      <c r="K43" s="179"/>
+      <c r="L43" s="179"/>
+      <c r="M43" s="179"/>
+      <c r="N43" s="179"/>
+      <c r="O43" s="179"/>
+      <c r="P43" s="179"/>
+      <c r="Q43" s="179"/>
+      <c r="R43" s="179"/>
+      <c r="S43" s="179"/>
+      <c r="T43" s="179"/>
+      <c r="U43" s="180"/>
     </row>
     <row r="44" spans="2:21">
-      <c r="B44" s="183"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="184"/>
-      <c r="E44" s="184"/>
+      <c r="B44" s="181"/>
+      <c r="C44" s="182"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="182"/>
       <c r="U44" s="2"/>
     </row>
     <row r="45" spans="2:21" ht="67.500000" customHeight="1">
-      <c r="B45" s="161" t="s">
+      <c r="B45" s="159" t="s">
         <v>25</v>
       </c>
       <c r="C45" s="20"/>
@@ -38213,7 +38132,7 @@
       <c r="R45" s="20"/>
       <c r="S45" s="20"/>
       <c r="T45" s="20"/>
-      <c r="U45" s="160"/>
+      <c r="U45" s="158"/>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="22"/>
@@ -38223,7 +38142,7 @@
       <c r="U46" s="2"/>
     </row>
     <row r="47" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B47" s="151" t="s">
+      <c r="B47" s="149" t="s">
         <v>26</v>
       </c>
       <c r="C47" s="21"/>
@@ -38246,7 +38165,7 @@
       <c r="R47" s="20"/>
       <c r="S47" s="20"/>
       <c r="T47" s="20"/>
-      <c r="U47" s="160"/>
+      <c r="U47" s="158"/>
     </row>
     <row r="48" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B48" s="24"/>
@@ -38268,7 +38187,7 @@
       <c r="R48" s="20"/>
       <c r="S48" s="20"/>
       <c r="T48" s="20"/>
-      <c r="U48" s="160"/>
+      <c r="U48" s="158"/>
     </row>
     <row r="49" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B49" s="24"/>
@@ -38290,206 +38209,206 @@
       <c r="R49" s="20"/>
       <c r="S49" s="20"/>
       <c r="T49" s="20"/>
-      <c r="U49" s="160"/>
+      <c r="U49" s="158"/>
     </row>
     <row r="50" spans="2:21">
-      <c r="B50" s="183"/>
-      <c r="C50" s="184"/>
-      <c r="D50" s="184"/>
-      <c r="E50" s="184"/>
+      <c r="B50" s="181"/>
+      <c r="C50" s="182"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="182"/>
       <c r="U50" s="2"/>
     </row>
     <row r="51" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B51" s="161" t="s">
+      <c r="B51" s="159" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="153" t="s">
+      <c r="E51" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="F51" s="153"/>
-      <c r="G51" s="153"/>
-      <c r="H51" s="153"/>
-      <c r="I51" s="153"/>
-      <c r="J51" s="153"/>
-      <c r="K51" s="153"/>
-      <c r="L51" s="153"/>
-      <c r="M51" s="153"/>
-      <c r="N51" s="153"/>
-      <c r="O51" s="153"/>
-      <c r="P51" s="153"/>
-      <c r="Q51" s="153"/>
-      <c r="R51" s="153"/>
-      <c r="S51" s="153"/>
-      <c r="T51" s="153"/>
-      <c r="U51" s="154"/>
+      <c r="F51" s="151"/>
+      <c r="G51" s="151"/>
+      <c r="H51" s="151"/>
+      <c r="I51" s="151"/>
+      <c r="J51" s="151"/>
+      <c r="K51" s="151"/>
+      <c r="L51" s="151"/>
+      <c r="M51" s="151"/>
+      <c r="N51" s="151"/>
+      <c r="O51" s="151"/>
+      <c r="P51" s="151"/>
+      <c r="Q51" s="151"/>
+      <c r="R51" s="151"/>
+      <c r="S51" s="151"/>
+      <c r="T51" s="151"/>
+      <c r="U51" s="152"/>
     </row>
     <row r="52" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B52" s="255" t="s">
+      <c r="B52" s="251" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="256"/>
-      <c r="D52" s="256"/>
-      <c r="E52" s="256"/>
-      <c r="F52" s="256"/>
-      <c r="G52" s="256"/>
-      <c r="H52" s="256"/>
-      <c r="I52" s="256"/>
-      <c r="J52" s="256"/>
-      <c r="K52" s="256"/>
-      <c r="L52" s="256" t="s">
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
+      <c r="I52" s="252"/>
+      <c r="J52" s="252"/>
+      <c r="K52" s="252"/>
+      <c r="L52" s="252" t="s">
         <v>29</v>
       </c>
-      <c r="M52" s="256"/>
-      <c r="N52" s="256"/>
-      <c r="O52" s="256"/>
-      <c r="P52" s="256"/>
-      <c r="Q52" s="256"/>
-      <c r="R52" s="256"/>
-      <c r="S52" s="256"/>
-      <c r="T52" s="256"/>
-      <c r="U52" s="257"/>
+      <c r="M52" s="252"/>
+      <c r="N52" s="252"/>
+      <c r="O52" s="252"/>
+      <c r="P52" s="252"/>
+      <c r="Q52" s="252"/>
+      <c r="R52" s="252"/>
+      <c r="S52" s="252"/>
+      <c r="T52" s="252"/>
+      <c r="U52" s="253"/>
     </row>
     <row r="53" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B53" s="255" t="s">
+      <c r="B53" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="256"/>
-      <c r="D53" s="256"/>
-      <c r="E53" s="258" t="str">
+      <c r="C53" s="252"/>
+      <c r="D53" s="252"/>
+      <c r="E53" s="254" t="str">
         <f>G29</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="F53" s="258"/>
-      <c r="G53" s="258"/>
-      <c r="H53" s="258"/>
-      <c r="I53" s="258"/>
-      <c r="J53" s="258"/>
-      <c r="K53" s="258"/>
-      <c r="L53" s="256" t="s">
+      <c r="F53" s="254"/>
+      <c r="G53" s="254"/>
+      <c r="H53" s="254"/>
+      <c r="I53" s="254"/>
+      <c r="J53" s="254"/>
+      <c r="K53" s="254"/>
+      <c r="L53" s="252" t="s">
         <v>31</v>
       </c>
-      <c r="M53" s="256"/>
-      <c r="N53" s="256"/>
-      <c r="O53" s="259" t="s">
+      <c r="M53" s="252"/>
+      <c r="N53" s="252"/>
+      <c r="O53" s="255" t="s">
         <v>32</v>
       </c>
-      <c r="P53" s="259"/>
-      <c r="Q53" s="259"/>
-      <c r="R53" s="259"/>
-      <c r="S53" s="259"/>
-      <c r="T53" s="259"/>
-      <c r="U53" s="260"/>
+      <c r="P53" s="255"/>
+      <c r="Q53" s="255"/>
+      <c r="R53" s="255"/>
+      <c r="S53" s="255"/>
+      <c r="T53" s="255"/>
+      <c r="U53" s="256"/>
     </row>
     <row r="54" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B54" s="255" t="s">
+      <c r="B54" s="251" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="256"/>
-      <c r="D54" s="256"/>
-      <c r="E54" s="261" t="str">
+      <c r="C54" s="252"/>
+      <c r="D54" s="252"/>
+      <c r="E54" s="257" t="str">
         <f>G40</f>
         <v>인천 계양구 아나지로 199 (효성동)</v>
       </c>
-      <c r="F54" s="261"/>
-      <c r="G54" s="261"/>
-      <c r="H54" s="261"/>
-      <c r="I54" s="261"/>
-      <c r="J54" s="261"/>
-      <c r="K54" s="261"/>
-      <c r="L54" s="256" t="s">
+      <c r="F54" s="257"/>
+      <c r="G54" s="257"/>
+      <c r="H54" s="257"/>
+      <c r="I54" s="257"/>
+      <c r="J54" s="257"/>
+      <c r="K54" s="257"/>
+      <c r="L54" s="252" t="s">
         <v>34</v>
       </c>
-      <c r="M54" s="256"/>
-      <c r="N54" s="256"/>
-      <c r="O54" s="262" t="s">
+      <c r="M54" s="252"/>
+      <c r="N54" s="252"/>
+      <c r="O54" s="258" t="s">
         <v>175</v>
       </c>
-      <c r="P54" s="262"/>
-      <c r="Q54" s="262"/>
-      <c r="R54" s="262"/>
-      <c r="S54" s="262"/>
-      <c r="T54" s="262"/>
-      <c r="U54" s="263"/>
+      <c r="P54" s="258"/>
+      <c r="Q54" s="258"/>
+      <c r="R54" s="258"/>
+      <c r="S54" s="258"/>
+      <c r="T54" s="258"/>
+      <c r="U54" s="259"/>
     </row>
     <row r="55" spans="2:21" ht="40.500000" customHeight="1">
-      <c r="B55" s="264" t="s">
+      <c r="B55" s="260" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="265"/>
-      <c r="D55" s="265"/>
-      <c r="E55" s="266" t="s">
+      <c r="C55" s="261"/>
+      <c r="D55" s="261"/>
+      <c r="E55" s="262" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="266"/>
-      <c r="G55" s="266"/>
-      <c r="H55" s="266"/>
-      <c r="I55" s="266"/>
-      <c r="J55" s="266"/>
-      <c r="K55" s="266"/>
-      <c r="L55" s="265" t="s">
+      <c r="F55" s="262"/>
+      <c r="G55" s="262"/>
+      <c r="H55" s="262"/>
+      <c r="I55" s="262"/>
+      <c r="J55" s="262"/>
+      <c r="K55" s="262"/>
+      <c r="L55" s="261" t="s">
         <v>37</v>
       </c>
-      <c r="M55" s="265"/>
-      <c r="N55" s="265"/>
-      <c r="O55" s="181" t="s">
+      <c r="M55" s="261"/>
+      <c r="N55" s="261"/>
+      <c r="O55" s="179" t="s">
         <v>38</v>
       </c>
-      <c r="P55" s="181"/>
-      <c r="Q55" s="181"/>
-      <c r="R55" s="181"/>
-      <c r="S55" s="181"/>
-      <c r="T55" s="181"/>
-      <c r="U55" s="182"/>
+      <c r="P55" s="179"/>
+      <c r="Q55" s="179"/>
+      <c r="R55" s="179"/>
+      <c r="S55" s="179"/>
+      <c r="T55" s="179"/>
+      <c r="U55" s="180"/>
     </row>
     <row r="56" spans="2:21" ht="16.500000">
-      <c r="B56" s="187" t="s">
+      <c r="B56" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="C56" s="187"/>
-      <c r="D56" s="187"/>
-      <c r="E56" s="187"/>
-      <c r="F56" s="187"/>
-      <c r="G56" s="187"/>
-      <c r="H56" s="187"/>
-      <c r="I56" s="187"/>
-      <c r="J56" s="187"/>
-      <c r="K56" s="187"/>
-      <c r="L56" s="187"/>
-      <c r="M56" s="187"/>
-      <c r="N56" s="187"/>
-      <c r="O56" s="187"/>
-      <c r="P56" s="187"/>
-      <c r="Q56" s="187"/>
-      <c r="R56" s="187"/>
-      <c r="S56" s="187"/>
-      <c r="T56" s="187"/>
-      <c r="U56" s="187"/>
+      <c r="C56" s="184"/>
+      <c r="D56" s="184"/>
+      <c r="E56" s="184"/>
+      <c r="F56" s="184"/>
+      <c r="G56" s="184"/>
+      <c r="H56" s="184"/>
+      <c r="I56" s="184"/>
+      <c r="J56" s="184"/>
+      <c r="K56" s="184"/>
+      <c r="L56" s="184"/>
+      <c r="M56" s="184"/>
+      <c r="N56" s="184"/>
+      <c r="O56" s="184"/>
+      <c r="P56" s="184"/>
+      <c r="Q56" s="184"/>
+      <c r="R56" s="184"/>
+      <c r="S56" s="184"/>
+      <c r="T56" s="184"/>
+      <c r="U56" s="184"/>
     </row>
     <row r="57" spans="2:21" ht="25.500000">
-      <c r="B57" s="162" t="s">
+      <c r="B57" s="160" t="s">
         <v>141</v>
       </c>
-      <c r="C57" s="162"/>
-      <c r="D57" s="162"/>
-      <c r="E57" s="162"/>
-      <c r="F57" s="162"/>
-      <c r="G57" s="162"/>
-      <c r="H57" s="162"/>
-      <c r="I57" s="162"/>
-      <c r="J57" s="162"/>
-      <c r="K57" s="162"/>
-      <c r="L57" s="162"/>
-      <c r="M57" s="162"/>
-      <c r="N57" s="162"/>
-      <c r="O57" s="162"/>
-      <c r="P57" s="162"/>
-      <c r="Q57" s="162"/>
-      <c r="R57" s="162"/>
-      <c r="S57" s="162"/>
-      <c r="T57" s="162"/>
-      <c r="U57" s="162"/>
+      <c r="C57" s="160"/>
+      <c r="D57" s="160"/>
+      <c r="E57" s="160"/>
+      <c r="F57" s="160"/>
+      <c r="G57" s="160"/>
+      <c r="H57" s="160"/>
+      <c r="I57" s="160"/>
+      <c r="J57" s="160"/>
+      <c r="K57" s="160"/>
+      <c r="L57" s="160"/>
+      <c r="M57" s="160"/>
+      <c r="N57" s="160"/>
+      <c r="O57" s="160"/>
+      <c r="P57" s="160"/>
+      <c r="Q57" s="160"/>
+      <c r="R57" s="160"/>
+      <c r="S57" s="160"/>
+      <c r="T57" s="160"/>
+      <c r="U57" s="160"/>
     </row>
     <row r="58" spans="2:21" ht="14.250000">
       <c r="B58" s="25"/>
@@ -38498,28 +38417,28 @@
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B59" s="188" t="s">
+      <c r="B59" s="185" t="s">
         <v>152</v>
       </c>
-      <c r="C59" s="188"/>
-      <c r="D59" s="188"/>
-      <c r="E59" s="188"/>
-      <c r="F59" s="188"/>
-      <c r="G59" s="188"/>
-      <c r="H59" s="188"/>
-      <c r="I59" s="188"/>
-      <c r="J59" s="188"/>
-      <c r="K59" s="188"/>
-      <c r="L59" s="188"/>
-      <c r="M59" s="188"/>
-      <c r="N59" s="188"/>
-      <c r="O59" s="188"/>
-      <c r="P59" s="188"/>
-      <c r="Q59" s="188"/>
-      <c r="R59" s="188"/>
-      <c r="S59" s="188"/>
-      <c r="T59" s="188"/>
-      <c r="U59" s="188"/>
+      <c r="C59" s="185"/>
+      <c r="D59" s="185"/>
+      <c r="E59" s="185"/>
+      <c r="F59" s="185"/>
+      <c r="G59" s="185"/>
+      <c r="H59" s="185"/>
+      <c r="I59" s="185"/>
+      <c r="J59" s="185"/>
+      <c r="K59" s="185"/>
+      <c r="L59" s="185"/>
+      <c r="M59" s="185"/>
+      <c r="N59" s="185"/>
+      <c r="O59" s="185"/>
+      <c r="P59" s="185"/>
+      <c r="Q59" s="185"/>
+      <c r="R59" s="185"/>
+      <c r="S59" s="185"/>
+      <c r="T59" s="185"/>
+      <c r="U59" s="185"/>
     </row>
     <row r="60" spans="2:21" ht="28.500000" customHeight="1">
       <c r="B60" s="20" t="s">
@@ -38531,15 +38450,15 @@
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
-      <c r="I60" s="190" t="str">
+      <c r="I60" s="186" t="str">
         <f>E53</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="J60" s="190"/>
-      <c r="K60" s="190"/>
-      <c r="L60" s="190"/>
-      <c r="M60" s="190"/>
-      <c r="N60" s="190"/>
+      <c r="J60" s="186"/>
+      <c r="K60" s="186"/>
+      <c r="L60" s="186"/>
+      <c r="M60" s="186"/>
+      <c r="N60" s="186"/>
       <c r="O60" s="20" t="s">
         <v>174</v>
       </c>
@@ -38551,28 +38470,28 @@
       <c r="U60" s="20"/>
     </row>
     <row r="61" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B61" s="188" t="s">
+      <c r="B61" s="185" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="188"/>
-      <c r="D61" s="188"/>
-      <c r="E61" s="188"/>
-      <c r="F61" s="188"/>
-      <c r="G61" s="188"/>
-      <c r="H61" s="188"/>
-      <c r="I61" s="188"/>
-      <c r="J61" s="188"/>
-      <c r="K61" s="188"/>
-      <c r="L61" s="188"/>
-      <c r="M61" s="188"/>
-      <c r="N61" s="188"/>
-      <c r="O61" s="188"/>
-      <c r="P61" s="188"/>
-      <c r="Q61" s="188"/>
-      <c r="R61" s="188"/>
-      <c r="S61" s="188"/>
-      <c r="T61" s="188"/>
-      <c r="U61" s="188"/>
+      <c r="C61" s="185"/>
+      <c r="D61" s="185"/>
+      <c r="E61" s="185"/>
+      <c r="F61" s="185"/>
+      <c r="G61" s="185"/>
+      <c r="H61" s="185"/>
+      <c r="I61" s="185"/>
+      <c r="J61" s="185"/>
+      <c r="K61" s="185"/>
+      <c r="L61" s="185"/>
+      <c r="M61" s="185"/>
+      <c r="N61" s="185"/>
+      <c r="O61" s="185"/>
+      <c r="P61" s="185"/>
+      <c r="Q61" s="185"/>
+      <c r="R61" s="185"/>
+      <c r="S61" s="185"/>
+      <c r="T61" s="185"/>
+      <c r="U61" s="185"/>
     </row>
     <row r="62" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B62" s="20"/>
@@ -38586,17 +38505,17 @@
       <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B63" s="186" t="s">
+      <c r="B63" s="161" t="s">
         <v>161</v>
       </c>
-      <c r="C63" s="186"/>
-      <c r="D63" s="186"/>
-      <c r="E63" s="186"/>
-      <c r="F63" s="186"/>
-      <c r="G63" s="186"/>
-      <c r="H63" s="186"/>
-      <c r="I63" s="186"/>
-      <c r="J63" s="186"/>
+      <c r="C63" s="161"/>
+      <c r="D63" s="161"/>
+      <c r="E63" s="161"/>
+      <c r="F63" s="161"/>
+      <c r="G63" s="161"/>
+      <c r="H63" s="161"/>
+      <c r="I63" s="161"/>
+      <c r="J63" s="161"/>
     </row>
     <row r="64" spans="2:21" ht="94.500000" customHeight="1">
       <c r="C64" s="20" t="s">
@@ -38628,28 +38547,28 @@
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B66" s="186" t="s">
+      <c r="B66" s="161" t="s">
         <v>100</v>
       </c>
-      <c r="C66" s="186"/>
-      <c r="D66" s="186"/>
-      <c r="E66" s="186"/>
-      <c r="F66" s="186"/>
-      <c r="G66" s="186"/>
-      <c r="H66" s="186"/>
-      <c r="I66" s="186"/>
-      <c r="J66" s="186"/>
-      <c r="K66" s="186"/>
-      <c r="L66" s="186"/>
-      <c r="M66" s="186"/>
-      <c r="N66" s="186"/>
-      <c r="O66" s="186"/>
-      <c r="P66" s="186"/>
-      <c r="Q66" s="186"/>
-      <c r="R66" s="186"/>
-      <c r="S66" s="186"/>
-      <c r="T66" s="186"/>
-      <c r="U66" s="186"/>
+      <c r="C66" s="161"/>
+      <c r="D66" s="161"/>
+      <c r="E66" s="161"/>
+      <c r="F66" s="161"/>
+      <c r="G66" s="161"/>
+      <c r="H66" s="161"/>
+      <c r="I66" s="161"/>
+      <c r="J66" s="161"/>
+      <c r="K66" s="161"/>
+      <c r="L66" s="161"/>
+      <c r="M66" s="161"/>
+      <c r="N66" s="161"/>
+      <c r="O66" s="161"/>
+      <c r="P66" s="161"/>
+      <c r="Q66" s="161"/>
+      <c r="R66" s="161"/>
+      <c r="S66" s="161"/>
+      <c r="T66" s="161"/>
+      <c r="U66" s="161"/>
     </row>
     <row r="67" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C67" s="50" t="str">
@@ -38677,7 +38596,7 @@
     </row>
     <row r="68" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C68" s="50" t="str">
-        <f>"② 위      치 : "&amp;E54</f>
+        <f>"② 위      치 : "&amp;갑지!L22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D68" s="50"/>
@@ -38754,28 +38673,28 @@
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B72" s="186" t="s">
+      <c r="B72" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="186"/>
-      <c r="D72" s="186"/>
-      <c r="E72" s="186"/>
-      <c r="F72" s="186"/>
-      <c r="G72" s="186"/>
-      <c r="H72" s="186"/>
-      <c r="I72" s="186"/>
-      <c r="J72" s="186"/>
-      <c r="K72" s="186"/>
-      <c r="L72" s="186"/>
-      <c r="M72" s="186"/>
-      <c r="N72" s="186"/>
-      <c r="O72" s="186"/>
-      <c r="P72" s="186"/>
-      <c r="Q72" s="186"/>
-      <c r="R72" s="186"/>
-      <c r="S72" s="186"/>
-      <c r="T72" s="186"/>
-      <c r="U72" s="186"/>
+      <c r="C72" s="161"/>
+      <c r="D72" s="161"/>
+      <c r="E72" s="161"/>
+      <c r="F72" s="161"/>
+      <c r="G72" s="161"/>
+      <c r="H72" s="161"/>
+      <c r="I72" s="161"/>
+      <c r="J72" s="161"/>
+      <c r="K72" s="161"/>
+      <c r="L72" s="161"/>
+      <c r="M72" s="161"/>
+      <c r="N72" s="161"/>
+      <c r="O72" s="161"/>
+      <c r="P72" s="161"/>
+      <c r="Q72" s="161"/>
+      <c r="R72" s="161"/>
+      <c r="S72" s="161"/>
+      <c r="T72" s="161"/>
+      <c r="U72" s="161"/>
     </row>
     <row r="73" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C73" s="27" t="s">
@@ -39006,28 +38925,28 @@
       <c r="U82" s="50"/>
     </row>
     <row r="83" spans="2:21" ht="18.750000">
-      <c r="B83" s="186" t="s">
+      <c r="B83" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="C83" s="186"/>
-      <c r="D83" s="186"/>
-      <c r="E83" s="186"/>
-      <c r="F83" s="186"/>
-      <c r="G83" s="186"/>
-      <c r="H83" s="186"/>
-      <c r="I83" s="186"/>
-      <c r="J83" s="186"/>
-      <c r="K83" s="186"/>
-      <c r="L83" s="186"/>
-      <c r="M83" s="186"/>
-      <c r="N83" s="186"/>
-      <c r="O83" s="186"/>
-      <c r="P83" s="186"/>
-      <c r="Q83" s="186"/>
-      <c r="R83" s="186"/>
-      <c r="S83" s="186"/>
-      <c r="T83" s="186"/>
-      <c r="U83" s="186"/>
+      <c r="C83" s="161"/>
+      <c r="D83" s="161"/>
+      <c r="E83" s="161"/>
+      <c r="F83" s="161"/>
+      <c r="G83" s="161"/>
+      <c r="H83" s="161"/>
+      <c r="I83" s="161"/>
+      <c r="J83" s="161"/>
+      <c r="K83" s="161"/>
+      <c r="L83" s="161"/>
+      <c r="M83" s="161"/>
+      <c r="N83" s="161"/>
+      <c r="O83" s="161"/>
+      <c r="P83" s="161"/>
+      <c r="Q83" s="161"/>
+      <c r="R83" s="161"/>
+      <c r="S83" s="161"/>
+      <c r="T83" s="161"/>
+      <c r="U83" s="161"/>
     </row>
     <row r="84" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B84" s="115"/>
@@ -39060,28 +38979,28 @@
       <c r="I85" s="3"/>
     </row>
     <row r="86" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B86" s="186" t="s">
+      <c r="B86" s="161" t="s">
         <v>115</v>
       </c>
-      <c r="C86" s="186"/>
-      <c r="D86" s="186"/>
-      <c r="E86" s="186"/>
-      <c r="F86" s="186"/>
-      <c r="G86" s="186"/>
-      <c r="H86" s="186"/>
-      <c r="I86" s="186"/>
-      <c r="J86" s="186"/>
-      <c r="K86" s="186"/>
-      <c r="L86" s="186"/>
-      <c r="M86" s="186"/>
-      <c r="N86" s="186"/>
-      <c r="O86" s="186"/>
-      <c r="P86" s="186"/>
-      <c r="Q86" s="186"/>
-      <c r="R86" s="186"/>
-      <c r="S86" s="186"/>
-      <c r="T86" s="186"/>
-      <c r="U86" s="186"/>
+      <c r="C86" s="161"/>
+      <c r="D86" s="161"/>
+      <c r="E86" s="161"/>
+      <c r="F86" s="161"/>
+      <c r="G86" s="161"/>
+      <c r="H86" s="161"/>
+      <c r="I86" s="161"/>
+      <c r="J86" s="161"/>
+      <c r="K86" s="161"/>
+      <c r="L86" s="161"/>
+      <c r="M86" s="161"/>
+      <c r="N86" s="161"/>
+      <c r="O86" s="161"/>
+      <c r="P86" s="161"/>
+      <c r="Q86" s="161"/>
+      <c r="R86" s="161"/>
+      <c r="S86" s="161"/>
+      <c r="T86" s="161"/>
+      <c r="U86" s="161"/>
     </row>
     <row r="87" spans="2:21" ht="49.500000" customHeight="1">
       <c r="C87" s="20" t="s">
@@ -39117,97 +39036,97 @@
       <c r="J88" s="27"/>
     </row>
     <row r="89" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B89" s="163" t="s">
+      <c r="B89" s="161" t="s">
         <v>116</v>
       </c>
-      <c r="C89" s="163"/>
-      <c r="D89" s="163"/>
-      <c r="E89" s="163"/>
-      <c r="F89" s="163"/>
-      <c r="G89" s="163"/>
-      <c r="H89" s="163"/>
-      <c r="I89" s="163"/>
-      <c r="J89" s="163"/>
-      <c r="K89" s="163"/>
-      <c r="L89" s="163"/>
-      <c r="M89" s="163"/>
-      <c r="N89" s="163"/>
-      <c r="O89" s="163"/>
-      <c r="P89" s="163"/>
-      <c r="Q89" s="163"/>
-      <c r="R89" s="163"/>
-      <c r="S89" s="163"/>
-      <c r="T89" s="163"/>
-      <c r="U89" s="163"/>
+      <c r="C89" s="161"/>
+      <c r="D89" s="161"/>
+      <c r="E89" s="161"/>
+      <c r="F89" s="161"/>
+      <c r="G89" s="161"/>
+      <c r="H89" s="161"/>
+      <c r="I89" s="161"/>
+      <c r="J89" s="161"/>
+      <c r="K89" s="161"/>
+      <c r="L89" s="161"/>
+      <c r="M89" s="161"/>
+      <c r="N89" s="161"/>
+      <c r="O89" s="161"/>
+      <c r="P89" s="161"/>
+      <c r="Q89" s="161"/>
+      <c r="R89" s="161"/>
+      <c r="S89" s="161"/>
+      <c r="T89" s="161"/>
+      <c r="U89" s="161"/>
     </row>
     <row r="90" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C90" s="120" t="s">
+      <c r="C90" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D90" s="120"/>
-      <c r="E90" s="120"/>
-      <c r="F90" s="120"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="120"/>
-      <c r="I90" s="120"/>
-      <c r="J90" s="120"/>
-      <c r="K90" s="120"/>
-      <c r="L90" s="120"/>
-      <c r="M90" s="120"/>
-      <c r="N90" s="120"/>
-      <c r="O90" s="120"/>
-      <c r="P90" s="120"/>
-      <c r="Q90" s="120"/>
-      <c r="R90" s="120"/>
-      <c r="S90" s="120"/>
-      <c r="T90" s="120"/>
-      <c r="U90" s="120"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20"/>
+      <c r="K90" s="20"/>
+      <c r="L90" s="20"/>
+      <c r="M90" s="20"/>
+      <c r="N90" s="20"/>
+      <c r="O90" s="20"/>
+      <c r="P90" s="20"/>
+      <c r="Q90" s="20"/>
+      <c r="R90" s="20"/>
+      <c r="S90" s="20"/>
+      <c r="T90" s="20"/>
+      <c r="U90" s="20"/>
     </row>
     <row r="91" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C91" s="120" t="s">
+      <c r="C91" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D91" s="120"/>
-      <c r="E91" s="120"/>
-      <c r="F91" s="120"/>
-      <c r="G91" s="120"/>
-      <c r="H91" s="120"/>
-      <c r="I91" s="120"/>
-      <c r="J91" s="120"/>
-      <c r="K91" s="120"/>
-      <c r="L91" s="120"/>
-      <c r="M91" s="120"/>
-      <c r="N91" s="120"/>
-      <c r="O91" s="120"/>
-      <c r="P91" s="120"/>
-      <c r="Q91" s="120"/>
-      <c r="R91" s="120"/>
-      <c r="S91" s="120"/>
-      <c r="T91" s="120"/>
-      <c r="U91" s="120"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="20"/>
+      <c r="L91" s="20"/>
+      <c r="M91" s="20"/>
+      <c r="N91" s="20"/>
+      <c r="O91" s="20"/>
+      <c r="P91" s="20"/>
+      <c r="Q91" s="20"/>
+      <c r="R91" s="20"/>
+      <c r="S91" s="20"/>
+      <c r="T91" s="20"/>
+      <c r="U91" s="20"/>
     </row>
     <row r="92" spans="2:21" ht="47.000000" customHeight="1">
-      <c r="C92" s="120" t="s">
+      <c r="C92" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D92" s="120"/>
-      <c r="E92" s="120"/>
-      <c r="F92" s="120"/>
-      <c r="G92" s="120"/>
-      <c r="H92" s="120"/>
-      <c r="I92" s="120"/>
-      <c r="J92" s="120"/>
-      <c r="K92" s="120"/>
-      <c r="L92" s="120"/>
-      <c r="M92" s="120"/>
-      <c r="N92" s="120"/>
-      <c r="O92" s="120"/>
-      <c r="P92" s="120"/>
-      <c r="Q92" s="120"/>
-      <c r="R92" s="120"/>
-      <c r="S92" s="120"/>
-      <c r="T92" s="120"/>
-      <c r="U92" s="120"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="20"/>
+      <c r="L92" s="20"/>
+      <c r="M92" s="20"/>
+      <c r="N92" s="20"/>
+      <c r="O92" s="20"/>
+      <c r="P92" s="20"/>
+      <c r="Q92" s="20"/>
+      <c r="R92" s="20"/>
+      <c r="S92" s="20"/>
+      <c r="T92" s="20"/>
+      <c r="U92" s="20"/>
     </row>
     <row r="93" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B93" s="116"/>
@@ -39232,98 +39151,98 @@
       <c r="U93" s="46"/>
     </row>
     <row r="94" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B94" s="163" t="s">
+      <c r="B94" s="161" t="s">
         <v>117</v>
       </c>
-      <c r="C94" s="163"/>
-      <c r="D94" s="163"/>
-      <c r="E94" s="163"/>
-      <c r="F94" s="163"/>
-      <c r="G94" s="163"/>
-      <c r="H94" s="163"/>
-      <c r="I94" s="163"/>
-      <c r="J94" s="163"/>
-      <c r="K94" s="163"/>
-      <c r="L94" s="163"/>
-      <c r="M94" s="163"/>
-      <c r="N94" s="163"/>
-      <c r="O94" s="163"/>
-      <c r="P94" s="163"/>
-      <c r="Q94" s="163"/>
-      <c r="R94" s="163"/>
-      <c r="S94" s="163"/>
-      <c r="T94" s="163"/>
-      <c r="U94" s="163"/>
+      <c r="C94" s="161"/>
+      <c r="D94" s="161"/>
+      <c r="E94" s="161"/>
+      <c r="F94" s="161"/>
+      <c r="G94" s="161"/>
+      <c r="H94" s="161"/>
+      <c r="I94" s="161"/>
+      <c r="J94" s="161"/>
+      <c r="K94" s="161"/>
+      <c r="L94" s="161"/>
+      <c r="M94" s="161"/>
+      <c r="N94" s="161"/>
+      <c r="O94" s="161"/>
+      <c r="P94" s="161"/>
+      <c r="Q94" s="161"/>
+      <c r="R94" s="161"/>
+      <c r="S94" s="161"/>
+      <c r="T94" s="161"/>
+      <c r="U94" s="161"/>
     </row>
     <row r="95" spans="2:21" ht="69.000000" customHeight="1">
-      <c r="C95" s="120" t="s">
+      <c r="C95" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D95" s="120"/>
-      <c r="E95" s="120"/>
-      <c r="F95" s="120"/>
-      <c r="G95" s="120"/>
-      <c r="H95" s="120"/>
-      <c r="I95" s="120"/>
-      <c r="J95" s="120"/>
-      <c r="K95" s="120"/>
-      <c r="L95" s="120"/>
-      <c r="M95" s="120"/>
-      <c r="N95" s="120"/>
-      <c r="O95" s="120"/>
-      <c r="P95" s="120"/>
-      <c r="Q95" s="120"/>
-      <c r="R95" s="120"/>
-      <c r="S95" s="120"/>
-      <c r="T95" s="120"/>
-      <c r="U95" s="120"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20"/>
+      <c r="G95" s="20"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
+      <c r="K95" s="20"/>
+      <c r="L95" s="20"/>
+      <c r="M95" s="20"/>
+      <c r="N95" s="20"/>
+      <c r="O95" s="20"/>
+      <c r="P95" s="20"/>
+      <c r="Q95" s="20"/>
+      <c r="R95" s="20"/>
+      <c r="S95" s="20"/>
+      <c r="T95" s="20"/>
+      <c r="U95" s="20"/>
     </row>
     <row r="96" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="C96" s="120" t="s">
+      <c r="C96" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="D96" s="120"/>
-      <c r="E96" s="120"/>
-      <c r="F96" s="120"/>
-      <c r="G96" s="120"/>
-      <c r="H96" s="120"/>
-      <c r="I96" s="120"/>
-      <c r="J96" s="120"/>
-      <c r="K96" s="120"/>
-      <c r="L96" s="120"/>
-      <c r="M96" s="120"/>
-      <c r="N96" s="120"/>
-      <c r="O96" s="120"/>
-      <c r="P96" s="120"/>
-      <c r="Q96" s="120"/>
-      <c r="R96" s="120"/>
-      <c r="S96" s="120"/>
-      <c r="T96" s="120"/>
-      <c r="U96" s="120"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
+      <c r="K96" s="20"/>
+      <c r="L96" s="20"/>
+      <c r="M96" s="20"/>
+      <c r="N96" s="20"/>
+      <c r="O96" s="20"/>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="20"/>
+      <c r="R96" s="20"/>
+      <c r="S96" s="20"/>
+      <c r="T96" s="20"/>
+      <c r="U96" s="20"/>
     </row>
     <row r="97" spans="2:21" ht="33.000000" customHeight="1">
-      <c r="B97" s="119"/>
-      <c r="C97" s="189" t="s">
+      <c r="B97" s="26"/>
+      <c r="C97" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="189"/>
-      <c r="E97" s="189"/>
-      <c r="F97" s="189"/>
-      <c r="G97" s="189"/>
-      <c r="H97" s="189"/>
-      <c r="I97" s="189"/>
-      <c r="J97" s="189"/>
-      <c r="K97" s="189"/>
-      <c r="L97" s="189"/>
-      <c r="M97" s="189"/>
-      <c r="N97" s="189"/>
-      <c r="O97" s="189"/>
-      <c r="P97" s="189"/>
-      <c r="Q97" s="189"/>
-      <c r="R97" s="189"/>
-      <c r="S97" s="189"/>
-      <c r="T97" s="189"/>
-      <c r="U97" s="189"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="19"/>
+      <c r="K97" s="19"/>
+      <c r="L97" s="19"/>
+      <c r="M97" s="19"/>
+      <c r="N97" s="19"/>
+      <c r="O97" s="19"/>
+      <c r="P97" s="19"/>
+      <c r="Q97" s="19"/>
+      <c r="R97" s="19"/>
+      <c r="S97" s="19"/>
+      <c r="T97" s="19"/>
+      <c r="U97" s="19"/>
     </row>
     <row r="98" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B98" s="116"/>
@@ -39348,74 +39267,74 @@
       <c r="U98" s="46"/>
     </row>
     <row r="99" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B99" s="163" t="s">
+      <c r="B99" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="C99" s="163"/>
-      <c r="D99" s="163"/>
-      <c r="E99" s="163"/>
-      <c r="F99" s="163"/>
-      <c r="G99" s="163"/>
-      <c r="H99" s="163"/>
-      <c r="I99" s="163"/>
-      <c r="J99" s="163"/>
-      <c r="K99" s="163"/>
-      <c r="L99" s="163"/>
-      <c r="M99" s="163"/>
-      <c r="N99" s="163"/>
-      <c r="O99" s="163"/>
-      <c r="P99" s="163"/>
-      <c r="Q99" s="163"/>
-      <c r="R99" s="163"/>
-      <c r="S99" s="163"/>
-      <c r="T99" s="163"/>
-      <c r="U99" s="163"/>
+      <c r="C99" s="161"/>
+      <c r="D99" s="161"/>
+      <c r="E99" s="161"/>
+      <c r="F99" s="161"/>
+      <c r="G99" s="161"/>
+      <c r="H99" s="161"/>
+      <c r="I99" s="161"/>
+      <c r="J99" s="161"/>
+      <c r="K99" s="161"/>
+      <c r="L99" s="161"/>
+      <c r="M99" s="161"/>
+      <c r="N99" s="161"/>
+      <c r="O99" s="161"/>
+      <c r="P99" s="161"/>
+      <c r="Q99" s="161"/>
+      <c r="R99" s="161"/>
+      <c r="S99" s="161"/>
+      <c r="T99" s="161"/>
+      <c r="U99" s="161"/>
     </row>
     <row r="100" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C100" s="120" t="s">
+      <c r="C100" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D100" s="120"/>
-      <c r="E100" s="120"/>
-      <c r="F100" s="120"/>
-      <c r="G100" s="120"/>
-      <c r="H100" s="120"/>
-      <c r="I100" s="120"/>
-      <c r="J100" s="120"/>
-      <c r="K100" s="120"/>
-      <c r="L100" s="120"/>
-      <c r="M100" s="120"/>
-      <c r="N100" s="120"/>
-      <c r="O100" s="120"/>
-      <c r="P100" s="120"/>
-      <c r="Q100" s="120"/>
-      <c r="R100" s="120"/>
-      <c r="S100" s="120"/>
-      <c r="T100" s="120"/>
-      <c r="U100" s="120"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="20"/>
+      <c r="J100" s="20"/>
+      <c r="K100" s="20"/>
+      <c r="L100" s="20"/>
+      <c r="M100" s="20"/>
+      <c r="N100" s="20"/>
+      <c r="O100" s="20"/>
+      <c r="P100" s="20"/>
+      <c r="Q100" s="20"/>
+      <c r="R100" s="20"/>
+      <c r="S100" s="20"/>
+      <c r="T100" s="20"/>
+      <c r="U100" s="20"/>
     </row>
     <row r="101" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C101" s="120" t="s">
+      <c r="C101" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D101" s="120"/>
-      <c r="E101" s="120"/>
-      <c r="F101" s="120"/>
-      <c r="G101" s="120"/>
-      <c r="H101" s="120"/>
-      <c r="I101" s="120"/>
-      <c r="J101" s="120"/>
-      <c r="K101" s="120"/>
-      <c r="L101" s="120"/>
-      <c r="M101" s="120"/>
-      <c r="N101" s="120"/>
-      <c r="O101" s="120"/>
-      <c r="P101" s="120"/>
-      <c r="Q101" s="120"/>
-      <c r="R101" s="120"/>
-      <c r="S101" s="120"/>
-      <c r="T101" s="120"/>
-      <c r="U101" s="120"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="20"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="20"/>
+      <c r="J101" s="20"/>
+      <c r="K101" s="20"/>
+      <c r="L101" s="20"/>
+      <c r="M101" s="20"/>
+      <c r="N101" s="20"/>
+      <c r="O101" s="20"/>
+      <c r="P101" s="20"/>
+      <c r="Q101" s="20"/>
+      <c r="R101" s="20"/>
+      <c r="S101" s="20"/>
+      <c r="T101" s="20"/>
+      <c r="U101" s="20"/>
     </row>
     <row r="102" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B102" s="116"/>
@@ -39440,74 +39359,74 @@
       <c r="U102" s="46"/>
     </row>
     <row r="103" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B103" s="163" t="s">
+      <c r="B103" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="C103" s="163"/>
-      <c r="D103" s="163"/>
-      <c r="E103" s="163"/>
-      <c r="F103" s="163"/>
-      <c r="G103" s="163"/>
-      <c r="H103" s="163"/>
-      <c r="I103" s="163"/>
-      <c r="J103" s="163"/>
-      <c r="K103" s="163"/>
-      <c r="L103" s="163"/>
-      <c r="M103" s="163"/>
-      <c r="N103" s="163"/>
-      <c r="O103" s="163"/>
-      <c r="P103" s="163"/>
-      <c r="Q103" s="163"/>
-      <c r="R103" s="163"/>
-      <c r="S103" s="163"/>
-      <c r="T103" s="163"/>
-      <c r="U103" s="163"/>
+      <c r="C103" s="161"/>
+      <c r="D103" s="161"/>
+      <c r="E103" s="161"/>
+      <c r="F103" s="161"/>
+      <c r="G103" s="161"/>
+      <c r="H103" s="161"/>
+      <c r="I103" s="161"/>
+      <c r="J103" s="161"/>
+      <c r="K103" s="161"/>
+      <c r="L103" s="161"/>
+      <c r="M103" s="161"/>
+      <c r="N103" s="161"/>
+      <c r="O103" s="161"/>
+      <c r="P103" s="161"/>
+      <c r="Q103" s="161"/>
+      <c r="R103" s="161"/>
+      <c r="S103" s="161"/>
+      <c r="T103" s="161"/>
+      <c r="U103" s="161"/>
     </row>
     <row r="104" spans="2:21" ht="49.000000" customHeight="1">
-      <c r="C104" s="120" t="s">
+      <c r="C104" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D104" s="120"/>
-      <c r="E104" s="120"/>
-      <c r="F104" s="120"/>
-      <c r="G104" s="120"/>
-      <c r="H104" s="120"/>
-      <c r="I104" s="120"/>
-      <c r="J104" s="120"/>
-      <c r="K104" s="120"/>
-      <c r="L104" s="120"/>
-      <c r="M104" s="120"/>
-      <c r="N104" s="120"/>
-      <c r="O104" s="120"/>
-      <c r="P104" s="120"/>
-      <c r="Q104" s="120"/>
-      <c r="R104" s="120"/>
-      <c r="S104" s="120"/>
-      <c r="T104" s="120"/>
-      <c r="U104" s="120"/>
+      <c r="D104" s="20"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="20"/>
+      <c r="G104" s="20"/>
+      <c r="H104" s="20"/>
+      <c r="I104" s="20"/>
+      <c r="J104" s="20"/>
+      <c r="K104" s="20"/>
+      <c r="L104" s="20"/>
+      <c r="M104" s="20"/>
+      <c r="N104" s="20"/>
+      <c r="O104" s="20"/>
+      <c r="P104" s="20"/>
+      <c r="Q104" s="20"/>
+      <c r="R104" s="20"/>
+      <c r="S104" s="20"/>
+      <c r="T104" s="20"/>
+      <c r="U104" s="20"/>
     </row>
     <row r="105" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C105" s="120" t="s">
+      <c r="C105" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D105" s="120"/>
-      <c r="E105" s="120"/>
-      <c r="F105" s="120"/>
-      <c r="G105" s="120"/>
-      <c r="H105" s="120"/>
-      <c r="I105" s="120"/>
-      <c r="J105" s="120"/>
-      <c r="K105" s="120"/>
-      <c r="L105" s="120"/>
-      <c r="M105" s="120"/>
-      <c r="N105" s="120"/>
-      <c r="O105" s="120"/>
-      <c r="P105" s="120"/>
-      <c r="Q105" s="120"/>
-      <c r="R105" s="120"/>
-      <c r="S105" s="120"/>
-      <c r="T105" s="120"/>
-      <c r="U105" s="120"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="20"/>
+      <c r="I105" s="20"/>
+      <c r="J105" s="20"/>
+      <c r="K105" s="20"/>
+      <c r="L105" s="20"/>
+      <c r="M105" s="20"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20"/>
+      <c r="P105" s="20"/>
+      <c r="Q105" s="20"/>
+      <c r="R105" s="20"/>
+      <c r="S105" s="20"/>
+      <c r="T105" s="20"/>
+      <c r="U105" s="20"/>
     </row>
     <row r="106" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B106" s="116"/>
@@ -39532,74 +39451,74 @@
       <c r="U106" s="46"/>
     </row>
     <row r="107" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B107" s="163" t="s">
+      <c r="B107" s="161" t="s">
         <v>126</v>
       </c>
-      <c r="C107" s="163"/>
-      <c r="D107" s="163"/>
-      <c r="E107" s="163"/>
-      <c r="F107" s="163"/>
-      <c r="G107" s="163"/>
-      <c r="H107" s="163"/>
-      <c r="I107" s="163"/>
-      <c r="J107" s="163"/>
-      <c r="K107" s="163"/>
-      <c r="L107" s="163"/>
-      <c r="M107" s="163"/>
-      <c r="N107" s="163"/>
-      <c r="O107" s="163"/>
-      <c r="P107" s="163"/>
-      <c r="Q107" s="163"/>
-      <c r="R107" s="163"/>
-      <c r="S107" s="163"/>
-      <c r="T107" s="163"/>
-      <c r="U107" s="163"/>
+      <c r="C107" s="161"/>
+      <c r="D107" s="161"/>
+      <c r="E107" s="161"/>
+      <c r="F107" s="161"/>
+      <c r="G107" s="161"/>
+      <c r="H107" s="161"/>
+      <c r="I107" s="161"/>
+      <c r="J107" s="161"/>
+      <c r="K107" s="161"/>
+      <c r="L107" s="161"/>
+      <c r="M107" s="161"/>
+      <c r="N107" s="161"/>
+      <c r="O107" s="161"/>
+      <c r="P107" s="161"/>
+      <c r="Q107" s="161"/>
+      <c r="R107" s="161"/>
+      <c r="S107" s="161"/>
+      <c r="T107" s="161"/>
+      <c r="U107" s="161"/>
     </row>
     <row r="108" spans="2:21" ht="33.000000" customHeight="1">
-      <c r="C108" s="120" t="s">
+      <c r="C108" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D108" s="120"/>
-      <c r="E108" s="120"/>
-      <c r="F108" s="120"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="120"/>
-      <c r="I108" s="120"/>
-      <c r="J108" s="120"/>
-      <c r="K108" s="120"/>
-      <c r="L108" s="120"/>
-      <c r="M108" s="120"/>
-      <c r="N108" s="120"/>
-      <c r="O108" s="120"/>
-      <c r="P108" s="120"/>
-      <c r="Q108" s="120"/>
-      <c r="R108" s="120"/>
-      <c r="S108" s="120"/>
-      <c r="T108" s="120"/>
-      <c r="U108" s="120"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="20"/>
+      <c r="J108" s="20"/>
+      <c r="K108" s="20"/>
+      <c r="L108" s="20"/>
+      <c r="M108" s="20"/>
+      <c r="N108" s="20"/>
+      <c r="O108" s="20"/>
+      <c r="P108" s="20"/>
+      <c r="Q108" s="20"/>
+      <c r="R108" s="20"/>
+      <c r="S108" s="20"/>
+      <c r="T108" s="20"/>
+      <c r="U108" s="20"/>
     </row>
     <row r="109" spans="2:21" ht="49.000000" customHeight="1">
-      <c r="C109" s="120" t="s">
+      <c r="C109" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="D109" s="120"/>
-      <c r="E109" s="120"/>
-      <c r="F109" s="120"/>
-      <c r="G109" s="120"/>
-      <c r="H109" s="120"/>
-      <c r="I109" s="120"/>
-      <c r="J109" s="120"/>
-      <c r="K109" s="120"/>
-      <c r="L109" s="120"/>
-      <c r="M109" s="120"/>
-      <c r="N109" s="120"/>
-      <c r="O109" s="120"/>
-      <c r="P109" s="120"/>
-      <c r="Q109" s="120"/>
-      <c r="R109" s="120"/>
-      <c r="S109" s="120"/>
-      <c r="T109" s="120"/>
-      <c r="U109" s="120"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
+      <c r="K109" s="20"/>
+      <c r="L109" s="20"/>
+      <c r="M109" s="20"/>
+      <c r="N109" s="20"/>
+      <c r="O109" s="20"/>
+      <c r="P109" s="20"/>
+      <c r="Q109" s="20"/>
+      <c r="R109" s="20"/>
+      <c r="S109" s="20"/>
+      <c r="T109" s="20"/>
+      <c r="U109" s="20"/>
     </row>
     <row r="110" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B110" s="116"/>
@@ -39624,143 +39543,143 @@
       <c r="U110" s="46"/>
     </row>
     <row r="111" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B111" s="163" t="s">
+      <c r="B111" s="161" t="s">
         <v>127</v>
       </c>
-      <c r="C111" s="163"/>
-      <c r="D111" s="163"/>
-      <c r="E111" s="163"/>
-      <c r="F111" s="163"/>
-      <c r="G111" s="163"/>
-      <c r="H111" s="163"/>
-      <c r="I111" s="163"/>
-      <c r="J111" s="163"/>
-      <c r="K111" s="163"/>
-      <c r="L111" s="163"/>
-      <c r="M111" s="163"/>
-      <c r="N111" s="163"/>
-      <c r="O111" s="163"/>
-      <c r="P111" s="163"/>
-      <c r="Q111" s="163"/>
-      <c r="R111" s="163"/>
-      <c r="S111" s="163"/>
-      <c r="T111" s="163"/>
-      <c r="U111" s="163"/>
+      <c r="C111" s="161"/>
+      <c r="D111" s="161"/>
+      <c r="E111" s="161"/>
+      <c r="F111" s="161"/>
+      <c r="G111" s="161"/>
+      <c r="H111" s="161"/>
+      <c r="I111" s="161"/>
+      <c r="J111" s="161"/>
+      <c r="K111" s="161"/>
+      <c r="L111" s="161"/>
+      <c r="M111" s="161"/>
+      <c r="N111" s="161"/>
+      <c r="O111" s="161"/>
+      <c r="P111" s="161"/>
+      <c r="Q111" s="161"/>
+      <c r="R111" s="161"/>
+      <c r="S111" s="161"/>
+      <c r="T111" s="161"/>
+      <c r="U111" s="161"/>
     </row>
     <row r="112" spans="2:21" ht="16.500000" customHeight="1">
-      <c r="C112" s="120" t="s">
+      <c r="C112" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D112" s="120"/>
-      <c r="E112" s="120"/>
-      <c r="F112" s="120"/>
-      <c r="G112" s="120"/>
-      <c r="H112" s="120"/>
-      <c r="I112" s="120"/>
-      <c r="J112" s="120"/>
-      <c r="K112" s="120"/>
-      <c r="L112" s="120"/>
-      <c r="M112" s="120"/>
-      <c r="N112" s="120"/>
-      <c r="O112" s="120"/>
-      <c r="P112" s="120"/>
-      <c r="Q112" s="120"/>
-      <c r="R112" s="120"/>
-      <c r="S112" s="120"/>
-      <c r="T112" s="120"/>
-      <c r="U112" s="120"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
+      <c r="I112" s="20"/>
+      <c r="J112" s="20"/>
+      <c r="K112" s="20"/>
+      <c r="L112" s="20"/>
+      <c r="M112" s="20"/>
+      <c r="N112" s="20"/>
+      <c r="O112" s="20"/>
+      <c r="P112" s="20"/>
+      <c r="Q112" s="20"/>
+      <c r="R112" s="20"/>
+      <c r="S112" s="20"/>
+      <c r="T112" s="20"/>
+      <c r="U112" s="20"/>
     </row>
     <row r="113" spans="2:21" ht="14.250000">
-      <c r="C113" s="120"/>
-      <c r="D113" s="120" t="s">
+      <c r="C113" s="20"/>
+      <c r="D113" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E113" s="120"/>
-      <c r="F113" s="120"/>
-      <c r="G113" s="120"/>
-      <c r="H113" s="120"/>
-      <c r="I113" s="120"/>
-      <c r="J113" s="120"/>
-      <c r="K113" s="120"/>
-      <c r="L113" s="120"/>
-      <c r="M113" s="120"/>
-      <c r="N113" s="120"/>
-      <c r="O113" s="120"/>
-      <c r="P113" s="120"/>
-      <c r="Q113" s="120"/>
-      <c r="R113" s="120"/>
-      <c r="S113" s="120"/>
-      <c r="T113" s="120"/>
-      <c r="U113" s="120"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="20"/>
+      <c r="J113" s="20"/>
+      <c r="K113" s="20"/>
+      <c r="L113" s="20"/>
+      <c r="M113" s="20"/>
+      <c r="N113" s="20"/>
+      <c r="O113" s="20"/>
+      <c r="P113" s="20"/>
+      <c r="Q113" s="20"/>
+      <c r="R113" s="20"/>
+      <c r="S113" s="20"/>
+      <c r="T113" s="20"/>
+      <c r="U113" s="20"/>
     </row>
     <row r="114" spans="2:21" ht="38.000000" customHeight="1">
-      <c r="C114" s="120"/>
-      <c r="D114" s="191" t="s">
+      <c r="C114" s="20"/>
+      <c r="D114" s="187" t="s">
         <v>130</v>
       </c>
-      <c r="E114" s="191"/>
-      <c r="F114" s="191"/>
-      <c r="G114" s="191"/>
-      <c r="H114" s="191"/>
-      <c r="I114" s="191"/>
-      <c r="J114" s="191"/>
-      <c r="K114" s="191"/>
-      <c r="L114" s="191"/>
-      <c r="M114" s="191"/>
-      <c r="N114" s="191"/>
-      <c r="O114" s="191"/>
-      <c r="P114" s="191"/>
-      <c r="Q114" s="191"/>
-      <c r="R114" s="191"/>
-      <c r="S114" s="191"/>
-      <c r="T114" s="191"/>
-      <c r="U114" s="191"/>
+      <c r="E114" s="187"/>
+      <c r="F114" s="187"/>
+      <c r="G114" s="187"/>
+      <c r="H114" s="187"/>
+      <c r="I114" s="187"/>
+      <c r="J114" s="187"/>
+      <c r="K114" s="187"/>
+      <c r="L114" s="187"/>
+      <c r="M114" s="187"/>
+      <c r="N114" s="187"/>
+      <c r="O114" s="187"/>
+      <c r="P114" s="187"/>
+      <c r="Q114" s="187"/>
+      <c r="R114" s="187"/>
+      <c r="S114" s="187"/>
+      <c r="T114" s="187"/>
+      <c r="U114" s="187"/>
     </row>
     <row r="115" spans="2:21" ht="33.000000" customHeight="1">
-      <c r="C115" s="120"/>
-      <c r="D115" s="120" t="s">
+      <c r="C115" s="20"/>
+      <c r="D115" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E115" s="120"/>
-      <c r="F115" s="120"/>
-      <c r="G115" s="120"/>
-      <c r="H115" s="120"/>
-      <c r="I115" s="120"/>
-      <c r="J115" s="120"/>
-      <c r="K115" s="120"/>
-      <c r="L115" s="120"/>
-      <c r="M115" s="120"/>
-      <c r="N115" s="120"/>
-      <c r="O115" s="120"/>
-      <c r="P115" s="120"/>
-      <c r="Q115" s="120"/>
-      <c r="R115" s="120"/>
-      <c r="S115" s="120"/>
-      <c r="T115" s="120"/>
-      <c r="U115" s="120"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="20"/>
+      <c r="G115" s="20"/>
+      <c r="H115" s="20"/>
+      <c r="I115" s="20"/>
+      <c r="J115" s="20"/>
+      <c r="K115" s="20"/>
+      <c r="L115" s="20"/>
+      <c r="M115" s="20"/>
+      <c r="N115" s="20"/>
+      <c r="O115" s="20"/>
+      <c r="P115" s="20"/>
+      <c r="Q115" s="20"/>
+      <c r="R115" s="20"/>
+      <c r="S115" s="20"/>
+      <c r="T115" s="20"/>
+      <c r="U115" s="20"/>
     </row>
     <row r="116" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="C116" s="120" t="s">
+      <c r="C116" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D116" s="120"/>
-      <c r="E116" s="120"/>
-      <c r="F116" s="120"/>
-      <c r="G116" s="120"/>
-      <c r="H116" s="120"/>
-      <c r="I116" s="120"/>
-      <c r="J116" s="120"/>
-      <c r="K116" s="120"/>
-      <c r="L116" s="120"/>
-      <c r="M116" s="120"/>
-      <c r="N116" s="120"/>
-      <c r="O116" s="120"/>
-      <c r="P116" s="120"/>
-      <c r="Q116" s="120"/>
-      <c r="R116" s="120"/>
-      <c r="S116" s="120"/>
-      <c r="T116" s="120"/>
-      <c r="U116" s="120"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20"/>
+      <c r="H116" s="20"/>
+      <c r="I116" s="20"/>
+      <c r="J116" s="20"/>
+      <c r="K116" s="20"/>
+      <c r="L116" s="20"/>
+      <c r="M116" s="20"/>
+      <c r="N116" s="20"/>
+      <c r="O116" s="20"/>
+      <c r="P116" s="20"/>
+      <c r="Q116" s="20"/>
+      <c r="R116" s="20"/>
+      <c r="S116" s="20"/>
+      <c r="T116" s="20"/>
+      <c r="U116" s="20"/>
     </row>
     <row r="117" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B117" s="116"/>
@@ -39785,98 +39704,98 @@
       <c r="U117" s="46"/>
     </row>
     <row r="118" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B118" s="163" t="s">
+      <c r="B118" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="C118" s="163"/>
-      <c r="D118" s="163"/>
-      <c r="E118" s="163"/>
-      <c r="F118" s="163"/>
-      <c r="G118" s="163"/>
-      <c r="H118" s="163"/>
-      <c r="I118" s="163"/>
-      <c r="J118" s="163"/>
-      <c r="K118" s="163"/>
-      <c r="L118" s="163"/>
-      <c r="M118" s="163"/>
-      <c r="N118" s="163"/>
-      <c r="O118" s="163"/>
-      <c r="P118" s="163"/>
-      <c r="Q118" s="163"/>
-      <c r="R118" s="163"/>
-      <c r="S118" s="163"/>
-      <c r="T118" s="163"/>
-      <c r="U118" s="163"/>
+      <c r="C118" s="161"/>
+      <c r="D118" s="161"/>
+      <c r="E118" s="161"/>
+      <c r="F118" s="161"/>
+      <c r="G118" s="161"/>
+      <c r="H118" s="161"/>
+      <c r="I118" s="161"/>
+      <c r="J118" s="161"/>
+      <c r="K118" s="161"/>
+      <c r="L118" s="161"/>
+      <c r="M118" s="161"/>
+      <c r="N118" s="161"/>
+      <c r="O118" s="161"/>
+      <c r="P118" s="161"/>
+      <c r="Q118" s="161"/>
+      <c r="R118" s="161"/>
+      <c r="S118" s="161"/>
+      <c r="T118" s="161"/>
+      <c r="U118" s="161"/>
     </row>
     <row r="119" spans="2:21" ht="33.000000" customHeight="1">
-      <c r="C119" s="120" t="s">
+      <c r="C119" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D119" s="120"/>
-      <c r="E119" s="120"/>
-      <c r="F119" s="120"/>
-      <c r="G119" s="120"/>
-      <c r="H119" s="120"/>
-      <c r="I119" s="120"/>
-      <c r="J119" s="120"/>
-      <c r="K119" s="120"/>
-      <c r="L119" s="120"/>
-      <c r="M119" s="120"/>
-      <c r="N119" s="120"/>
-      <c r="O119" s="120"/>
-      <c r="P119" s="120"/>
-      <c r="Q119" s="120"/>
-      <c r="R119" s="120"/>
-      <c r="S119" s="120"/>
-      <c r="T119" s="120"/>
-      <c r="U119" s="120"/>
+      <c r="D119" s="20"/>
+      <c r="E119" s="20"/>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="20"/>
+      <c r="J119" s="20"/>
+      <c r="K119" s="20"/>
+      <c r="L119" s="20"/>
+      <c r="M119" s="20"/>
+      <c r="N119" s="20"/>
+      <c r="O119" s="20"/>
+      <c r="P119" s="20"/>
+      <c r="Q119" s="20"/>
+      <c r="R119" s="20"/>
+      <c r="S119" s="20"/>
+      <c r="T119" s="20"/>
+      <c r="U119" s="20"/>
     </row>
     <row r="120" spans="2:21" ht="32.000000" customHeight="1">
-      <c r="C120" s="120" t="s">
+      <c r="C120" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D120" s="120"/>
-      <c r="E120" s="120"/>
-      <c r="F120" s="120"/>
-      <c r="G120" s="120"/>
-      <c r="H120" s="120"/>
-      <c r="I120" s="120"/>
-      <c r="J120" s="120"/>
-      <c r="K120" s="120"/>
-      <c r="L120" s="120"/>
-      <c r="M120" s="120"/>
-      <c r="N120" s="120"/>
-      <c r="O120" s="120"/>
-      <c r="P120" s="120"/>
-      <c r="Q120" s="120"/>
-      <c r="R120" s="120"/>
-      <c r="S120" s="120"/>
-      <c r="T120" s="120"/>
-      <c r="U120" s="120"/>
+      <c r="D120" s="20"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="20"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="20"/>
+      <c r="J120" s="20"/>
+      <c r="K120" s="20"/>
+      <c r="L120" s="20"/>
+      <c r="M120" s="20"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="20"/>
+      <c r="P120" s="20"/>
+      <c r="Q120" s="20"/>
+      <c r="R120" s="20"/>
+      <c r="S120" s="20"/>
+      <c r="T120" s="20"/>
+      <c r="U120" s="20"/>
     </row>
     <row r="121" spans="2:21" ht="33.000000" customHeight="1">
       <c r="B121" s="116"/>
-      <c r="C121" s="120" t="s">
+      <c r="C121" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D121" s="120"/>
-      <c r="E121" s="120"/>
-      <c r="F121" s="120"/>
-      <c r="G121" s="120"/>
-      <c r="H121" s="120"/>
-      <c r="I121" s="120"/>
-      <c r="J121" s="120"/>
-      <c r="K121" s="120"/>
-      <c r="L121" s="120"/>
-      <c r="M121" s="120"/>
-      <c r="N121" s="120"/>
-      <c r="O121" s="120"/>
-      <c r="P121" s="120"/>
-      <c r="Q121" s="120"/>
-      <c r="R121" s="120"/>
-      <c r="S121" s="120"/>
-      <c r="T121" s="120"/>
-      <c r="U121" s="120"/>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="20"/>
+      <c r="I121" s="20"/>
+      <c r="J121" s="20"/>
+      <c r="K121" s="20"/>
+      <c r="L121" s="20"/>
+      <c r="M121" s="20"/>
+      <c r="N121" s="20"/>
+      <c r="O121" s="20"/>
+      <c r="P121" s="20"/>
+      <c r="Q121" s="20"/>
+      <c r="R121" s="20"/>
+      <c r="S121" s="20"/>
+      <c r="T121" s="20"/>
+      <c r="U121" s="20"/>
     </row>
     <row r="122" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B122" s="116"/>
@@ -39901,51 +39820,51 @@
       <c r="U122" s="46"/>
     </row>
     <row r="123" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B123" s="163" t="s">
+      <c r="B123" s="161" t="s">
         <v>136</v>
       </c>
-      <c r="C123" s="163"/>
-      <c r="D123" s="163"/>
-      <c r="E123" s="163"/>
-      <c r="F123" s="163"/>
-      <c r="G123" s="163"/>
-      <c r="H123" s="163"/>
-      <c r="I123" s="163"/>
-      <c r="J123" s="163"/>
-      <c r="K123" s="163"/>
-      <c r="L123" s="163"/>
-      <c r="M123" s="163"/>
-      <c r="N123" s="163"/>
-      <c r="O123" s="163"/>
-      <c r="P123" s="163"/>
-      <c r="Q123" s="163"/>
-      <c r="R123" s="163"/>
-      <c r="S123" s="163"/>
-      <c r="T123" s="163"/>
-      <c r="U123" s="163"/>
+      <c r="C123" s="161"/>
+      <c r="D123" s="161"/>
+      <c r="E123" s="161"/>
+      <c r="F123" s="161"/>
+      <c r="G123" s="161"/>
+      <c r="H123" s="161"/>
+      <c r="I123" s="161"/>
+      <c r="J123" s="161"/>
+      <c r="K123" s="161"/>
+      <c r="L123" s="161"/>
+      <c r="M123" s="161"/>
+      <c r="N123" s="161"/>
+      <c r="O123" s="161"/>
+      <c r="P123" s="161"/>
+      <c r="Q123" s="161"/>
+      <c r="R123" s="161"/>
+      <c r="S123" s="161"/>
+      <c r="T123" s="161"/>
+      <c r="U123" s="161"/>
     </row>
     <row r="124" spans="2:21" ht="33.000000" customHeight="1">
-      <c r="C124" s="120" t="s">
+      <c r="C124" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D124" s="120"/>
-      <c r="E124" s="120"/>
-      <c r="F124" s="120"/>
-      <c r="G124" s="120"/>
-      <c r="H124" s="120"/>
-      <c r="I124" s="120"/>
-      <c r="J124" s="120"/>
-      <c r="K124" s="120"/>
-      <c r="L124" s="120"/>
-      <c r="M124" s="120"/>
-      <c r="N124" s="120"/>
-      <c r="O124" s="120"/>
-      <c r="P124" s="120"/>
-      <c r="Q124" s="120"/>
-      <c r="R124" s="120"/>
-      <c r="S124" s="120"/>
-      <c r="T124" s="120"/>
-      <c r="U124" s="120"/>
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="20"/>
+      <c r="J124" s="20"/>
+      <c r="K124" s="20"/>
+      <c r="L124" s="20"/>
+      <c r="M124" s="20"/>
+      <c r="N124" s="20"/>
+      <c r="O124" s="20"/>
+      <c r="P124" s="20"/>
+      <c r="Q124" s="20"/>
+      <c r="R124" s="20"/>
+      <c r="S124" s="20"/>
+      <c r="T124" s="20"/>
+      <c r="U124" s="20"/>
     </row>
     <row r="125" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B125" s="116"/>
@@ -39970,40 +39889,40 @@
       <c r="U125" s="46"/>
     </row>
     <row r="126" spans="2:21" ht="20.000000" customHeight="1">
-      <c r="B126" s="163" t="s">
+      <c r="B126" s="161" t="s">
         <v>137</v>
       </c>
-      <c r="C126" s="163"/>
-      <c r="D126" s="163"/>
-      <c r="E126" s="163"/>
-      <c r="F126" s="163"/>
-      <c r="G126" s="163"/>
-      <c r="H126" s="163"/>
-      <c r="I126" s="163"/>
-      <c r="J126" s="163"/>
+      <c r="C126" s="161"/>
+      <c r="D126" s="161"/>
+      <c r="E126" s="161"/>
+      <c r="F126" s="161"/>
+      <c r="G126" s="161"/>
+      <c r="H126" s="161"/>
+      <c r="I126" s="161"/>
+      <c r="J126" s="161"/>
     </row>
     <row r="127" spans="2:21" ht="40.000000" customHeight="1">
-      <c r="C127" s="120" t="s">
+      <c r="C127" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="120"/>
-      <c r="E127" s="120"/>
-      <c r="F127" s="120"/>
-      <c r="G127" s="120"/>
-      <c r="H127" s="120"/>
-      <c r="I127" s="120"/>
-      <c r="J127" s="120"/>
-      <c r="K127" s="120"/>
-      <c r="L127" s="120"/>
-      <c r="M127" s="120"/>
-      <c r="N127" s="120"/>
-      <c r="O127" s="120"/>
-      <c r="P127" s="120"/>
-      <c r="Q127" s="120"/>
-      <c r="R127" s="120"/>
-      <c r="S127" s="120"/>
-      <c r="T127" s="120"/>
-      <c r="U127" s="120"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="20"/>
+      <c r="I127" s="20"/>
+      <c r="J127" s="20"/>
+      <c r="K127" s="20"/>
+      <c r="L127" s="20"/>
+      <c r="M127" s="20"/>
+      <c r="N127" s="20"/>
+      <c r="O127" s="20"/>
+      <c r="P127" s="20"/>
+      <c r="Q127" s="20"/>
+      <c r="R127" s="20"/>
+      <c r="S127" s="20"/>
+      <c r="T127" s="20"/>
+      <c r="U127" s="20"/>
     </row>
     <row r="128" spans="2:21" ht="409.500000" customHeight="1">
       <c r="B128" s="116"/>
